--- a/Source Data Process_CB/Biagolini_SuppTable1.xlsx
+++ b/Source Data Process_CB/Biagolini_SuppTable1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kate/Desktop/CooperativeBreedingEvolution/Source Data Process_CB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB3E1A7C-EF95-4E47-AB47-A620B9306F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DBF515-2F65-3A48-8F3D-A0DEFB313D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1160" yWindow="660" windowWidth="28040" windowHeight="17280" xr2:uid="{10AD7567-51C1-244C-9C49-3C4EE696AFD4}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1741" uniqueCount="959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2530" uniqueCount="959">
   <si>
     <t>OR</t>
   </si>
@@ -3567,10 +3567,18 @@
       <c r="I3" s="7">
         <v>44</v>
       </c>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
+      <c r="J3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N3" s="5" t="s">
         <v>18</v>
       </c>
@@ -3647,10 +3655,18 @@
       <c r="I5" s="7">
         <v>19</v>
       </c>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
+      <c r="J5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N5" s="5" t="s">
         <v>23</v>
       </c>
@@ -3683,10 +3699,18 @@
       <c r="I6" s="7">
         <v>40</v>
       </c>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
+      <c r="J6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N6" s="5" t="s">
         <v>25</v>
       </c>
@@ -3719,10 +3743,18 @@
       <c r="I7" s="7">
         <v>25</v>
       </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="J7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N7" s="5" t="s">
         <v>28</v>
       </c>
@@ -3755,10 +3787,18 @@
       <c r="I8" s="7">
         <v>23</v>
       </c>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+      <c r="J8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N8" s="5" t="s">
         <v>30</v>
       </c>
@@ -3791,10 +3831,18 @@
       <c r="I9" s="7">
         <v>24</v>
       </c>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
+      <c r="J9" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N9" s="5" t="s">
         <v>30</v>
       </c>
@@ -3827,10 +3875,18 @@
       <c r="I10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="7"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
+      <c r="J10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="N10" s="5" t="s">
         <v>33</v>
       </c>
@@ -3863,10 +3919,18 @@
       <c r="I11" s="7">
         <v>42</v>
       </c>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
+      <c r="J11" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N11" s="5" t="s">
         <v>35</v>
       </c>
@@ -3899,10 +3963,18 @@
       <c r="I12" s="7">
         <v>72</v>
       </c>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
+      <c r="J12" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N12" s="5" t="s">
         <v>37</v>
       </c>
@@ -3935,10 +4007,18 @@
       <c r="I13" s="7">
         <v>85</v>
       </c>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
+      <c r="J13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N13" s="5" t="s">
         <v>39</v>
       </c>
@@ -3971,10 +4051,18 @@
       <c r="I14" s="7">
         <v>4</v>
       </c>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
+      <c r="J14" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N14" s="5" t="s">
         <v>41</v>
       </c>
@@ -4007,10 +4095,18 @@
       <c r="I15" s="7">
         <v>38</v>
       </c>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
+      <c r="J15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N15" s="5" t="s">
         <v>44</v>
       </c>
@@ -4087,10 +4183,18 @@
       <c r="I17" s="7">
         <v>4</v>
       </c>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
+      <c r="J17" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N17" s="5" t="s">
         <v>51</v>
       </c>
@@ -4123,10 +4227,18 @@
       <c r="I18" s="7">
         <v>16</v>
       </c>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
+      <c r="J18" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N18" s="5" t="s">
         <v>54</v>
       </c>
@@ -4159,10 +4271,18 @@
       <c r="I19" s="7">
         <v>88</v>
       </c>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
+      <c r="J19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N19" s="5" t="s">
         <v>57</v>
       </c>
@@ -4195,10 +4315,18 @@
       <c r="I20" s="7">
         <v>32</v>
       </c>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
+      <c r="J20" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N20" s="5" t="s">
         <v>59</v>
       </c>
@@ -4231,10 +4359,18 @@
       <c r="I21" s="7">
         <v>38</v>
       </c>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
+      <c r="J21" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N21" s="5" t="s">
         <v>61</v>
       </c>
@@ -4267,10 +4403,18 @@
       <c r="I22" s="7">
         <v>77</v>
       </c>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
+      <c r="J22" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N22" s="5" t="s">
         <v>63</v>
       </c>
@@ -4303,10 +4447,18 @@
       <c r="I23" s="7">
         <v>27</v>
       </c>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
+      <c r="J23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N23" s="5" t="s">
         <v>65</v>
       </c>
@@ -4383,10 +4535,18 @@
       <c r="I25" s="7">
         <v>24</v>
       </c>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
+      <c r="J25" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N25" s="5" t="s">
         <v>71</v>
       </c>
@@ -4463,10 +4623,18 @@
       <c r="I27" s="7">
         <v>20</v>
       </c>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
+      <c r="J27" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N27" s="5" t="s">
         <v>76</v>
       </c>
@@ -4499,10 +4667,18 @@
       <c r="I28" s="7">
         <v>26</v>
       </c>
-      <c r="J28" s="7"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
+      <c r="J28" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="N28" s="5" t="s">
         <v>79</v>
       </c>
@@ -4623,10 +4799,18 @@
       <c r="I31" s="7">
         <v>30</v>
       </c>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8"/>
+      <c r="J31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N31" s="5" t="s">
         <v>88</v>
       </c>
@@ -4659,10 +4843,18 @@
       <c r="I32" s="7">
         <v>11</v>
       </c>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
+      <c r="J32" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N32" s="5" t="s">
         <v>90</v>
       </c>
@@ -4695,10 +4887,18 @@
       <c r="I33" s="7">
         <v>24</v>
       </c>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
+      <c r="J33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M33" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N33" s="5" t="s">
         <v>92</v>
       </c>
@@ -4731,10 +4931,18 @@
       <c r="I34" s="7">
         <v>22</v>
       </c>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
+      <c r="J34" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M34" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N34" s="5" t="s">
         <v>94</v>
       </c>
@@ -4767,10 +4975,18 @@
       <c r="I35" s="7">
         <v>30</v>
       </c>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8"/>
+      <c r="J35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M35" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N35" s="5" t="s">
         <v>96</v>
       </c>
@@ -4803,10 +5019,18 @@
       <c r="I36" s="7">
         <v>83</v>
       </c>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="8"/>
+      <c r="J36" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M36" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N36" s="5" t="s">
         <v>98</v>
       </c>
@@ -4839,10 +5063,18 @@
       <c r="I37" s="7">
         <v>10</v>
       </c>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="8"/>
+      <c r="J37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M37" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N37" s="5" t="s">
         <v>100</v>
       </c>
@@ -4919,10 +5151,18 @@
       <c r="I39" s="7">
         <v>15</v>
       </c>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
-      <c r="L39" s="8"/>
-      <c r="M39" s="8"/>
+      <c r="J39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M39" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N39" s="5" t="s">
         <v>106</v>
       </c>
@@ -4999,10 +5239,18 @@
       <c r="I41" s="7">
         <v>56</v>
       </c>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
-      <c r="L41" s="8"/>
-      <c r="M41" s="8"/>
+      <c r="J41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M41" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N41" s="5" t="s">
         <v>110</v>
       </c>
@@ -5035,10 +5283,18 @@
       <c r="I42" s="7">
         <v>27</v>
       </c>
-      <c r="J42" s="8"/>
-      <c r="K42" s="8"/>
-      <c r="L42" s="8"/>
-      <c r="M42" s="8"/>
+      <c r="J42" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K42" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L42" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M42" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N42" s="5" t="s">
         <v>112</v>
       </c>
@@ -5071,10 +5327,18 @@
       <c r="I43" s="7">
         <v>40</v>
       </c>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
-      <c r="M43" s="8"/>
+      <c r="J43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M43" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N43" s="5" t="s">
         <v>114</v>
       </c>
@@ -5107,10 +5371,18 @@
       <c r="I44" s="7">
         <v>47</v>
       </c>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8"/>
-      <c r="L44" s="8"/>
-      <c r="M44" s="8"/>
+      <c r="J44" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M44" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N44" s="5" t="s">
         <v>117</v>
       </c>
@@ -5231,10 +5503,18 @@
       <c r="I47" s="7">
         <v>15</v>
       </c>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
-      <c r="M47" s="8"/>
+      <c r="J47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M47" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N47" s="5" t="s">
         <v>123</v>
       </c>
@@ -5267,10 +5547,18 @@
       <c r="I48" s="7">
         <v>16</v>
       </c>
-      <c r="J48" s="8"/>
-      <c r="K48" s="8"/>
-      <c r="L48" s="8"/>
-      <c r="M48" s="8"/>
+      <c r="J48" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K48" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L48" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M48" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N48" s="5" t="s">
         <v>126</v>
       </c>
@@ -5303,10 +5591,18 @@
       <c r="I49" s="7">
         <v>13</v>
       </c>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="8"/>
+      <c r="J49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M49" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N49" s="5" t="s">
         <v>128</v>
       </c>
@@ -5383,10 +5679,18 @@
       <c r="I51" s="7">
         <v>49</v>
       </c>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="8"/>
-      <c r="M51" s="8"/>
+      <c r="J51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M51" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N51" s="5" t="s">
         <v>134</v>
       </c>
@@ -5463,10 +5767,18 @@
       <c r="I53" s="7">
         <v>21</v>
       </c>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="8"/>
-      <c r="M53" s="8"/>
+      <c r="J53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M53" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N53" s="5" t="s">
         <v>139</v>
       </c>
@@ -5499,10 +5811,18 @@
       <c r="I54" s="7">
         <v>18</v>
       </c>
-      <c r="J54" s="8"/>
-      <c r="K54" s="8"/>
-      <c r="L54" s="8"/>
-      <c r="M54" s="8"/>
+      <c r="J54" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L54" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M54" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N54" s="5" t="s">
         <v>142</v>
       </c>
@@ -5535,10 +5855,18 @@
       <c r="I55" s="7">
         <v>17</v>
       </c>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="8"/>
-      <c r="M55" s="8"/>
+      <c r="J55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M55" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N55" s="5" t="s">
         <v>144</v>
       </c>
@@ -5571,10 +5899,18 @@
       <c r="I56" s="7">
         <v>31</v>
       </c>
-      <c r="J56" s="8"/>
-      <c r="K56" s="8"/>
-      <c r="L56" s="8"/>
-      <c r="M56" s="8"/>
+      <c r="J56" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L56" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M56" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N56" s="5" t="s">
         <v>146</v>
       </c>
@@ -5607,10 +5943,18 @@
       <c r="I57" s="7">
         <v>35</v>
       </c>
-      <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="8"/>
-      <c r="M57" s="8"/>
+      <c r="J57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M57" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N57" s="5" t="s">
         <v>148</v>
       </c>
@@ -5643,10 +5987,18 @@
       <c r="I58" s="7">
         <v>21</v>
       </c>
-      <c r="J58" s="8"/>
-      <c r="K58" s="8"/>
-      <c r="L58" s="8"/>
-      <c r="M58" s="8"/>
+      <c r="J58" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K58" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L58" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M58" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N58" s="5" t="s">
         <v>150</v>
       </c>
@@ -5855,10 +6207,18 @@
       <c r="I63" s="7">
         <v>18</v>
       </c>
-      <c r="J63" s="8"/>
-      <c r="K63" s="8"/>
-      <c r="L63" s="8"/>
-      <c r="M63" s="8"/>
+      <c r="J63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M63" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N63" s="5" t="s">
         <v>163</v>
       </c>
@@ -5935,10 +6295,18 @@
       <c r="I65" s="7">
         <v>146</v>
       </c>
-      <c r="J65" s="8"/>
-      <c r="K65" s="8"/>
-      <c r="L65" s="8"/>
-      <c r="M65" s="8"/>
+      <c r="J65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M65" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N65" s="5" t="s">
         <v>167</v>
       </c>
@@ -5971,10 +6339,18 @@
       <c r="I66" s="7">
         <v>31</v>
       </c>
-      <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
-      <c r="L66" s="8"/>
-      <c r="M66" s="8"/>
+      <c r="J66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M66" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N66" s="5" t="s">
         <v>169</v>
       </c>
@@ -6007,10 +6383,18 @@
       <c r="I67" s="7">
         <v>47</v>
       </c>
-      <c r="J67" s="8"/>
-      <c r="K67" s="8"/>
-      <c r="L67" s="8"/>
-      <c r="M67" s="8"/>
+      <c r="J67" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K67" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L67" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M67" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N67" s="5" t="s">
         <v>172</v>
       </c>
@@ -6043,10 +6427,18 @@
       <c r="I68" s="7">
         <v>18</v>
       </c>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="8"/>
-      <c r="M68" s="8"/>
+      <c r="J68" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K68" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L68" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M68" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N68" s="5" t="s">
         <v>175</v>
       </c>
@@ -6079,10 +6471,18 @@
       <c r="I69" s="7">
         <v>13</v>
       </c>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8"/>
-      <c r="L69" s="8"/>
-      <c r="M69" s="8"/>
+      <c r="J69" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K69" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L69" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M69" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N69" s="5" t="s">
         <v>178</v>
       </c>
@@ -6115,10 +6515,18 @@
       <c r="I70" s="7">
         <v>11</v>
       </c>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="8"/>
+      <c r="J70" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K70" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L70" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M70" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N70" s="5" t="s">
         <v>180</v>
       </c>
@@ -6503,10 +6911,18 @@
       <c r="I79" s="7">
         <v>52</v>
       </c>
-      <c r="J79" s="8"/>
-      <c r="K79" s="8"/>
-      <c r="L79" s="8"/>
-      <c r="M79" s="8"/>
+      <c r="J79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M79" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N79" s="5" t="s">
         <v>203</v>
       </c>
@@ -6539,10 +6955,18 @@
       <c r="I80" s="7">
         <v>39</v>
       </c>
-      <c r="J80" s="8"/>
-      <c r="K80" s="8"/>
-      <c r="L80" s="8"/>
-      <c r="M80" s="8"/>
+      <c r="J80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M80" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N80" s="5" t="s">
         <v>206</v>
       </c>
@@ -6575,10 +6999,18 @@
       <c r="I81" s="7">
         <v>19</v>
       </c>
-      <c r="J81" s="8"/>
-      <c r="K81" s="8"/>
-      <c r="L81" s="8"/>
-      <c r="M81" s="8"/>
+      <c r="J81" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K81" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L81" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M81" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N81" s="5" t="s">
         <v>209</v>
       </c>
@@ -6611,10 +7043,18 @@
       <c r="I82" s="7">
         <v>20</v>
       </c>
-      <c r="J82" s="8"/>
-      <c r="K82" s="8"/>
-      <c r="L82" s="8"/>
-      <c r="M82" s="8"/>
+      <c r="J82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M82" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N82" s="5" t="s">
         <v>211</v>
       </c>
@@ -6647,10 +7087,18 @@
       <c r="I83" s="7">
         <v>25</v>
       </c>
-      <c r="J83" s="8"/>
-      <c r="K83" s="8"/>
-      <c r="L83" s="8"/>
-      <c r="M83" s="8"/>
+      <c r="J83" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K83" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L83" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M83" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N83" s="5" t="s">
         <v>213</v>
       </c>
@@ -6727,10 +7175,18 @@
       <c r="I85" s="7">
         <v>40</v>
       </c>
-      <c r="J85" s="8"/>
-      <c r="K85" s="8"/>
-      <c r="L85" s="8"/>
-      <c r="M85" s="8"/>
+      <c r="J85" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K85" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L85" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M85" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N85" s="5" t="s">
         <v>218</v>
       </c>
@@ -6895,10 +7351,18 @@
       <c r="I89" s="7">
         <v>35</v>
       </c>
-      <c r="J89" s="8"/>
-      <c r="K89" s="8"/>
-      <c r="L89" s="8"/>
-      <c r="M89" s="8"/>
+      <c r="J89" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K89" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L89" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M89" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N89" s="5" t="s">
         <v>228</v>
       </c>
@@ -6931,10 +7395,18 @@
       <c r="I90" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J90" s="8"/>
-      <c r="K90" s="8"/>
-      <c r="L90" s="8"/>
-      <c r="M90" s="8"/>
+      <c r="J90" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K90" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L90" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M90" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N90" s="5" t="s">
         <v>230</v>
       </c>
@@ -6967,10 +7439,18 @@
       <c r="I91" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J91" s="8"/>
-      <c r="K91" s="8"/>
-      <c r="L91" s="8"/>
-      <c r="M91" s="8"/>
+      <c r="J91" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K91" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L91" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M91" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N91" s="5" t="s">
         <v>232</v>
       </c>
@@ -7091,10 +7571,18 @@
       <c r="I94" s="7">
         <v>12</v>
       </c>
-      <c r="J94" s="8"/>
-      <c r="K94" s="8"/>
-      <c r="L94" s="8"/>
-      <c r="M94" s="8"/>
+      <c r="J94" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K94" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L94" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M94" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N94" s="5" t="s">
         <v>240</v>
       </c>
@@ -7127,10 +7615,18 @@
       <c r="I95" s="7">
         <v>18</v>
       </c>
-      <c r="J95" s="8"/>
-      <c r="K95" s="8"/>
-      <c r="L95" s="8"/>
-      <c r="M95" s="8"/>
+      <c r="J95" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K95" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L95" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M95" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N95" s="5" t="s">
         <v>243</v>
       </c>
@@ -7251,10 +7747,18 @@
       <c r="I98" s="7">
         <v>32</v>
       </c>
-      <c r="J98" s="8"/>
-      <c r="K98" s="8"/>
-      <c r="L98" s="8"/>
-      <c r="M98" s="8"/>
+      <c r="J98" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K98" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L98" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M98" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N98" s="5" t="s">
         <v>249</v>
       </c>
@@ -7287,10 +7791,18 @@
       <c r="I99" s="7">
         <v>572</v>
       </c>
-      <c r="J99" s="8"/>
-      <c r="K99" s="8"/>
-      <c r="L99" s="8"/>
-      <c r="M99" s="8"/>
+      <c r="J99" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K99" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L99" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M99" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N99" s="5" t="s">
         <v>251</v>
       </c>
@@ -7323,10 +7835,18 @@
       <c r="I100" s="7">
         <v>84</v>
       </c>
-      <c r="J100" s="8"/>
-      <c r="K100" s="8"/>
-      <c r="L100" s="8"/>
-      <c r="M100" s="8"/>
+      <c r="J100" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K100" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L100" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M100" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N100" s="5" t="s">
         <v>253</v>
       </c>
@@ -7359,10 +7879,18 @@
       <c r="I101" s="7">
         <v>34</v>
       </c>
-      <c r="J101" s="8"/>
-      <c r="K101" s="8"/>
-      <c r="L101" s="8"/>
-      <c r="M101" s="8"/>
+      <c r="J101" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K101" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L101" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M101" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N101" s="5" t="s">
         <v>255</v>
       </c>
@@ -7395,10 +7923,18 @@
       <c r="I102" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J102" s="8"/>
-      <c r="K102" s="8"/>
-      <c r="L102" s="8"/>
-      <c r="M102" s="8"/>
+      <c r="J102" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K102" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L102" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M102" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N102" s="5" t="s">
         <v>257</v>
       </c>
@@ -7431,10 +7967,18 @@
       <c r="I103" s="7">
         <v>113</v>
       </c>
-      <c r="J103" s="8"/>
-      <c r="K103" s="8"/>
-      <c r="L103" s="8"/>
-      <c r="M103" s="8"/>
+      <c r="J103" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K103" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L103" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M103" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N103" s="5" t="s">
         <v>259</v>
       </c>
@@ -7467,10 +8011,18 @@
       <c r="I104" s="7">
         <v>879</v>
       </c>
-      <c r="J104" s="8"/>
-      <c r="K104" s="8"/>
-      <c r="L104" s="8"/>
-      <c r="M104" s="8"/>
+      <c r="J104" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K104" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L104" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M104" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N104" s="5" t="s">
         <v>261</v>
       </c>
@@ -7547,10 +8099,18 @@
       <c r="I106" s="7">
         <v>228</v>
       </c>
-      <c r="J106" s="7"/>
-      <c r="K106" s="9"/>
-      <c r="L106" s="9"/>
-      <c r="M106" s="9"/>
+      <c r="J106" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K106" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="L106" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="M106" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="N106" s="5" t="s">
         <v>265</v>
       </c>
@@ -7583,10 +8143,18 @@
       <c r="I107" s="7">
         <v>91</v>
       </c>
-      <c r="J107" s="8"/>
-      <c r="K107" s="8"/>
-      <c r="L107" s="8"/>
-      <c r="M107" s="8"/>
+      <c r="J107" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K107" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L107" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M107" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N107" s="5" t="s">
         <v>267</v>
       </c>
@@ -7619,10 +8187,18 @@
       <c r="I108" s="7">
         <v>31</v>
       </c>
-      <c r="J108" s="8"/>
-      <c r="K108" s="8"/>
-      <c r="L108" s="8"/>
-      <c r="M108" s="8"/>
+      <c r="J108" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K108" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L108" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M108" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N108" s="5" t="s">
         <v>269</v>
       </c>
@@ -7655,10 +8231,18 @@
       <c r="I109" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J109" s="8"/>
-      <c r="K109" s="8"/>
-      <c r="L109" s="8"/>
-      <c r="M109" s="8"/>
+      <c r="J109" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K109" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L109" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M109" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N109" s="5" t="s">
         <v>271</v>
       </c>
@@ -7691,10 +8275,18 @@
       <c r="I110" s="7">
         <v>21</v>
       </c>
-      <c r="J110" s="8"/>
-      <c r="K110" s="8"/>
-      <c r="L110" s="8"/>
-      <c r="M110" s="8"/>
+      <c r="J110" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K110" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L110" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M110" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N110" s="5" t="s">
         <v>273</v>
       </c>
@@ -7727,10 +8319,18 @@
       <c r="I111" s="7">
         <v>52</v>
       </c>
-      <c r="J111" s="8"/>
-      <c r="K111" s="8"/>
-      <c r="L111" s="8"/>
-      <c r="M111" s="8"/>
+      <c r="J111" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K111" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L111" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M111" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N111" s="5" t="s">
         <v>275</v>
       </c>
@@ -7763,10 +8363,18 @@
       <c r="I112" s="7">
         <v>101</v>
       </c>
-      <c r="J112" s="8"/>
-      <c r="K112" s="8"/>
-      <c r="L112" s="8"/>
-      <c r="M112" s="8"/>
+      <c r="J112" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K112" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L112" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M112" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N112" s="5" t="s">
         <v>278</v>
       </c>
@@ -7799,10 +8407,18 @@
       <c r="I113" s="7">
         <v>96</v>
       </c>
-      <c r="J113" s="8"/>
-      <c r="K113" s="8"/>
-      <c r="L113" s="8"/>
-      <c r="M113" s="8"/>
+      <c r="J113" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K113" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L113" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M113" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N113" s="5" t="s">
         <v>280</v>
       </c>
@@ -7835,10 +8451,18 @@
       <c r="I114" s="7">
         <v>26</v>
       </c>
-      <c r="J114" s="8"/>
-      <c r="K114" s="8"/>
-      <c r="L114" s="8"/>
-      <c r="M114" s="8"/>
+      <c r="J114" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K114" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L114" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M114" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N114" s="5" t="s">
         <v>283</v>
       </c>
@@ -7871,10 +8495,18 @@
       <c r="I115" s="7">
         <v>15</v>
       </c>
-      <c r="J115" s="8"/>
-      <c r="K115" s="8"/>
-      <c r="L115" s="8"/>
-      <c r="M115" s="8"/>
+      <c r="J115" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K115" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L115" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M115" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N115" s="5" t="s">
         <v>285</v>
       </c>
@@ -7951,10 +8583,18 @@
       <c r="I117" s="7">
         <v>35</v>
       </c>
-      <c r="J117" s="8"/>
-      <c r="K117" s="8"/>
-      <c r="L117" s="8"/>
-      <c r="M117" s="8"/>
+      <c r="J117" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K117" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L117" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M117" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N117" s="5" t="s">
         <v>289</v>
       </c>
@@ -7987,10 +8627,18 @@
       <c r="I118" s="7">
         <v>13</v>
       </c>
-      <c r="J118" s="8"/>
-      <c r="K118" s="8"/>
-      <c r="L118" s="8"/>
-      <c r="M118" s="8"/>
+      <c r="J118" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K118" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L118" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M118" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N118" s="5" t="s">
         <v>291</v>
       </c>
@@ -8023,10 +8671,18 @@
       <c r="I119" s="7">
         <v>34</v>
       </c>
-      <c r="J119" s="8"/>
-      <c r="K119" s="8"/>
-      <c r="L119" s="8"/>
-      <c r="M119" s="8"/>
+      <c r="J119" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K119" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L119" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M119" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N119" s="5" t="s">
         <v>293</v>
       </c>
@@ -8059,10 +8715,18 @@
       <c r="I120" s="7">
         <v>15</v>
       </c>
-      <c r="J120" s="8"/>
-      <c r="K120" s="8"/>
-      <c r="L120" s="8"/>
-      <c r="M120" s="8"/>
+      <c r="J120" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K120" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L120" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M120" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N120" s="5" t="s">
         <v>295</v>
       </c>
@@ -8095,10 +8759,18 @@
       <c r="I121" s="7">
         <v>68</v>
       </c>
-      <c r="J121" s="8"/>
-      <c r="K121" s="8"/>
-      <c r="L121" s="8"/>
-      <c r="M121" s="8"/>
+      <c r="J121" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K121" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L121" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M121" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N121" s="5" t="s">
         <v>297</v>
       </c>
@@ -8131,10 +8803,18 @@
       <c r="I122" s="7">
         <v>47</v>
       </c>
-      <c r="J122" s="8"/>
-      <c r="K122" s="8"/>
-      <c r="L122" s="8"/>
-      <c r="M122" s="8"/>
+      <c r="J122" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K122" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L122" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M122" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N122" s="5" t="s">
         <v>300</v>
       </c>
@@ -8167,10 +8847,18 @@
       <c r="I123" s="7">
         <v>19</v>
       </c>
-      <c r="J123" s="8"/>
-      <c r="K123" s="8"/>
-      <c r="L123" s="8"/>
-      <c r="M123" s="8"/>
+      <c r="J123" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K123" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L123" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M123" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N123" s="5" t="s">
         <v>303</v>
       </c>
@@ -8203,10 +8891,18 @@
       <c r="I124" s="7">
         <v>20</v>
       </c>
-      <c r="J124" s="8"/>
-      <c r="K124" s="8"/>
-      <c r="L124" s="8"/>
-      <c r="M124" s="8"/>
+      <c r="J124" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K124" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L124" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M124" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N124" s="5" t="s">
         <v>304</v>
       </c>
@@ -8239,10 +8935,18 @@
       <c r="I125" s="7">
         <v>660</v>
       </c>
-      <c r="J125" s="8"/>
-      <c r="K125" s="8"/>
-      <c r="L125" s="8"/>
-      <c r="M125" s="8"/>
+      <c r="J125" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K125" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L125" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M125" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N125" s="5" t="s">
         <v>306</v>
       </c>
@@ -8275,10 +8979,18 @@
       <c r="I126" s="7">
         <v>70</v>
       </c>
-      <c r="J126" s="8"/>
-      <c r="K126" s="8"/>
-      <c r="L126" s="8"/>
-      <c r="M126" s="8"/>
+      <c r="J126" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K126" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L126" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M126" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N126" s="5" t="s">
         <v>308</v>
       </c>
@@ -8311,10 +9023,18 @@
       <c r="I127" s="7">
         <v>297</v>
       </c>
-      <c r="J127" s="8"/>
-      <c r="K127" s="8"/>
-      <c r="L127" s="8"/>
-      <c r="M127" s="8"/>
+      <c r="J127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M127" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N127" s="5" t="s">
         <v>310</v>
       </c>
@@ -8347,10 +9067,18 @@
       <c r="I128" s="7">
         <v>92</v>
       </c>
-      <c r="J128" s="8"/>
-      <c r="K128" s="8"/>
-      <c r="L128" s="8"/>
-      <c r="M128" s="8"/>
+      <c r="J128" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K128" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L128" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M128" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N128" s="5" t="s">
         <v>312</v>
       </c>
@@ -8383,10 +9111,18 @@
       <c r="I129" s="7">
         <v>31</v>
       </c>
-      <c r="J129" s="8"/>
-      <c r="K129" s="8"/>
-      <c r="L129" s="8"/>
-      <c r="M129" s="8"/>
+      <c r="J129" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K129" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L129" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M129" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N129" s="5" t="s">
         <v>314</v>
       </c>
@@ -8463,10 +9199,18 @@
       <c r="I131" s="7">
         <v>78</v>
       </c>
-      <c r="J131" s="8"/>
-      <c r="K131" s="8"/>
-      <c r="L131" s="8"/>
-      <c r="M131" s="8"/>
+      <c r="J131" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K131" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L131" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M131" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N131" s="5" t="s">
         <v>318</v>
       </c>
@@ -8499,10 +9243,18 @@
       <c r="I132" s="7">
         <v>52</v>
       </c>
-      <c r="J132" s="8"/>
-      <c r="K132" s="8"/>
-      <c r="L132" s="8"/>
-      <c r="M132" s="8"/>
+      <c r="J132" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K132" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L132" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M132" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N132" s="5" t="s">
         <v>320</v>
       </c>
@@ -8579,10 +9331,18 @@
       <c r="I134" s="7">
         <v>30</v>
       </c>
-      <c r="J134" s="8"/>
-      <c r="K134" s="8"/>
-      <c r="L134" s="8"/>
-      <c r="M134" s="8"/>
+      <c r="J134" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K134" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L134" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M134" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N134" s="5" t="s">
         <v>325</v>
       </c>
@@ -8615,10 +9375,18 @@
       <c r="I135" s="7">
         <v>48</v>
       </c>
-      <c r="J135" s="8"/>
-      <c r="K135" s="8"/>
-      <c r="L135" s="8"/>
-      <c r="M135" s="8"/>
+      <c r="J135" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K135" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L135" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M135" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N135" s="5" t="s">
         <v>327</v>
       </c>
@@ -8651,10 +9419,18 @@
       <c r="I136" s="7">
         <v>24</v>
       </c>
-      <c r="J136" s="8"/>
-      <c r="K136" s="8"/>
-      <c r="L136" s="8"/>
-      <c r="M136" s="8"/>
+      <c r="J136" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K136" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L136" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M136" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N136" s="5" t="s">
         <v>330</v>
       </c>
@@ -8731,10 +9507,18 @@
       <c r="I138" s="7">
         <v>36</v>
       </c>
-      <c r="J138" s="8"/>
-      <c r="K138" s="8"/>
-      <c r="L138" s="8"/>
-      <c r="M138" s="8"/>
+      <c r="J138" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K138" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L138" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M138" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N138" s="5" t="s">
         <v>334</v>
       </c>
@@ -8767,10 +9551,18 @@
       <c r="I139" s="7">
         <v>31</v>
       </c>
-      <c r="J139" s="8"/>
-      <c r="K139" s="8"/>
-      <c r="L139" s="8"/>
-      <c r="M139" s="8"/>
+      <c r="J139" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K139" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L139" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M139" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N139" s="5" t="s">
         <v>336</v>
       </c>
@@ -8803,10 +9595,18 @@
       <c r="I140" s="7">
         <v>44</v>
       </c>
-      <c r="J140" s="8"/>
-      <c r="K140" s="8"/>
-      <c r="L140" s="8"/>
-      <c r="M140" s="8"/>
+      <c r="J140" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K140" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L140" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M140" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N140" s="5" t="s">
         <v>339</v>
       </c>
@@ -9015,10 +9815,18 @@
       <c r="I145" s="7">
         <v>27</v>
       </c>
-      <c r="J145" s="8"/>
-      <c r="K145" s="8"/>
-      <c r="L145" s="8"/>
-      <c r="M145" s="8"/>
+      <c r="J145" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K145" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L145" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M145" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N145" s="5" t="s">
         <v>349</v>
       </c>
@@ -9051,10 +9859,18 @@
       <c r="I146" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J146" s="8"/>
-      <c r="K146" s="8"/>
-      <c r="L146" s="8"/>
-      <c r="M146" s="8"/>
+      <c r="J146" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K146" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L146" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M146" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N146" s="5" t="s">
         <v>352</v>
       </c>
@@ -9175,10 +9991,18 @@
       <c r="I149" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J149" s="8"/>
-      <c r="K149" s="8"/>
-      <c r="L149" s="8"/>
-      <c r="M149" s="8"/>
+      <c r="J149" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K149" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L149" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M149" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N149" s="5" t="s">
         <v>352</v>
       </c>
@@ -9211,10 +10035,18 @@
       <c r="I150" s="7">
         <v>57</v>
       </c>
-      <c r="J150" s="8"/>
-      <c r="K150" s="8"/>
-      <c r="L150" s="8"/>
-      <c r="M150" s="8"/>
+      <c r="J150" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K150" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L150" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M150" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N150" s="5" t="s">
         <v>359</v>
       </c>
@@ -9247,10 +10079,18 @@
       <c r="I151" s="7">
         <v>165</v>
       </c>
-      <c r="J151" s="8"/>
-      <c r="K151" s="8"/>
-      <c r="L151" s="8"/>
-      <c r="M151" s="8"/>
+      <c r="J151" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K151" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L151" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M151" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N151" s="5" t="s">
         <v>362</v>
       </c>
@@ -9415,10 +10255,18 @@
       <c r="I155" s="7">
         <v>33</v>
       </c>
-      <c r="J155" s="8"/>
-      <c r="K155" s="8"/>
-      <c r="L155" s="8"/>
-      <c r="M155" s="8"/>
+      <c r="J155" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K155" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L155" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M155" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N155" s="5" t="s">
         <v>373</v>
       </c>
@@ -9451,10 +10299,18 @@
       <c r="I156" s="7">
         <v>25</v>
       </c>
-      <c r="J156" s="8"/>
-      <c r="K156" s="8"/>
-      <c r="L156" s="8"/>
-      <c r="M156" s="8"/>
+      <c r="J156" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K156" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L156" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M156" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N156" s="5" t="s">
         <v>376</v>
       </c>
@@ -9531,10 +10387,18 @@
       <c r="I158" s="7">
         <v>65</v>
       </c>
-      <c r="J158" s="8"/>
-      <c r="K158" s="8"/>
-      <c r="L158" s="8"/>
-      <c r="M158" s="8"/>
+      <c r="J158" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K158" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L158" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M158" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N158" s="5" t="s">
         <v>383</v>
       </c>
@@ -9567,10 +10431,18 @@
       <c r="I159" s="7">
         <v>44</v>
       </c>
-      <c r="J159" s="8"/>
-      <c r="K159" s="8"/>
-      <c r="L159" s="8"/>
-      <c r="M159" s="8"/>
+      <c r="J159" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K159" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L159" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M159" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N159" s="5" t="s">
         <v>386</v>
       </c>
@@ -9603,10 +10475,18 @@
       <c r="I160" s="7">
         <v>50</v>
       </c>
-      <c r="J160" s="8"/>
-      <c r="K160" s="8"/>
-      <c r="L160" s="8"/>
-      <c r="M160" s="8"/>
+      <c r="J160" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K160" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L160" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M160" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N160" s="5" t="s">
         <v>388</v>
       </c>
@@ -9683,10 +10563,18 @@
       <c r="I162" s="7">
         <v>31</v>
       </c>
-      <c r="J162" s="8"/>
-      <c r="K162" s="8"/>
-      <c r="L162" s="8"/>
-      <c r="M162" s="8"/>
+      <c r="J162" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K162" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L162" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M162" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N162" s="5" t="s">
         <v>393</v>
       </c>
@@ -9719,10 +10607,18 @@
       <c r="I163" s="7">
         <v>20</v>
       </c>
-      <c r="J163" s="8"/>
-      <c r="K163" s="8"/>
-      <c r="L163" s="8"/>
-      <c r="M163" s="8"/>
+      <c r="J163" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K163" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L163" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M163" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N163" s="5" t="s">
         <v>395</v>
       </c>
@@ -9755,10 +10651,18 @@
       <c r="I164" s="17">
         <v>861</v>
       </c>
-      <c r="J164" s="19"/>
-      <c r="K164" s="19"/>
-      <c r="L164" s="19"/>
-      <c r="M164" s="19"/>
+      <c r="J164" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="K164" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="L164" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="M164" s="19" t="s">
+        <v>13</v>
+      </c>
       <c r="N164" s="13" t="s">
         <v>397</v>
       </c>
@@ -9807,10 +10711,18 @@
       <c r="I166" s="17">
         <v>477</v>
       </c>
-      <c r="J166" s="19"/>
-      <c r="K166" s="19"/>
-      <c r="L166" s="19"/>
-      <c r="M166" s="19"/>
+      <c r="J166" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="K166" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="L166" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="M166" s="19" t="s">
+        <v>13</v>
+      </c>
       <c r="N166" s="13" t="s">
         <v>400</v>
       </c>
@@ -9859,10 +10771,18 @@
       <c r="I168" s="7">
         <v>115</v>
       </c>
-      <c r="J168" s="8"/>
-      <c r="K168" s="8"/>
-      <c r="L168" s="8"/>
-      <c r="M168" s="8"/>
+      <c r="J168" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K168" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L168" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M168" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N168" s="5" t="s">
         <v>403</v>
       </c>
@@ -9895,10 +10815,18 @@
       <c r="I169" s="7">
         <v>24</v>
       </c>
-      <c r="J169" s="8"/>
-      <c r="K169" s="8"/>
-      <c r="L169" s="8"/>
-      <c r="M169" s="8"/>
+      <c r="J169" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K169" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L169" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M169" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N169" s="5" t="s">
         <v>406</v>
       </c>
@@ -9931,10 +10859,18 @@
       <c r="I170" s="7">
         <v>40</v>
       </c>
-      <c r="J170" s="8"/>
-      <c r="K170" s="8"/>
-      <c r="L170" s="8"/>
-      <c r="M170" s="8"/>
+      <c r="J170" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K170" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L170" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M170" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N170" s="5" t="s">
         <v>409</v>
       </c>
@@ -10055,10 +10991,18 @@
       <c r="I173" s="7">
         <v>33</v>
       </c>
-      <c r="J173" s="8"/>
-      <c r="K173" s="8"/>
-      <c r="L173" s="8"/>
-      <c r="M173" s="8"/>
+      <c r="J173" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K173" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L173" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M173" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N173" s="5" t="s">
         <v>419</v>
       </c>
@@ -10091,10 +11035,18 @@
       <c r="I174" s="7">
         <v>199</v>
       </c>
-      <c r="J174" s="8"/>
-      <c r="K174" s="8"/>
-      <c r="L174" s="8"/>
-      <c r="M174" s="8"/>
+      <c r="J174" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K174" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L174" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M174" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N174" s="5" t="s">
         <v>422</v>
       </c>
@@ -10127,10 +11079,18 @@
       <c r="I175" s="7">
         <v>120</v>
       </c>
-      <c r="J175" s="8"/>
-      <c r="K175" s="8"/>
-      <c r="L175" s="8"/>
-      <c r="M175" s="8"/>
+      <c r="J175" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K175" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L175" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M175" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N175" s="5" t="s">
         <v>425</v>
       </c>
@@ -10163,10 +11123,18 @@
       <c r="I176" s="7">
         <v>132</v>
       </c>
-      <c r="J176" s="8"/>
-      <c r="K176" s="8"/>
-      <c r="L176" s="8"/>
-      <c r="M176" s="8"/>
+      <c r="J176" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K176" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L176" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M176" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N176" s="5" t="s">
         <v>428</v>
       </c>
@@ -10199,10 +11167,18 @@
       <c r="I177" s="7">
         <v>160</v>
       </c>
-      <c r="J177" s="8"/>
-      <c r="K177" s="8"/>
-      <c r="L177" s="8"/>
-      <c r="M177" s="8"/>
+      <c r="J177" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K177" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L177" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M177" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N177" s="5" t="s">
         <v>431</v>
       </c>
@@ -10235,10 +11211,18 @@
       <c r="I178" s="7">
         <v>511</v>
       </c>
-      <c r="J178" s="8"/>
-      <c r="K178" s="8"/>
-      <c r="L178" s="8"/>
-      <c r="M178" s="8"/>
+      <c r="J178" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K178" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L178" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M178" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N178" s="5" t="s">
         <v>435</v>
       </c>
@@ -10271,10 +11255,18 @@
       <c r="I179" s="7">
         <v>75</v>
       </c>
-      <c r="J179" s="8"/>
-      <c r="K179" s="8"/>
-      <c r="L179" s="8"/>
-      <c r="M179" s="8"/>
+      <c r="J179" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K179" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L179" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M179" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N179" s="5" t="s">
         <v>438</v>
       </c>
@@ -10351,10 +11343,18 @@
       <c r="I181" s="7">
         <v>91</v>
       </c>
-      <c r="J181" s="8"/>
-      <c r="K181" s="8"/>
-      <c r="L181" s="8"/>
-      <c r="M181" s="8"/>
+      <c r="J181" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K181" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L181" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M181" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N181" s="5" t="s">
         <v>445</v>
       </c>
@@ -10387,10 +11387,18 @@
       <c r="I182" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J182" s="8"/>
-      <c r="K182" s="8"/>
-      <c r="L182" s="8"/>
-      <c r="M182" s="8"/>
+      <c r="J182" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K182" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L182" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M182" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N182" s="5" t="s">
         <v>448</v>
       </c>
@@ -10555,10 +11563,18 @@
       <c r="I186" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J186" s="8"/>
-      <c r="K186" s="8"/>
-      <c r="L186" s="8"/>
-      <c r="M186" s="8"/>
+      <c r="J186" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K186" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L186" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M186" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N186" s="5" t="s">
         <v>462</v>
       </c>
@@ -10723,10 +11739,18 @@
       <c r="I190" s="7">
         <v>25</v>
       </c>
-      <c r="J190" s="8"/>
-      <c r="K190" s="8"/>
-      <c r="L190" s="8"/>
-      <c r="M190" s="8"/>
+      <c r="J190" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K190" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L190" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M190" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N190" s="5" t="s">
         <v>479</v>
       </c>
@@ -10803,10 +11827,18 @@
       <c r="I192" s="7">
         <v>25</v>
       </c>
-      <c r="J192" s="8"/>
-      <c r="K192" s="8"/>
-      <c r="L192" s="8"/>
-      <c r="M192" s="8"/>
+      <c r="J192" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K192" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L192" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M192" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N192" s="5" t="s">
         <v>487</v>
       </c>
@@ -10927,10 +11959,18 @@
       <c r="I195" s="7">
         <v>149</v>
       </c>
-      <c r="J195" s="8"/>
-      <c r="K195" s="8"/>
-      <c r="L195" s="8"/>
-      <c r="M195" s="8"/>
+      <c r="J195" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K195" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L195" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M195" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N195" s="5" t="s">
         <v>498</v>
       </c>
@@ -11095,10 +12135,18 @@
       <c r="I199" s="7">
         <v>18</v>
       </c>
-      <c r="J199" s="8"/>
-      <c r="K199" s="8"/>
-      <c r="L199" s="8"/>
-      <c r="M199" s="8"/>
+      <c r="J199" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K199" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L199" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M199" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N199" s="5" t="s">
         <v>511</v>
       </c>
@@ -11131,10 +12179,18 @@
       <c r="I200" s="7">
         <v>93</v>
       </c>
-      <c r="J200" s="8"/>
-      <c r="K200" s="8"/>
-      <c r="L200" s="8"/>
-      <c r="M200" s="8"/>
+      <c r="J200" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K200" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L200" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M200" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N200" s="5" t="s">
         <v>514</v>
       </c>
@@ -11387,10 +12443,18 @@
       <c r="I206" s="7">
         <v>102</v>
       </c>
-      <c r="J206" s="8"/>
-      <c r="K206" s="8"/>
-      <c r="L206" s="8"/>
-      <c r="M206" s="8"/>
+      <c r="J206" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K206" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L206" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M206" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N206" s="5" t="s">
         <v>532</v>
       </c>
@@ -11555,10 +12619,18 @@
       <c r="I210" s="7">
         <v>9</v>
       </c>
-      <c r="J210" s="8"/>
-      <c r="K210" s="8"/>
-      <c r="L210" s="8"/>
-      <c r="M210" s="8"/>
+      <c r="J210" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K210" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L210" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M210" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N210" s="5" t="s">
         <v>545</v>
       </c>
@@ -11591,10 +12663,18 @@
       <c r="I211" s="7">
         <v>50</v>
       </c>
-      <c r="J211" s="8"/>
-      <c r="K211" s="8"/>
-      <c r="L211" s="8"/>
-      <c r="M211" s="8"/>
+      <c r="J211" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K211" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L211" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M211" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N211" s="5" t="s">
         <v>548</v>
       </c>
@@ -11627,10 +12707,18 @@
       <c r="I212" s="7">
         <v>19</v>
       </c>
-      <c r="J212" s="8"/>
-      <c r="K212" s="8"/>
-      <c r="L212" s="8"/>
-      <c r="M212" s="8"/>
+      <c r="J212" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K212" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L212" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M212" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N212" s="5" t="s">
         <v>552</v>
       </c>
@@ -11663,10 +12751,18 @@
       <c r="I213" s="7">
         <v>17</v>
       </c>
-      <c r="J213" s="8"/>
-      <c r="K213" s="8"/>
-      <c r="L213" s="8"/>
-      <c r="M213" s="8"/>
+      <c r="J213" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K213" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L213" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M213" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N213" s="5" t="s">
         <v>555</v>
       </c>
@@ -11699,10 +12795,18 @@
       <c r="I214" s="7">
         <v>31</v>
       </c>
-      <c r="J214" s="8"/>
-      <c r="K214" s="8"/>
-      <c r="L214" s="8"/>
-      <c r="M214" s="8"/>
+      <c r="J214" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K214" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L214" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M214" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N214" s="5" t="s">
         <v>558</v>
       </c>
@@ -11911,10 +13015,18 @@
       <c r="I219" s="7">
         <v>31</v>
       </c>
-      <c r="J219" s="8"/>
-      <c r="K219" s="8"/>
-      <c r="L219" s="8"/>
-      <c r="M219" s="8"/>
+      <c r="J219" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K219" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L219" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M219" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N219" s="5" t="s">
         <v>575</v>
       </c>
@@ -11947,10 +13059,18 @@
       <c r="I220" s="7">
         <v>23</v>
       </c>
-      <c r="J220" s="8"/>
-      <c r="K220" s="8"/>
-      <c r="L220" s="8"/>
-      <c r="M220" s="8"/>
+      <c r="J220" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K220" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L220" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M220" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N220" s="5" t="s">
         <v>578</v>
       </c>
@@ -11983,10 +13103,18 @@
       <c r="I221" s="7">
         <v>50</v>
       </c>
-      <c r="J221" s="8"/>
-      <c r="K221" s="8"/>
-      <c r="L221" s="8"/>
-      <c r="M221" s="8"/>
+      <c r="J221" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K221" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L221" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M221" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N221" s="5" t="s">
         <v>581</v>
       </c>
@@ -12019,10 +13147,18 @@
       <c r="I222" s="7">
         <v>51</v>
       </c>
-      <c r="J222" s="8"/>
-      <c r="K222" s="8"/>
-      <c r="L222" s="8"/>
-      <c r="M222" s="8"/>
+      <c r="J222" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K222" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L222" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M222" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N222" s="5" t="s">
         <v>584</v>
       </c>
@@ -12055,10 +13191,18 @@
       <c r="I223" s="7">
         <v>973</v>
       </c>
-      <c r="J223" s="8"/>
-      <c r="K223" s="8"/>
-      <c r="L223" s="8"/>
-      <c r="M223" s="8"/>
+      <c r="J223" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K223" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L223" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M223" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N223" s="5" t="s">
         <v>587</v>
       </c>
@@ -12135,10 +13279,18 @@
       <c r="I225" s="7">
         <v>51</v>
       </c>
-      <c r="J225" s="8"/>
-      <c r="K225" s="8"/>
-      <c r="L225" s="8"/>
-      <c r="M225" s="8"/>
+      <c r="J225" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K225" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L225" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M225" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N225" s="5" t="s">
         <v>594</v>
       </c>
@@ -12171,11 +13323,21 @@
       <c r="I226" s="17">
         <v>472</v>
       </c>
-      <c r="J226" s="19"/>
-      <c r="K226" s="19"/>
-      <c r="L226" s="19"/>
-      <c r="M226" s="19"/>
-      <c r="N226" s="10"/>
+      <c r="J226" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="K226" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="L226" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="M226" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="N226" s="10" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="227" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A227" s="16"/>
@@ -12223,10 +13385,18 @@
       <c r="I228" s="7">
         <v>55</v>
       </c>
-      <c r="J228" s="8"/>
-      <c r="K228" s="8"/>
-      <c r="L228" s="8"/>
-      <c r="M228" s="8"/>
+      <c r="J228" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K228" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L228" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M228" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N228" s="5" t="s">
         <v>600</v>
       </c>
@@ -12259,10 +13429,18 @@
       <c r="I229" s="7">
         <v>53</v>
       </c>
-      <c r="J229" s="8"/>
-      <c r="K229" s="8"/>
-      <c r="L229" s="8"/>
-      <c r="M229" s="8"/>
+      <c r="J229" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K229" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L229" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M229" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N229" s="5" t="s">
         <v>603</v>
       </c>
@@ -12295,10 +13473,18 @@
       <c r="I230" s="7">
         <v>38</v>
       </c>
-      <c r="J230" s="8"/>
-      <c r="K230" s="8"/>
-      <c r="L230" s="8"/>
-      <c r="M230" s="8"/>
+      <c r="J230" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K230" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L230" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M230" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N230" s="5" t="s">
         <v>606</v>
       </c>
@@ -12331,10 +13517,18 @@
       <c r="I231" s="7">
         <v>329</v>
       </c>
-      <c r="J231" s="8"/>
-      <c r="K231" s="8"/>
-      <c r="L231" s="8"/>
-      <c r="M231" s="8"/>
+      <c r="J231" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K231" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L231" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M231" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N231" s="5" t="s">
         <v>609</v>
       </c>
@@ -12411,10 +13605,18 @@
       <c r="I233" s="7">
         <v>21</v>
       </c>
-      <c r="J233" s="8"/>
-      <c r="K233" s="8"/>
-      <c r="L233" s="8"/>
-      <c r="M233" s="8"/>
+      <c r="J233" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K233" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L233" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M233" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N233" s="5" t="s">
         <v>615</v>
       </c>
@@ -12447,10 +13649,18 @@
       <c r="I234" s="7">
         <v>11</v>
       </c>
-      <c r="J234" s="8"/>
-      <c r="K234" s="8"/>
-      <c r="L234" s="8"/>
-      <c r="M234" s="8"/>
+      <c r="J234" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K234" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L234" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M234" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N234" s="5" t="s">
         <v>618</v>
       </c>
@@ -12483,10 +13693,18 @@
       <c r="I235" s="7">
         <v>19</v>
       </c>
-      <c r="J235" s="8"/>
-      <c r="K235" s="8"/>
-      <c r="L235" s="8"/>
-      <c r="M235" s="8"/>
+      <c r="J235" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K235" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L235" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M235" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N235" s="5" t="s">
         <v>621</v>
       </c>
@@ -12519,10 +13737,18 @@
       <c r="I236" s="7">
         <v>74</v>
       </c>
-      <c r="J236" s="8"/>
-      <c r="K236" s="8"/>
-      <c r="L236" s="8"/>
-      <c r="M236" s="8"/>
+      <c r="J236" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K236" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L236" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M236" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N236" s="5" t="s">
         <v>624</v>
       </c>
@@ -12555,10 +13781,18 @@
       <c r="I237" s="7">
         <v>15</v>
       </c>
-      <c r="J237" s="8"/>
-      <c r="K237" s="8"/>
-      <c r="L237" s="8"/>
-      <c r="M237" s="8"/>
+      <c r="J237" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K237" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L237" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M237" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N237" s="5" t="s">
         <v>628</v>
       </c>
@@ -12591,10 +13825,18 @@
       <c r="I238" s="7">
         <v>13</v>
       </c>
-      <c r="J238" s="8"/>
-      <c r="K238" s="8"/>
-      <c r="L238" s="8"/>
-      <c r="M238" s="8"/>
+      <c r="J238" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K238" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L238" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M238" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N238" s="5" t="s">
         <v>628</v>
       </c>
@@ -12627,10 +13869,18 @@
       <c r="I239" s="7">
         <v>39</v>
       </c>
-      <c r="J239" s="8"/>
-      <c r="K239" s="8"/>
-      <c r="L239" s="8"/>
-      <c r="M239" s="8"/>
+      <c r="J239" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K239" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L239" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M239" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N239" s="5" t="s">
         <v>633</v>
       </c>
@@ -12707,10 +13957,18 @@
       <c r="I241" s="7">
         <v>67</v>
       </c>
-      <c r="J241" s="8"/>
-      <c r="K241" s="8"/>
-      <c r="L241" s="8"/>
-      <c r="M241" s="8"/>
+      <c r="J241" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K241" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L241" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M241" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N241" s="5" t="s">
         <v>639</v>
       </c>
@@ -12743,10 +14001,18 @@
       <c r="I242" s="7">
         <v>16</v>
       </c>
-      <c r="J242" s="8"/>
-      <c r="K242" s="8"/>
-      <c r="L242" s="8"/>
-      <c r="M242" s="8"/>
+      <c r="J242" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K242" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L242" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M242" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N242" s="5" t="s">
         <v>642</v>
       </c>
@@ -12779,10 +14045,18 @@
       <c r="I243" s="7">
         <v>20</v>
       </c>
-      <c r="J243" s="8"/>
-      <c r="K243" s="8"/>
-      <c r="L243" s="8"/>
-      <c r="M243" s="8"/>
+      <c r="J243" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K243" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L243" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M243" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N243" s="5" t="s">
         <v>645</v>
       </c>
@@ -12815,10 +14089,18 @@
       <c r="I244" s="7">
         <v>42</v>
       </c>
-      <c r="J244" s="8"/>
-      <c r="K244" s="8"/>
-      <c r="L244" s="8"/>
-      <c r="M244" s="8"/>
+      <c r="J244" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K244" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L244" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M244" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N244" s="5" t="s">
         <v>648</v>
       </c>
@@ -12851,10 +14133,18 @@
       <c r="I245" s="7">
         <v>109</v>
       </c>
-      <c r="J245" s="8"/>
-      <c r="K245" s="8"/>
-      <c r="L245" s="8"/>
-      <c r="M245" s="8"/>
+      <c r="J245" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K245" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L245" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M245" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N245" s="5" t="s">
         <v>651</v>
       </c>
@@ -12887,10 +14177,18 @@
       <c r="I246" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J246" s="8"/>
-      <c r="K246" s="8"/>
-      <c r="L246" s="8"/>
-      <c r="M246" s="8"/>
+      <c r="J246" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K246" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L246" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M246" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N246" s="5" t="s">
         <v>655</v>
       </c>
@@ -12923,10 +14221,18 @@
       <c r="I247" s="7">
         <v>7</v>
       </c>
-      <c r="J247" s="8"/>
-      <c r="K247" s="8"/>
-      <c r="L247" s="8"/>
-      <c r="M247" s="8"/>
+      <c r="J247" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K247" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L247" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M247" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N247" s="5" t="s">
         <v>658</v>
       </c>
@@ -12959,10 +14265,18 @@
       <c r="I248" s="7">
         <v>16</v>
       </c>
-      <c r="J248" s="8"/>
-      <c r="K248" s="8"/>
-      <c r="L248" s="8"/>
-      <c r="M248" s="8"/>
+      <c r="J248" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K248" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L248" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M248" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N248" s="5" t="s">
         <v>658</v>
       </c>
@@ -12995,10 +14309,18 @@
       <c r="I249" s="7">
         <v>53</v>
       </c>
-      <c r="J249" s="8"/>
-      <c r="K249" s="8"/>
-      <c r="L249" s="8"/>
-      <c r="M249" s="8"/>
+      <c r="J249" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K249" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L249" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M249" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N249" s="5" t="s">
         <v>664</v>
       </c>
@@ -13119,10 +14441,18 @@
       <c r="I252" s="7">
         <v>50</v>
       </c>
-      <c r="J252" s="8"/>
-      <c r="K252" s="8"/>
-      <c r="L252" s="8"/>
-      <c r="M252" s="8"/>
+      <c r="J252" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K252" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L252" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M252" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N252" s="5" t="s">
         <v>675</v>
       </c>
@@ -13287,10 +14617,18 @@
       <c r="I256" s="7">
         <v>407</v>
       </c>
-      <c r="J256" s="8"/>
-      <c r="K256" s="8"/>
-      <c r="L256" s="8"/>
-      <c r="M256" s="8"/>
+      <c r="J256" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K256" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L256" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M256" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N256" s="5" t="s">
         <v>688</v>
       </c>
@@ -13323,10 +14661,18 @@
       <c r="I257" s="7">
         <v>170</v>
       </c>
-      <c r="J257" s="8"/>
-      <c r="K257" s="8"/>
-      <c r="L257" s="8"/>
-      <c r="M257" s="8"/>
+      <c r="J257" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K257" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L257" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M257" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N257" s="5" t="s">
         <v>691</v>
       </c>
@@ -13359,10 +14705,18 @@
       <c r="I258" s="7">
         <v>29</v>
       </c>
-      <c r="J258" s="8"/>
-      <c r="K258" s="8"/>
-      <c r="L258" s="8"/>
-      <c r="M258" s="8"/>
+      <c r="J258" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K258" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L258" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M258" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N258" s="5" t="s">
         <v>694</v>
       </c>
@@ -13395,10 +14749,18 @@
       <c r="I259" s="7">
         <v>83</v>
       </c>
-      <c r="J259" s="8"/>
-      <c r="K259" s="8"/>
-      <c r="L259" s="8"/>
-      <c r="M259" s="8"/>
+      <c r="J259" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K259" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L259" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M259" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N259" s="5" t="s">
         <v>697</v>
       </c>
@@ -13431,10 +14793,18 @@
       <c r="I260" s="7">
         <v>87</v>
       </c>
-      <c r="J260" s="8"/>
-      <c r="K260" s="8"/>
-      <c r="L260" s="8"/>
-      <c r="M260" s="8"/>
+      <c r="J260" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K260" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L260" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M260" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N260" s="5" t="s">
         <v>697</v>
       </c>
@@ -13467,10 +14837,18 @@
       <c r="I261" s="7">
         <v>42</v>
       </c>
-      <c r="J261" s="8"/>
-      <c r="K261" s="8"/>
-      <c r="L261" s="8"/>
-      <c r="M261" s="8"/>
+      <c r="J261" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K261" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L261" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M261" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N261" s="5" t="s">
         <v>703</v>
       </c>
@@ -13503,10 +14881,18 @@
       <c r="I262" s="7">
         <v>63</v>
       </c>
-      <c r="J262" s="8"/>
-      <c r="K262" s="8"/>
-      <c r="L262" s="8"/>
-      <c r="M262" s="8"/>
+      <c r="J262" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K262" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L262" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M262" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N262" s="5" t="s">
         <v>707</v>
       </c>
@@ -13539,10 +14925,18 @@
       <c r="I263" s="7">
         <v>83</v>
       </c>
-      <c r="J263" s="8"/>
-      <c r="K263" s="8"/>
-      <c r="L263" s="8"/>
-      <c r="M263" s="8"/>
+      <c r="J263" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K263" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L263" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M263" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N263" s="5" t="s">
         <v>711</v>
       </c>
@@ -13575,10 +14969,18 @@
       <c r="I264" s="7">
         <v>98</v>
       </c>
-      <c r="J264" s="8"/>
-      <c r="K264" s="8"/>
-      <c r="L264" s="8"/>
-      <c r="M264" s="8"/>
+      <c r="J264" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K264" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L264" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M264" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N264" s="5" t="s">
         <v>714</v>
       </c>
@@ -13611,10 +15013,18 @@
       <c r="I265" s="7">
         <v>28</v>
       </c>
-      <c r="J265" s="8"/>
-      <c r="K265" s="8"/>
-      <c r="L265" s="8"/>
-      <c r="M265" s="8"/>
+      <c r="J265" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K265" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L265" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M265" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N265" s="5" t="s">
         <v>717</v>
       </c>
@@ -13647,10 +15057,18 @@
       <c r="I266" s="7">
         <v>34</v>
       </c>
-      <c r="J266" s="8"/>
-      <c r="K266" s="8"/>
-      <c r="L266" s="8"/>
-      <c r="M266" s="8"/>
+      <c r="J266" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K266" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L266" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M266" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N266" s="5" t="s">
         <v>720</v>
       </c>
@@ -13683,10 +15101,18 @@
       <c r="I267" s="7">
         <v>41</v>
       </c>
-      <c r="J267" s="8"/>
-      <c r="K267" s="8"/>
-      <c r="L267" s="8"/>
-      <c r="M267" s="8"/>
+      <c r="J267" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K267" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L267" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M267" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N267" s="5" t="s">
         <v>723</v>
       </c>
@@ -13719,10 +15145,18 @@
       <c r="I268" s="7">
         <v>49</v>
       </c>
-      <c r="J268" s="8"/>
-      <c r="K268" s="8"/>
-      <c r="L268" s="8"/>
-      <c r="M268" s="8"/>
+      <c r="J268" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K268" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L268" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M268" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N268" s="5" t="s">
         <v>727</v>
       </c>
@@ -13755,10 +15189,18 @@
       <c r="I269" s="7">
         <v>13</v>
       </c>
-      <c r="J269" s="8"/>
-      <c r="K269" s="8"/>
-      <c r="L269" s="8"/>
-      <c r="M269" s="8"/>
+      <c r="J269" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K269" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L269" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M269" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N269" s="5" t="s">
         <v>731</v>
       </c>
@@ -13791,10 +15233,18 @@
       <c r="I270" s="7">
         <v>18</v>
       </c>
-      <c r="J270" s="8"/>
-      <c r="K270" s="8"/>
-      <c r="L270" s="8"/>
-      <c r="M270" s="8"/>
+      <c r="J270" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K270" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L270" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M270" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N270" s="5" t="s">
         <v>734</v>
       </c>
@@ -13827,10 +15277,18 @@
       <c r="I271" s="7">
         <v>38</v>
       </c>
-      <c r="J271" s="8"/>
-      <c r="K271" s="8"/>
-      <c r="L271" s="8"/>
-      <c r="M271" s="8"/>
+      <c r="J271" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K271" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L271" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M271" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N271" s="5" t="s">
         <v>737</v>
       </c>
@@ -13863,10 +15321,18 @@
       <c r="I272" s="7">
         <v>21</v>
       </c>
-      <c r="J272" s="8"/>
-      <c r="K272" s="8"/>
-      <c r="L272" s="8"/>
-      <c r="M272" s="8"/>
+      <c r="J272" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K272" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L272" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M272" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N272" s="5" t="s">
         <v>740</v>
       </c>
@@ -13899,10 +15365,18 @@
       <c r="I273" s="7">
         <v>32</v>
       </c>
-      <c r="J273" s="8"/>
-      <c r="K273" s="8"/>
-      <c r="L273" s="8"/>
-      <c r="M273" s="8"/>
+      <c r="J273" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K273" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L273" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M273" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N273" s="5" t="s">
         <v>744</v>
       </c>
@@ -13935,10 +15409,18 @@
       <c r="I274" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J274" s="8"/>
-      <c r="K274" s="8"/>
-      <c r="L274" s="8"/>
-      <c r="M274" s="8"/>
+      <c r="J274" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K274" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L274" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M274" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N274" s="5" t="s">
         <v>747</v>
       </c>
@@ -13971,10 +15453,18 @@
       <c r="I275" s="7">
         <v>16</v>
       </c>
-      <c r="J275" s="8"/>
-      <c r="K275" s="8"/>
-      <c r="L275" s="8"/>
-      <c r="M275" s="8"/>
+      <c r="J275" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K275" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L275" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M275" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N275" s="5" t="s">
         <v>750</v>
       </c>
@@ -14007,10 +15497,18 @@
       <c r="I276" s="7">
         <v>23</v>
       </c>
-      <c r="J276" s="8"/>
-      <c r="K276" s="8"/>
-      <c r="L276" s="8"/>
-      <c r="M276" s="8"/>
+      <c r="J276" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K276" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L276" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M276" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N276" s="5" t="s">
         <v>753</v>
       </c>
@@ -14043,10 +15541,18 @@
       <c r="I277" s="7">
         <v>52</v>
       </c>
-      <c r="J277" s="8"/>
-      <c r="K277" s="8"/>
-      <c r="L277" s="8"/>
-      <c r="M277" s="8"/>
+      <c r="J277" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K277" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L277" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M277" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N277" s="5" t="s">
         <v>756</v>
       </c>
@@ -14079,10 +15585,18 @@
       <c r="I278" s="7">
         <v>17</v>
       </c>
-      <c r="J278" s="8"/>
-      <c r="K278" s="8"/>
-      <c r="L278" s="8"/>
-      <c r="M278" s="8"/>
+      <c r="J278" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K278" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L278" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M278" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N278" s="5" t="s">
         <v>759</v>
       </c>
@@ -14115,10 +15629,18 @@
       <c r="I279" s="7">
         <v>37</v>
       </c>
-      <c r="J279" s="8"/>
-      <c r="K279" s="8"/>
-      <c r="L279" s="8"/>
-      <c r="M279" s="8"/>
+      <c r="J279" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K279" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L279" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M279" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N279" s="5" t="s">
         <v>762</v>
       </c>
@@ -14151,10 +15673,18 @@
       <c r="I280" s="7">
         <v>95</v>
       </c>
-      <c r="J280" s="8"/>
-      <c r="K280" s="8"/>
-      <c r="L280" s="8"/>
-      <c r="M280" s="8"/>
+      <c r="J280" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K280" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L280" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M280" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N280" s="5" t="s">
         <v>766</v>
       </c>
@@ -14231,10 +15761,18 @@
       <c r="I282" s="7">
         <v>92</v>
       </c>
-      <c r="J282" s="8"/>
-      <c r="K282" s="8"/>
-      <c r="L282" s="8"/>
-      <c r="M282" s="8"/>
+      <c r="J282" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K282" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L282" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M282" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N282" s="5" t="s">
         <v>774</v>
       </c>
@@ -14267,10 +15805,18 @@
       <c r="I283" s="7">
         <v>124</v>
       </c>
-      <c r="J283" s="8"/>
-      <c r="K283" s="8"/>
-      <c r="L283" s="8"/>
-      <c r="M283" s="8"/>
+      <c r="J283" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K283" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L283" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M283" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N283" s="5" t="s">
         <v>778</v>
       </c>
@@ -14303,10 +15849,18 @@
       <c r="I284" s="7">
         <v>30</v>
       </c>
-      <c r="J284" s="8"/>
-      <c r="K284" s="8"/>
-      <c r="L284" s="8"/>
-      <c r="M284" s="8"/>
+      <c r="J284" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K284" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L284" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M284" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N284" s="5" t="s">
         <v>781</v>
       </c>
@@ -14339,10 +15893,18 @@
       <c r="I285" s="7">
         <v>21</v>
       </c>
-      <c r="J285" s="8"/>
-      <c r="K285" s="8"/>
-      <c r="L285" s="8"/>
-      <c r="M285" s="8"/>
+      <c r="J285" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K285" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L285" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M285" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N285" s="5" t="s">
         <v>785</v>
       </c>
@@ -14375,10 +15937,18 @@
       <c r="I286" s="7">
         <v>398</v>
       </c>
-      <c r="J286" s="8"/>
-      <c r="K286" s="8"/>
-      <c r="L286" s="8"/>
-      <c r="M286" s="8"/>
+      <c r="J286" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K286" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L286" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M286" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N286" s="5" t="s">
         <v>788</v>
       </c>
@@ -14411,10 +15981,18 @@
       <c r="I287" s="7">
         <v>14</v>
       </c>
-      <c r="J287" s="8"/>
-      <c r="K287" s="8"/>
-      <c r="L287" s="8"/>
-      <c r="M287" s="8"/>
+      <c r="J287" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K287" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L287" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M287" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N287" s="5" t="s">
         <v>791</v>
       </c>

--- a/Source Data Process_CB/Biagolini_SuppTable1.xlsx
+++ b/Source Data Process_CB/Biagolini_SuppTable1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10509"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10711"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kate/Desktop/CooperativeBreedingEvolution/Source Data Process_CB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DBF515-2F65-3A48-8F3D-A0DEFB313D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CF63F8-97DD-B640-A11F-83C370228D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1160" yWindow="660" windowWidth="28040" windowHeight="17280" xr2:uid="{10AD7567-51C1-244C-9C49-3C4EE696AFD4}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2530" uniqueCount="959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2529" uniqueCount="958">
   <si>
     <t>OR</t>
   </si>
@@ -1230,45 +1230,30 @@
     <t>[268; 270; 273; 290-298]</t>
   </si>
   <si>
-    <t>Periparus ater</t>
-  </si>
-  <si>
     <t>coal tit</t>
   </si>
   <si>
     <t>[293; 299-308]</t>
   </si>
   <si>
-    <t>Poecile atricapillus</t>
-  </si>
-  <si>
     <t>black-capped chickadees</t>
   </si>
   <si>
     <t>[309; 310]</t>
   </si>
   <si>
-    <t>Poecile montanus</t>
-  </si>
-  <si>
     <t>willow tit</t>
   </si>
   <si>
     <t>[311]</t>
   </si>
   <si>
-    <t>Poecile varius</t>
-  </si>
-  <si>
     <t>varied tits</t>
   </si>
   <si>
     <t>[312]</t>
   </si>
   <si>
-    <t>Pseudopodoces humilis</t>
-  </si>
-  <si>
     <t>ground-tit</t>
   </si>
   <si>
@@ -1278,54 +1263,36 @@
     <t>Parulidae</t>
   </si>
   <si>
-    <t>Dendroica caerulescens</t>
-  </si>
-  <si>
     <t>black-throated blue warbler</t>
   </si>
   <si>
     <t>[317-320]</t>
   </si>
   <si>
-    <t>Dendroica pensylvanica</t>
-  </si>
-  <si>
     <t>chestnut-sided warblers</t>
   </si>
   <si>
     <t>[321; 322]</t>
   </si>
   <si>
-    <t>Dendroica petechia</t>
-  </si>
-  <si>
     <t>yellow warbler</t>
   </si>
   <si>
     <t>[323-325]</t>
   </si>
   <si>
-    <t>Geothlypis trichas</t>
-  </si>
-  <si>
     <t>yellowthroat</t>
   </si>
   <si>
     <t>[326-330]</t>
   </si>
   <si>
-    <t>Setophaga ruticilla</t>
-  </si>
-  <si>
     <t>american redstart</t>
   </si>
   <si>
     <t>[331-334]</t>
   </si>
   <si>
-    <t>Wilsonia citrina</t>
-  </si>
-  <si>
     <t>hooded warbler</t>
   </si>
   <si>
@@ -1335,27 +1302,18 @@
     <t>Passeridae</t>
   </si>
   <si>
-    <t>Passer domesticus</t>
-  </si>
-  <si>
     <t>house sparrow</t>
   </si>
   <si>
     <t>[338-345]</t>
   </si>
   <si>
-    <t>Passer montanus</t>
-  </si>
-  <si>
     <t>tree sparrows</t>
   </si>
   <si>
     <t>[346]</t>
   </si>
   <si>
-    <t>Petronia petronia</t>
-  </si>
-  <si>
     <t>rock sparrow</t>
   </si>
   <si>
@@ -1365,18 +1323,12 @@
     <t>Petroicidae</t>
   </si>
   <si>
-    <t>Petroica australis</t>
-  </si>
-  <si>
     <t>new zealand robin</t>
   </si>
   <si>
     <t>[84; 348]</t>
   </si>
   <si>
-    <t>Petroica goodenovii</t>
-  </si>
-  <si>
     <t>red-capped robin</t>
   </si>
   <si>
@@ -1386,9 +1338,6 @@
     <t>Pipridae</t>
   </si>
   <si>
-    <t>Chiroxiphia lanceolata</t>
-  </si>
-  <si>
     <t>lance-tailed manakin</t>
   </si>
   <si>
@@ -1398,27 +1347,18 @@
     <t>Ploceidae</t>
   </si>
   <si>
-    <t>Euplectes orix</t>
-  </si>
-  <si>
     <t>red bishops</t>
   </si>
   <si>
     <t>[351-353]</t>
   </si>
   <si>
-    <t>Plocepasser mahali</t>
-  </si>
-  <si>
     <t>white-browed sparrow-weaver</t>
   </si>
   <si>
     <t>[354]</t>
   </si>
   <si>
-    <t>Quelea quelea</t>
-  </si>
-  <si>
     <t>red-billed quelea</t>
   </si>
   <si>
@@ -1428,9 +1368,6 @@
     <t>Pomatostomidae</t>
   </si>
   <si>
-    <t>Pomatostomus temporalis</t>
-  </si>
-  <si>
     <t>grey-crowned babbler</t>
   </si>
   <si>
@@ -1440,9 +1377,6 @@
     <t>Prunellidae</t>
   </si>
   <si>
-    <t>Prunella collaris</t>
-  </si>
-  <si>
     <t>alpine accentor</t>
   </si>
   <si>
@@ -1452,9 +1386,6 @@
     <t>[357; 358]</t>
   </si>
   <si>
-    <t>Prunella modularis</t>
-  </si>
-  <si>
     <t>dunnock</t>
   </si>
   <si>
@@ -1467,9 +1398,6 @@
     <t>Ptilogonatidae</t>
   </si>
   <si>
-    <t>Phainopepla nitens</t>
-  </si>
-  <si>
     <t>phainopepla</t>
   </si>
   <si>
@@ -1479,9 +1407,6 @@
     <t>Remizidae</t>
   </si>
   <si>
-    <t>Remiz pendulinus</t>
-  </si>
-  <si>
     <t>penduline tit</t>
   </si>
   <si>
@@ -1491,9 +1416,6 @@
     <t>Rhipiduridae</t>
   </si>
   <si>
-    <t>Rhipidura albiscapa</t>
-  </si>
-  <si>
     <t>grey fantail</t>
   </si>
   <si>
@@ -1503,9 +1425,6 @@
     <t>Sittidae</t>
   </si>
   <si>
-    <t>Sitta pusilla</t>
-  </si>
-  <si>
     <t xml:space="preserve">brown-headed nuthatch </t>
   </si>
   <si>
@@ -1515,27 +1434,18 @@
     <t>Sturnidae</t>
   </si>
   <si>
-    <t>Lamprotornis superbus</t>
-  </si>
-  <si>
     <t>superb starling</t>
   </si>
   <si>
     <t>[366]</t>
   </si>
   <si>
-    <t>Sturnus unicolor</t>
-  </si>
-  <si>
     <t>spotless starling</t>
   </si>
   <si>
     <t>[367; 368]</t>
   </si>
   <si>
-    <t>Sturnus vulgaris</t>
-  </si>
-  <si>
     <t>starling</t>
   </si>
   <si>
@@ -1545,88 +1455,58 @@
     <t>Sylviidae</t>
   </si>
   <si>
-    <t>Acrocephalus arundinaceus</t>
-  </si>
-  <si>
     <t>great reed-warbler</t>
   </si>
   <si>
     <t>[371-377]</t>
   </si>
   <si>
-    <t>Acrocephalus bistrigiceps</t>
-  </si>
-  <si>
     <t>black-browed reed warblers</t>
   </si>
   <si>
     <t>[378]</t>
   </si>
   <si>
-    <t>Acrocephalus melanopogon</t>
-  </si>
-  <si>
     <t>moustached warbler</t>
   </si>
   <si>
     <t>[379]</t>
   </si>
   <si>
-    <t>Acrocephalus paludicola</t>
-  </si>
-  <si>
     <t>aquatic warbler</t>
   </si>
   <si>
     <t>[374; 380]</t>
   </si>
   <si>
-    <t>Acrocephalus palustris</t>
-  </si>
-  <si>
     <t>marsh warbler</t>
   </si>
   <si>
     <t>[374]</t>
   </si>
   <si>
-    <t>Acrocephalus schoenobaenus</t>
-  </si>
-  <si>
     <t>sedge warbler</t>
   </si>
   <si>
     <t>[381-383]</t>
   </si>
   <si>
-    <t>Acrocephalus scirpaceus</t>
-  </si>
-  <si>
     <t xml:space="preserve">reed-warbler </t>
   </si>
   <si>
     <t>[384]</t>
   </si>
   <si>
-    <t>Acrocephalus sechellensis</t>
-  </si>
-  <si>
     <t>seychelles brush-warbler</t>
   </si>
   <si>
     <t>[385-387]</t>
   </si>
   <si>
-    <t>Acrocephalus vaughani</t>
-  </si>
-  <si>
     <t>henderson reed warbler</t>
   </si>
   <si>
     <t>[388]</t>
-  </si>
-  <si>
-    <t>Locustella luscinioides</t>
   </si>
   <si>
     <r>
@@ -1655,27 +1535,18 @@
     <t>[389; 390]</t>
   </si>
   <si>
-    <t>Phylloscopus fuscatus</t>
-  </si>
-  <si>
     <t>dusky warbler</t>
   </si>
   <si>
     <t>[391-393]</t>
   </si>
   <si>
-    <t>Phylloscopus sibilatrix</t>
-  </si>
-  <si>
     <t>wood warbler</t>
   </si>
   <si>
     <t>[394]</t>
   </si>
   <si>
-    <t>Phylloscopus trochilus</t>
-  </si>
-  <si>
     <t>willow warbler</t>
   </si>
   <si>
@@ -1685,18 +1556,12 @@
     <t>Thamnophilidae</t>
   </si>
   <si>
-    <t>Cercomacra tyrannina</t>
-  </si>
-  <si>
     <t>dusky antbird</t>
   </si>
   <si>
     <t>[398]</t>
   </si>
   <si>
-    <t>Thamnophilus atrinucha</t>
-  </si>
-  <si>
     <t>black-crowned antshrike</t>
   </si>
   <si>
@@ -1706,27 +1571,18 @@
     <t>Thraupidae</t>
   </si>
   <si>
-    <t>Habia fuscicauda</t>
-  </si>
-  <si>
     <t>redthroated ant-tanagers</t>
   </si>
   <si>
     <t>[400]</t>
   </si>
   <si>
-    <t>Piranga olivacea</t>
-  </si>
-  <si>
     <t>scarlet tanager</t>
   </si>
   <si>
     <t>[401]</t>
   </si>
   <si>
-    <t>Ramphocelus costaricensis</t>
-  </si>
-  <si>
     <t>cherrie s tanager</t>
   </si>
   <si>
@@ -1736,18 +1592,12 @@
     <t>Timaliidae</t>
   </si>
   <si>
-    <t>Turdoides bicolor</t>
-  </si>
-  <si>
     <t>pied bablers</t>
   </si>
   <si>
     <t>[403]</t>
   </si>
   <si>
-    <t>Turdoides squamiceps</t>
-  </si>
-  <si>
     <t>arabian babbler</t>
   </si>
   <si>
@@ -1757,63 +1607,42 @@
     <t>Troglodytidae</t>
   </si>
   <si>
-    <t>Campylorhynchus griseus</t>
-  </si>
-  <si>
     <t>bicolored wren</t>
   </si>
   <si>
     <t>[405]</t>
   </si>
   <si>
-    <t>Campylorhynchus nuchalis</t>
-  </si>
-  <si>
     <t>stripe-backed wren</t>
   </si>
   <si>
     <t>[406]</t>
   </si>
   <si>
-    <t>Thryothorus leucotis</t>
-  </si>
-  <si>
     <t>buff-breasted wrens</t>
   </si>
   <si>
     <t>[407]</t>
   </si>
   <si>
-    <t>Thryothorus ludovicianus</t>
-  </si>
-  <si>
     <t>carolina wren</t>
   </si>
   <si>
     <t>[408]</t>
   </si>
   <si>
-    <t>Thryothorus pleurostictus</t>
-  </si>
-  <si>
     <t>banded wren</t>
   </si>
   <si>
     <t>[409]</t>
   </si>
   <si>
-    <t>Thryothorus rufalbus</t>
-  </si>
-  <si>
     <t>rufous-and-white wren</t>
   </si>
   <si>
     <t>[410]</t>
   </si>
   <si>
-    <t>Troglodytes aedon</t>
-  </si>
-  <si>
     <t>house wren</t>
   </si>
   <si>
@@ -1823,108 +1652,69 @@
     <t>Turdidae</t>
   </si>
   <si>
-    <t>Erythropygia coryphaeus</t>
-  </si>
-  <si>
     <t xml:space="preserve">karoo scrub-robin </t>
   </si>
   <si>
     <t>[421]</t>
   </si>
   <si>
-    <t>Hylocichla mustelina</t>
-  </si>
-  <si>
     <t>wood thrush</t>
   </si>
   <si>
     <t>[422; 423]</t>
   </si>
   <si>
-    <t>Luscinia svecica</t>
-  </si>
-  <si>
     <t>bluethroat</t>
   </si>
   <si>
-    <t>[271; 424-430]</t>
-  </si>
-  <si>
-    <t>Oenanthe oenanthe</t>
-  </si>
-  <si>
     <t>wheatear</t>
   </si>
   <si>
     <t>[431-433]</t>
   </si>
   <si>
-    <t>Phoenicurus ochruros</t>
-  </si>
-  <si>
     <t>black redstarts</t>
   </si>
   <si>
     <t>[434]</t>
   </si>
   <si>
-    <t>Phoenicurus phoenicurus</t>
-  </si>
-  <si>
     <t xml:space="preserve">common redstart </t>
   </si>
   <si>
     <t>[435]</t>
   </si>
   <si>
-    <t>Sialia currucoides</t>
-  </si>
-  <si>
     <t>mountain bluebird</t>
   </si>
   <si>
     <t>[436-438]</t>
   </si>
   <si>
-    <t>Sialia mexicana</t>
-  </si>
-  <si>
     <t>western bluebird</t>
   </si>
   <si>
     <t>[439-445]</t>
   </si>
   <si>
-    <t>Sialia sialis</t>
-  </si>
-  <si>
     <t>eastern bluebird</t>
   </si>
   <si>
     <t>[446]</t>
   </si>
   <si>
-    <t>Turdus albicollis</t>
-  </si>
-  <si>
     <t>white-necked thrush</t>
   </si>
   <si>
     <t>[447]</t>
   </si>
   <si>
-    <t>Turdus grayi</t>
-  </si>
-  <si>
     <t>clay-colored robin</t>
   </si>
   <si>
     <t>[448]</t>
   </si>
   <si>
-    <t>Turdus migratorius</t>
-  </si>
-  <si>
     <t>american robin</t>
   </si>
   <si>
@@ -1934,78 +1724,51 @@
     <t>Tyrannidae</t>
   </si>
   <si>
-    <t>Elaenia chiriquensis</t>
-  </si>
-  <si>
     <t>lesser elaenia</t>
   </si>
   <si>
     <t>[451]</t>
   </si>
   <si>
-    <t>Elaenia flavogaster</t>
-  </si>
-  <si>
     <t>yellow-bellied elaenia</t>
   </si>
   <si>
-    <t>Empidonax minimus</t>
-  </si>
-  <si>
     <t>least flycatcher</t>
   </si>
   <si>
     <t>[452; 453]</t>
   </si>
   <si>
-    <t>Empidonax traillii</t>
-  </si>
-  <si>
     <t>willow flycatcher</t>
   </si>
   <si>
     <t>[454]</t>
   </si>
   <si>
-    <t>Empidonax virescens</t>
-  </si>
-  <si>
     <t>acadian flycatcher</t>
   </si>
   <si>
     <t>[423; 455; 456]</t>
   </si>
   <si>
-    <t>Pyrocephalus rubinus</t>
-  </si>
-  <si>
     <t>vermilion flycatcher</t>
   </si>
   <si>
     <t>[457]</t>
   </si>
   <si>
-    <t>Sayornis phoebe</t>
-  </si>
-  <si>
     <t>eastern phoebe</t>
   </si>
   <si>
     <t>[458]</t>
   </si>
   <si>
-    <t>Tyrannus forficatus</t>
-  </si>
-  <si>
     <t xml:space="preserve">scissor-tailed flycatcher </t>
   </si>
   <si>
     <t>[459]</t>
   </si>
   <si>
-    <t>Tyrannus tyrannus</t>
-  </si>
-  <si>
     <t>eastern kingbird</t>
   </si>
   <si>
@@ -2015,36 +1778,24 @@
     <t>Vireonidae</t>
   </si>
   <si>
-    <t>Vireo griseus</t>
-  </si>
-  <si>
     <t>white-eyed vireo</t>
   </si>
   <si>
     <t>[463]</t>
   </si>
   <si>
-    <t>Vireo olivaceus</t>
-  </si>
-  <si>
     <t>red-eyed vireo</t>
   </si>
   <si>
     <t>[464]</t>
   </si>
   <si>
-    <t>Vireo solitarius</t>
-  </si>
-  <si>
     <t>blue-headed vireo</t>
   </si>
   <si>
     <t>Zosteropidae</t>
   </si>
   <si>
-    <t>Zosterops lateralis</t>
-  </si>
-  <si>
     <t>capricorn silvereye</t>
   </si>
   <si>
@@ -2054,18 +1805,12 @@
     <t>Picidae</t>
   </si>
   <si>
-    <t>Colaptes auratus</t>
-  </si>
-  <si>
     <t>northern flickers</t>
   </si>
   <si>
     <t>[466]</t>
   </si>
   <si>
-    <t>Colaptes campestris</t>
-  </si>
-  <si>
     <t xml:space="preserve">campo flicker </t>
   </si>
   <si>
@@ -2075,36 +1820,24 @@
     <t>[467]</t>
   </si>
   <si>
-    <t>Jynx torquilla</t>
-  </si>
-  <si>
     <t>eurasian wryneck</t>
   </si>
   <si>
     <t>[468]</t>
   </si>
   <si>
-    <t>Leuconotopicus borealis</t>
-  </si>
-  <si>
     <t>red-cockaded woodpecker</t>
   </si>
   <si>
     <t>[469]</t>
   </si>
   <si>
-    <t>Melanerpes formicivorus</t>
-  </si>
-  <si>
     <t>acorn woodpecker</t>
   </si>
   <si>
     <t>[470; 471]</t>
   </si>
   <si>
-    <t>Picoides tridactylus</t>
-  </si>
-  <si>
     <t>three-toed woodpecker</t>
   </si>
   <si>
@@ -2114,54 +1847,36 @@
     <t>Diomedeidae</t>
   </si>
   <si>
-    <t>Diomedea exulans</t>
-  </si>
-  <si>
     <t>wandering albatross</t>
   </si>
   <si>
     <t>[474-476]</t>
   </si>
   <si>
-    <t>Phoebastria irrorata</t>
-  </si>
-  <si>
     <t>waved albatrosses</t>
   </si>
   <si>
     <t>[477-479]</t>
   </si>
   <si>
-    <t>Thalassarche cauta</t>
-  </si>
-  <si>
     <t>shy albatrosses</t>
   </si>
   <si>
     <t>[480]</t>
   </si>
   <si>
-    <t>Thalassarche chrysostoma</t>
-  </si>
-  <si>
     <t>grey-headed albatross</t>
   </si>
   <si>
     <t>[474]</t>
   </si>
   <si>
-    <t>Thalassarche melanophris</t>
-  </si>
-  <si>
     <t>black-browed albatross</t>
   </si>
   <si>
     <t>Hydrobatidae</t>
   </si>
   <si>
-    <t>Hydrobates leucorhous</t>
-  </si>
-  <si>
     <t>leach's storm petrel</t>
   </si>
   <si>
@@ -2171,9 +1886,6 @@
     <t>Oceanitidae</t>
   </si>
   <si>
-    <t>Oceanites oceanicus</t>
-  </si>
-  <si>
     <t>wilson's storm petrel</t>
   </si>
   <si>
@@ -2183,45 +1895,30 @@
     <t>Procellariidae</t>
   </si>
   <si>
-    <t>Ardenna tenuirostris</t>
-  </si>
-  <si>
     <t>short-tailed shearwater</t>
   </si>
   <si>
     <t>[483]</t>
   </si>
   <si>
-    <t>Calonectris diomedea</t>
-  </si>
-  <si>
     <t>cory's shearwater</t>
   </si>
   <si>
     <t>[484; 485]</t>
   </si>
   <si>
-    <t>Fulmarus glacialis</t>
-  </si>
-  <si>
     <t>northern fulmar</t>
   </si>
   <si>
     <t>[486]</t>
   </si>
   <si>
-    <t>Pachyptila belcheri</t>
-  </si>
-  <si>
     <t>thin-billed prions</t>
   </si>
   <si>
     <t>[487]</t>
   </si>
   <si>
-    <t>Thalassoica antarctica</t>
-  </si>
-  <si>
     <t>antarctic petrel</t>
   </si>
   <si>
@@ -2231,9 +1928,6 @@
     <t>Psittacidae</t>
   </si>
   <si>
-    <t>Cyanoliseus patagonus</t>
-  </si>
-  <si>
     <t>burrowing parrot</t>
   </si>
   <si>
@@ -2243,36 +1937,24 @@
     <t>Spheniscidae</t>
   </si>
   <si>
-    <t>Eudyptes schlegeli</t>
-  </si>
-  <si>
     <t>royal penguin</t>
   </si>
   <si>
     <t>[490]</t>
   </si>
   <si>
-    <t>Pygoscelis adeliae</t>
-  </si>
-  <si>
     <t>adelie penguin</t>
   </si>
   <si>
     <t>[491]</t>
   </si>
   <si>
-    <t>Pygoscelis antarcticus</t>
-  </si>
-  <si>
     <t>chinstrap penguin</t>
   </si>
   <si>
     <t>[492]</t>
   </si>
   <si>
-    <t>Spheniscus humboldti</t>
-  </si>
-  <si>
     <t>humboldt penguin</t>
   </si>
   <si>
@@ -2282,63 +1964,42 @@
     <t>Strigidae</t>
   </si>
   <si>
-    <t>Aegolius funereus</t>
-  </si>
-  <si>
     <t>boreal owl</t>
   </si>
   <si>
     <t>[494]</t>
   </si>
   <si>
-    <t>Athene cunicularia</t>
-  </si>
-  <si>
     <t>burrowing owl</t>
   </si>
   <si>
     <t>[495]</t>
   </si>
   <si>
-    <t>Athene noctua</t>
-  </si>
-  <si>
     <t>little owl</t>
   </si>
   <si>
     <t>[496]</t>
   </si>
   <si>
-    <t>Megascops asio</t>
-  </si>
-  <si>
     <t>eastern screech-owl</t>
   </si>
   <si>
     <t>[497]</t>
   </si>
   <si>
-    <t>Otus elegans</t>
-  </si>
-  <si>
     <t>lanyuscops owl</t>
   </si>
   <si>
     <t>[498]</t>
   </si>
   <si>
-    <t>Psiloscops flammeolus</t>
-  </si>
-  <si>
     <t>flammulated owl</t>
   </si>
   <si>
     <t>[499]</t>
   </si>
   <si>
-    <t>Strix aluco</t>
-  </si>
-  <si>
     <t>tawny owl</t>
   </si>
   <si>
@@ -2348,9 +2009,6 @@
     <t>Tytonidae</t>
   </si>
   <si>
-    <t>Tyto alba</t>
-  </si>
-  <si>
     <t>barn owl</t>
   </si>
   <si>
@@ -2360,9 +2018,6 @@
     <t>Tinamidae</t>
   </si>
   <si>
-    <t>Tinamus major</t>
-  </si>
-  <si>
     <t>great tinamou</t>
   </si>
   <si>
@@ -2372,9 +2027,6 @@
     <t>Fregatidae</t>
   </si>
   <si>
-    <t>Fregata minor</t>
-  </si>
-  <si>
     <t>great frigatebird</t>
   </si>
   <si>
@@ -2384,18 +2036,12 @@
     <t>Phalacrocoracidae</t>
   </si>
   <si>
-    <t>Phalacrocorax atriceps</t>
-  </si>
-  <si>
     <t>imperial shag</t>
   </si>
   <si>
     <t>[505; 506]</t>
   </si>
   <si>
-    <t>Phalacrocorax carbo</t>
-  </si>
-  <si>
     <t>great cormorant</t>
   </si>
   <si>
@@ -2405,27 +2051,18 @@
     <t>Sulidae</t>
   </si>
   <si>
-    <t>Sula granti</t>
-  </si>
-  <si>
     <t>nazca booby</t>
   </si>
   <si>
     <t>[508]</t>
   </si>
   <si>
-    <t>Sula nebouxii</t>
-  </si>
-  <si>
     <t>blue-footed booby</t>
   </si>
   <si>
     <t>[509-511]</t>
   </si>
   <si>
-    <t>Sula sula</t>
-  </si>
-  <si>
     <t>red-footed booby</t>
   </si>
   <si>
@@ -2931,6 +2568,366 @@
   </si>
   <si>
     <t>Buteo_ridgwayi</t>
+  </si>
+  <si>
+    <t>Sula_sula</t>
+  </si>
+  <si>
+    <t>Periparus_ater</t>
+  </si>
+  <si>
+    <t>Poecile_atricapillus</t>
+  </si>
+  <si>
+    <t>Poecile_montanus</t>
+  </si>
+  <si>
+    <t>Poecile_varius</t>
+  </si>
+  <si>
+    <t>Pseudopodoces_humilis</t>
+  </si>
+  <si>
+    <t>Dendroica_caerulescens</t>
+  </si>
+  <si>
+    <t>Dendroica_pensylvanica</t>
+  </si>
+  <si>
+    <t>Dendroica_petechia</t>
+  </si>
+  <si>
+    <t>Geothlypis_trichas</t>
+  </si>
+  <si>
+    <t>Setophaga_ruticilla</t>
+  </si>
+  <si>
+    <t>Wilsonia_citrina</t>
+  </si>
+  <si>
+    <t>Passer_domesticus</t>
+  </si>
+  <si>
+    <t>Passer_montanus</t>
+  </si>
+  <si>
+    <t>Petronia_petronia</t>
+  </si>
+  <si>
+    <t>Petroica_australis</t>
+  </si>
+  <si>
+    <t>Petroica_goodenovii</t>
+  </si>
+  <si>
+    <t>Chiroxiphia_lanceolata</t>
+  </si>
+  <si>
+    <t>Euplectes_orix</t>
+  </si>
+  <si>
+    <t>Plocepasser_mahali</t>
+  </si>
+  <si>
+    <t>Quelea_quelea</t>
+  </si>
+  <si>
+    <t>Pomatostomus_temporalis</t>
+  </si>
+  <si>
+    <t>Prunella_collaris</t>
+  </si>
+  <si>
+    <t>Prunella_modularis</t>
+  </si>
+  <si>
+    <t>Phainopepla_nitens</t>
+  </si>
+  <si>
+    <t>Remiz_pendulinus</t>
+  </si>
+  <si>
+    <t>Rhipidura_albiscapa</t>
+  </si>
+  <si>
+    <t>Sitta_pusilla</t>
+  </si>
+  <si>
+    <t>Lamprotornis_superbus</t>
+  </si>
+  <si>
+    <t>Sturnus_unicolor</t>
+  </si>
+  <si>
+    <t>Sturnus_vulgaris</t>
+  </si>
+  <si>
+    <t>Acrocephalus_arundinaceus</t>
+  </si>
+  <si>
+    <t>Acrocephalus_bistrigiceps</t>
+  </si>
+  <si>
+    <t>Acrocephalus_melanopogon</t>
+  </si>
+  <si>
+    <t>Acrocephalus_paludicola</t>
+  </si>
+  <si>
+    <t>Acrocephalus_palustris</t>
+  </si>
+  <si>
+    <t>Acrocephalus_schoenobaenus</t>
+  </si>
+  <si>
+    <t>Acrocephalus_scirpaceus</t>
+  </si>
+  <si>
+    <t>Acrocephalus_sechellensis</t>
+  </si>
+  <si>
+    <t>Acrocephalus_vaughani</t>
+  </si>
+  <si>
+    <t>Locustella_luscinioides</t>
+  </si>
+  <si>
+    <t>Phylloscopus_fuscatus</t>
+  </si>
+  <si>
+    <t>Phylloscopus_sibilatrix</t>
+  </si>
+  <si>
+    <t>Phylloscopus_trochilus</t>
+  </si>
+  <si>
+    <t>Cercomacra_tyrannina</t>
+  </si>
+  <si>
+    <t>Thamnophilus_atrinucha</t>
+  </si>
+  <si>
+    <t>Habia_fuscicauda</t>
+  </si>
+  <si>
+    <t>Piranga_olivacea</t>
+  </si>
+  <si>
+    <t>Ramphocelus_costaricensis</t>
+  </si>
+  <si>
+    <t>Turdoides_bicolor</t>
+  </si>
+  <si>
+    <t>Turdoides_squamiceps</t>
+  </si>
+  <si>
+    <t>Campylorhynchus_griseus</t>
+  </si>
+  <si>
+    <t>Campylorhynchus_nuchalis</t>
+  </si>
+  <si>
+    <t>Thryothorus_leucotis</t>
+  </si>
+  <si>
+    <t>Thryothorus_ludovicianus</t>
+  </si>
+  <si>
+    <t>Thryothorus_pleurostictus</t>
+  </si>
+  <si>
+    <t>Thryothorus_rufalbus</t>
+  </si>
+  <si>
+    <t>Troglodytes_aedon</t>
+  </si>
+  <si>
+    <t>Erythropygia_coryphaeus</t>
+  </si>
+  <si>
+    <t>Hylocichla_mustelina</t>
+  </si>
+  <si>
+    <t>Luscinia_svecica</t>
+  </si>
+  <si>
+    <t>Oenanthe_oenanthe</t>
+  </si>
+  <si>
+    <t>Phoenicurus_ochruros</t>
+  </si>
+  <si>
+    <t>Phoenicurus_phoenicurus</t>
+  </si>
+  <si>
+    <t>Sialia_currucoides</t>
+  </si>
+  <si>
+    <t>Sialia_mexicana</t>
+  </si>
+  <si>
+    <t>Sialia_sialis</t>
+  </si>
+  <si>
+    <t>Turdus_albicollis</t>
+  </si>
+  <si>
+    <t>Turdus_grayi</t>
+  </si>
+  <si>
+    <t>Turdus_migratorius</t>
+  </si>
+  <si>
+    <t>Elaenia_chiriquensis</t>
+  </si>
+  <si>
+    <t>Elaenia_flavogaster</t>
+  </si>
+  <si>
+    <t>Empidonax_minimus</t>
+  </si>
+  <si>
+    <t>Empidonax_traillii</t>
+  </si>
+  <si>
+    <t>Empidonax_virescens</t>
+  </si>
+  <si>
+    <t>Pyrocephalus_rubinus</t>
+  </si>
+  <si>
+    <t>Sayornis_phoebe</t>
+  </si>
+  <si>
+    <t>Tyrannus_forficatus</t>
+  </si>
+  <si>
+    <t>Tyrannus_tyrannus</t>
+  </si>
+  <si>
+    <t>Vireo_griseus</t>
+  </si>
+  <si>
+    <t>Vireo_olivaceus</t>
+  </si>
+  <si>
+    <t>Vireo_solitarius</t>
+  </si>
+  <si>
+    <t>Zosterops_lateralis</t>
+  </si>
+  <si>
+    <t>Colaptes_auratus</t>
+  </si>
+  <si>
+    <t>Colaptes_campestris</t>
+  </si>
+  <si>
+    <t>Jynx_torquilla</t>
+  </si>
+  <si>
+    <t>Leuconotopicus_borealis</t>
+  </si>
+  <si>
+    <t>Melanerpes_formicivorus</t>
+  </si>
+  <si>
+    <t>Picoides_tridactylus</t>
+  </si>
+  <si>
+    <t>Diomedea_exulans</t>
+  </si>
+  <si>
+    <t>Phoebastria_irrorata</t>
+  </si>
+  <si>
+    <t>Thalassarche_cauta</t>
+  </si>
+  <si>
+    <t>Thalassarche_chrysostoma</t>
+  </si>
+  <si>
+    <t>Thalassarche_melanophris</t>
+  </si>
+  <si>
+    <t>Hydrobates_leucorhous</t>
+  </si>
+  <si>
+    <t>Oceanites_oceanicus</t>
+  </si>
+  <si>
+    <t>Ardenna_tenuirostris</t>
+  </si>
+  <si>
+    <t>Calonectris_diomedea</t>
+  </si>
+  <si>
+    <t>Fulmarus_glacialis</t>
+  </si>
+  <si>
+    <t>Pachyptila_belcheri</t>
+  </si>
+  <si>
+    <t>Thalassoica_antarctica</t>
+  </si>
+  <si>
+    <t>Cyanoliseus_patagonus</t>
+  </si>
+  <si>
+    <t>Eudyptes_schlegeli</t>
+  </si>
+  <si>
+    <t>Pygoscelis_adeliae</t>
+  </si>
+  <si>
+    <t>Pygoscelis_antarcticus</t>
+  </si>
+  <si>
+    <t>Spheniscus_humboldti</t>
+  </si>
+  <si>
+    <t>Aegolius_funereus</t>
+  </si>
+  <si>
+    <t>Athene_cunicularia</t>
+  </si>
+  <si>
+    <t>Athene_noctua</t>
+  </si>
+  <si>
+    <t>Megascops_asio</t>
+  </si>
+  <si>
+    <t>Otus_elegans</t>
+  </si>
+  <si>
+    <t>Psiloscops_flammeolus</t>
+  </si>
+  <si>
+    <t>Strix_aluco</t>
+  </si>
+  <si>
+    <t>Tyto_alba</t>
+  </si>
+  <si>
+    <t>Tinamus_major</t>
+  </si>
+  <si>
+    <t>Fregata_minor</t>
+  </si>
+  <si>
+    <t>Phalacrocorax_atriceps</t>
+  </si>
+  <si>
+    <t>Phalacrocorax_carbo</t>
+  </si>
+  <si>
+    <t>Sula_granti</t>
+  </si>
+  <si>
+    <t>Sula_nebouxii</t>
   </si>
 </sst>
 </file>
@@ -3072,7 +3069,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3107,31 +3104,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3448,8 +3430,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5E40600-E148-6841-B5A6-7A57F75A1286}">
-  <dimension ref="A1:N287"/>
+  <dimension ref="A1:N284"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="27.1640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
@@ -3471,25 +3456,25 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>792</v>
+        <v>671</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>793</v>
+        <v>672</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>794</v>
+        <v>673</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>795</v>
+        <v>674</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>9</v>
@@ -3497,7 +3482,7 @@
     </row>
     <row r="2" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>955</v>
+        <v>834</v>
       </c>
       <c r="B2" s="4">
         <v>1</v>
@@ -3541,7 +3526,7 @@
     </row>
     <row r="3" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>956</v>
+        <v>835</v>
       </c>
       <c r="B3" s="4">
         <v>1</v>
@@ -3585,7 +3570,7 @@
     </row>
     <row r="4" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>957</v>
+        <v>836</v>
       </c>
       <c r="B4" s="4">
         <v>1</v>
@@ -3629,7 +3614,7 @@
     </row>
     <row r="5" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>958</v>
+        <v>837</v>
       </c>
       <c r="B5" s="4">
         <v>1</v>
@@ -3673,7 +3658,7 @@
     </row>
     <row r="6" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>796</v>
+        <v>675</v>
       </c>
       <c r="B6" s="4">
         <v>1</v>
@@ -3717,7 +3702,7 @@
     </row>
     <row r="7" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>797</v>
+        <v>676</v>
       </c>
       <c r="B7" s="4">
         <v>2</v>
@@ -3761,7 +3746,7 @@
     </row>
     <row r="8" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>798</v>
+        <v>677</v>
       </c>
       <c r="B8" s="4">
         <v>2</v>
@@ -3805,7 +3790,7 @@
     </row>
     <row r="9" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>799</v>
+        <v>678</v>
       </c>
       <c r="B9" s="4">
         <v>2</v>
@@ -3849,7 +3834,7 @@
     </row>
     <row r="10" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>800</v>
+        <v>679</v>
       </c>
       <c r="B10" s="4">
         <v>2</v>
@@ -3893,7 +3878,7 @@
     </row>
     <row r="11" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>801</v>
+        <v>680</v>
       </c>
       <c r="B11" s="4">
         <v>2</v>
@@ -3937,7 +3922,7 @@
     </row>
     <row r="12" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>802</v>
+        <v>681</v>
       </c>
       <c r="B12" s="4">
         <v>2</v>
@@ -3981,7 +3966,7 @@
     </row>
     <row r="13" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>803</v>
+        <v>682</v>
       </c>
       <c r="B13" s="4">
         <v>2</v>
@@ -4025,7 +4010,7 @@
     </row>
     <row r="14" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>804</v>
+        <v>683</v>
       </c>
       <c r="B14" s="4">
         <v>2</v>
@@ -4069,7 +4054,7 @@
     </row>
     <row r="15" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>805</v>
+        <v>684</v>
       </c>
       <c r="B15" s="4">
         <v>3</v>
@@ -4113,7 +4098,7 @@
     </row>
     <row r="16" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>806</v>
+        <v>685</v>
       </c>
       <c r="B16" s="4">
         <v>3</v>
@@ -4157,7 +4142,7 @@
     </row>
     <row r="17" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>807</v>
+        <v>686</v>
       </c>
       <c r="B17" s="4">
         <v>4</v>
@@ -4201,7 +4186,7 @@
     </row>
     <row r="18" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>808</v>
+        <v>687</v>
       </c>
       <c r="B18" s="4">
         <v>5</v>
@@ -4245,7 +4230,7 @@
     </row>
     <row r="19" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>809</v>
+        <v>688</v>
       </c>
       <c r="B19" s="4">
         <v>6</v>
@@ -4289,7 +4274,7 @@
     </row>
     <row r="20" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>810</v>
+        <v>689</v>
       </c>
       <c r="B20" s="4">
         <v>6</v>
@@ -4333,7 +4318,7 @@
     </row>
     <row r="21" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>811</v>
+        <v>690</v>
       </c>
       <c r="B21" s="4">
         <v>6</v>
@@ -4377,7 +4362,7 @@
     </row>
     <row r="22" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>812</v>
+        <v>691</v>
       </c>
       <c r="B22" s="4">
         <v>6</v>
@@ -4421,7 +4406,7 @@
     </row>
     <row r="23" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>813</v>
+        <v>692</v>
       </c>
       <c r="B23" s="4">
         <v>6</v>
@@ -4465,7 +4450,7 @@
     </row>
     <row r="24" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>814</v>
+        <v>693</v>
       </c>
       <c r="B24" s="4">
         <v>6</v>
@@ -4509,7 +4494,7 @@
     </row>
     <row r="25" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>815</v>
+        <v>694</v>
       </c>
       <c r="B25" s="4">
         <v>6</v>
@@ -4553,7 +4538,7 @@
     </row>
     <row r="26" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>816</v>
+        <v>695</v>
       </c>
       <c r="B26" s="4">
         <v>6</v>
@@ -4597,7 +4582,7 @@
     </row>
     <row r="27" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>817</v>
+        <v>696</v>
       </c>
       <c r="B27" s="4">
         <v>6</v>
@@ -4641,7 +4626,7 @@
     </row>
     <row r="28" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>818</v>
+        <v>697</v>
       </c>
       <c r="B28" s="4">
         <v>6</v>
@@ -4685,7 +4670,7 @@
     </row>
     <row r="29" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>819</v>
+        <v>698</v>
       </c>
       <c r="B29" s="4">
         <v>6</v>
@@ -4729,7 +4714,7 @@
     </row>
     <row r="30" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>820</v>
+        <v>699</v>
       </c>
       <c r="B30" s="4">
         <v>6</v>
@@ -4773,7 +4758,7 @@
     </row>
     <row r="31" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>821</v>
+        <v>700</v>
       </c>
       <c r="B31" s="4">
         <v>6</v>
@@ -4817,7 +4802,7 @@
     </row>
     <row r="32" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>822</v>
+        <v>701</v>
       </c>
       <c r="B32" s="4">
         <v>6</v>
@@ -4861,7 +4846,7 @@
     </row>
     <row r="33" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>823</v>
+        <v>702</v>
       </c>
       <c r="B33" s="4">
         <v>6</v>
@@ -4905,7 +4890,7 @@
     </row>
     <row r="34" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>824</v>
+        <v>703</v>
       </c>
       <c r="B34" s="4">
         <v>6</v>
@@ -4949,7 +4934,7 @@
     </row>
     <row r="35" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>825</v>
+        <v>704</v>
       </c>
       <c r="B35" s="4">
         <v>6</v>
@@ -4993,7 +4978,7 @@
     </row>
     <row r="36" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>826</v>
+        <v>705</v>
       </c>
       <c r="B36" s="4">
         <v>6</v>
@@ -5037,7 +5022,7 @@
     </row>
     <row r="37" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>827</v>
+        <v>706</v>
       </c>
       <c r="B37" s="4">
         <v>6</v>
@@ -5081,7 +5066,7 @@
     </row>
     <row r="38" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>828</v>
+        <v>707</v>
       </c>
       <c r="B38" s="4">
         <v>6</v>
@@ -5125,7 +5110,7 @@
     </row>
     <row r="39" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>829</v>
+        <v>708</v>
       </c>
       <c r="B39" s="4">
         <v>6</v>
@@ -5169,7 +5154,7 @@
     </row>
     <row r="40" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>830</v>
+        <v>709</v>
       </c>
       <c r="B40" s="4">
         <v>6</v>
@@ -5213,7 +5198,7 @@
     </row>
     <row r="41" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>831</v>
+        <v>710</v>
       </c>
       <c r="B41" s="4">
         <v>6</v>
@@ -5257,7 +5242,7 @@
     </row>
     <row r="42" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>832</v>
+        <v>711</v>
       </c>
       <c r="B42" s="4">
         <v>6</v>
@@ -5301,7 +5286,7 @@
     </row>
     <row r="43" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>833</v>
+        <v>712</v>
       </c>
       <c r="B43" s="4">
         <v>6</v>
@@ -5345,7 +5330,7 @@
     </row>
     <row r="44" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>834</v>
+        <v>713</v>
       </c>
       <c r="B44" s="4">
         <v>6</v>
@@ -5389,7 +5374,7 @@
     </row>
     <row r="45" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>835</v>
+        <v>714</v>
       </c>
       <c r="B45" s="4">
         <v>6</v>
@@ -5433,7 +5418,7 @@
     </row>
     <row r="46" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>836</v>
+        <v>715</v>
       </c>
       <c r="B46" s="4">
         <v>6</v>
@@ -5477,7 +5462,7 @@
     </row>
     <row r="47" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>837</v>
+        <v>716</v>
       </c>
       <c r="B47" s="4">
         <v>6</v>
@@ -5521,7 +5506,7 @@
     </row>
     <row r="48" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>838</v>
+        <v>717</v>
       </c>
       <c r="B48" s="4">
         <v>6</v>
@@ -5565,7 +5550,7 @@
     </row>
     <row r="49" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>839</v>
+        <v>718</v>
       </c>
       <c r="B49" s="4">
         <v>6</v>
@@ -5609,7 +5594,7 @@
     </row>
     <row r="50" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>840</v>
+        <v>719</v>
       </c>
       <c r="B50" s="4">
         <v>7</v>
@@ -5653,7 +5638,7 @@
     </row>
     <row r="51" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>841</v>
+        <v>720</v>
       </c>
       <c r="B51" s="4">
         <v>7</v>
@@ -5697,7 +5682,7 @@
     </row>
     <row r="52" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>842</v>
+        <v>721</v>
       </c>
       <c r="B52" s="4">
         <v>8</v>
@@ -5741,7 +5726,7 @@
     </row>
     <row r="53" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>843</v>
+        <v>722</v>
       </c>
       <c r="B53" s="4">
         <v>8</v>
@@ -5785,7 +5770,7 @@
     </row>
     <row r="54" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>844</v>
+        <v>723</v>
       </c>
       <c r="B54" s="4">
         <v>9</v>
@@ -5829,7 +5814,7 @@
     </row>
     <row r="55" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>845</v>
+        <v>724</v>
       </c>
       <c r="B55" s="4">
         <v>9</v>
@@ -5873,7 +5858,7 @@
     </row>
     <row r="56" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>846</v>
+        <v>725</v>
       </c>
       <c r="B56" s="4">
         <v>9</v>
@@ -5917,7 +5902,7 @@
     </row>
     <row r="57" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>847</v>
+        <v>726</v>
       </c>
       <c r="B57" s="4">
         <v>9</v>
@@ -5961,7 +5946,7 @@
     </row>
     <row r="58" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>848</v>
+        <v>727</v>
       </c>
       <c r="B58" s="4">
         <v>9</v>
@@ -6005,7 +5990,7 @@
     </row>
     <row r="59" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>849</v>
+        <v>728</v>
       </c>
       <c r="B59" s="4">
         <v>9</v>
@@ -6049,7 +6034,7 @@
     </row>
     <row r="60" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>850</v>
+        <v>729</v>
       </c>
       <c r="B60" s="4">
         <v>10</v>
@@ -6093,7 +6078,7 @@
     </row>
     <row r="61" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>851</v>
+        <v>730</v>
       </c>
       <c r="B61" s="4">
         <v>10</v>
@@ -6137,7 +6122,7 @@
     </row>
     <row r="62" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>852</v>
+        <v>731</v>
       </c>
       <c r="B62" s="4">
         <v>10</v>
@@ -6181,7 +6166,7 @@
     </row>
     <row r="63" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>853</v>
+        <v>732</v>
       </c>
       <c r="B63" s="4">
         <v>10</v>
@@ -6225,7 +6210,7 @@
     </row>
     <row r="64" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>854</v>
+        <v>733</v>
       </c>
       <c r="B64" s="4">
         <v>10</v>
@@ -6269,7 +6254,7 @@
     </row>
     <row r="65" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>855</v>
+        <v>734</v>
       </c>
       <c r="B65" s="4">
         <v>10</v>
@@ -6313,7 +6298,7 @@
     </row>
     <row r="66" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>856</v>
+        <v>735</v>
       </c>
       <c r="B66" s="4">
         <v>10</v>
@@ -6357,7 +6342,7 @@
     </row>
     <row r="67" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>857</v>
+        <v>736</v>
       </c>
       <c r="B67" s="4">
         <v>11</v>
@@ -6401,7 +6386,7 @@
     </row>
     <row r="68" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>858</v>
+        <v>737</v>
       </c>
       <c r="B68" s="4">
         <v>12</v>
@@ -6445,7 +6430,7 @@
     </row>
     <row r="69" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>859</v>
+        <v>738</v>
       </c>
       <c r="B69" s="4">
         <v>12</v>
@@ -6489,7 +6474,7 @@
     </row>
     <row r="70" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>860</v>
+        <v>739</v>
       </c>
       <c r="B70" s="4">
         <v>12</v>
@@ -6533,7 +6518,7 @@
     </row>
     <row r="71" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>861</v>
+        <v>740</v>
       </c>
       <c r="B71" s="4">
         <v>12</v>
@@ -6577,7 +6562,7 @@
     </row>
     <row r="72" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>862</v>
+        <v>741</v>
       </c>
       <c r="B72" s="4">
         <v>12</v>
@@ -6621,7 +6606,7 @@
     </row>
     <row r="73" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>863</v>
+        <v>742</v>
       </c>
       <c r="B73" s="4">
         <v>13</v>
@@ -6665,7 +6650,7 @@
     </row>
     <row r="74" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>864</v>
+        <v>743</v>
       </c>
       <c r="B74" s="4">
         <v>14</v>
@@ -6709,7 +6694,7 @@
     </row>
     <row r="75" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>865</v>
+        <v>744</v>
       </c>
       <c r="B75" s="4">
         <v>14</v>
@@ -6753,7 +6738,7 @@
     </row>
     <row r="76" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>866</v>
+        <v>745</v>
       </c>
       <c r="B76" s="4">
         <v>14</v>
@@ -6797,7 +6782,7 @@
     </row>
     <row r="77" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>867</v>
+        <v>746</v>
       </c>
       <c r="B77" s="4">
         <v>14</v>
@@ -6841,7 +6826,7 @@
     </row>
     <row r="78" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>868</v>
+        <v>747</v>
       </c>
       <c r="B78" s="4">
         <v>14</v>
@@ -6885,7 +6870,7 @@
     </row>
     <row r="79" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>869</v>
+        <v>748</v>
       </c>
       <c r="B79" s="4">
         <v>14</v>
@@ -6929,7 +6914,7 @@
     </row>
     <row r="80" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>870</v>
+        <v>749</v>
       </c>
       <c r="B80" s="4">
         <v>14</v>
@@ -6973,7 +6958,7 @@
     </row>
     <row r="81" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>871</v>
+        <v>750</v>
       </c>
       <c r="B81" s="4">
         <v>14</v>
@@ -7017,7 +7002,7 @@
     </row>
     <row r="82" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>872</v>
+        <v>751</v>
       </c>
       <c r="B82" s="4">
         <v>14</v>
@@ -7061,7 +7046,7 @@
     </row>
     <row r="83" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>873</v>
+        <v>752</v>
       </c>
       <c r="B83" s="4">
         <v>14</v>
@@ -7105,7 +7090,7 @@
     </row>
     <row r="84" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>874</v>
+        <v>753</v>
       </c>
       <c r="B84" s="4">
         <v>14</v>
@@ -7149,7 +7134,7 @@
     </row>
     <row r="85" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>875</v>
+        <v>754</v>
       </c>
       <c r="B85" s="4">
         <v>14</v>
@@ -7193,7 +7178,7 @@
     </row>
     <row r="86" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>876</v>
+        <v>755</v>
       </c>
       <c r="B86" s="4">
         <v>14</v>
@@ -7237,7 +7222,7 @@
     </row>
     <row r="87" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>877</v>
+        <v>756</v>
       </c>
       <c r="B87" s="4">
         <v>14</v>
@@ -7281,7 +7266,7 @@
     </row>
     <row r="88" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>878</v>
+        <v>757</v>
       </c>
       <c r="B88" s="4">
         <v>14</v>
@@ -7325,7 +7310,7 @@
     </row>
     <row r="89" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>879</v>
+        <v>758</v>
       </c>
       <c r="B89" s="4">
         <v>14</v>
@@ -7369,7 +7354,7 @@
     </row>
     <row r="90" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>880</v>
+        <v>759</v>
       </c>
       <c r="B90" s="4">
         <v>14</v>
@@ -7413,7 +7398,7 @@
     </row>
     <row r="91" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>881</v>
+        <v>760</v>
       </c>
       <c r="B91" s="4">
         <v>14</v>
@@ -7457,7 +7442,7 @@
     </row>
     <row r="92" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>882</v>
+        <v>761</v>
       </c>
       <c r="B92" s="4">
         <v>14</v>
@@ -7501,7 +7486,7 @@
     </row>
     <row r="93" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>883</v>
+        <v>762</v>
       </c>
       <c r="B93" s="4">
         <v>14</v>
@@ -7545,7 +7530,7 @@
     </row>
     <row r="94" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>884</v>
+        <v>763</v>
       </c>
       <c r="B94" s="4">
         <v>14</v>
@@ -7589,7 +7574,7 @@
     </row>
     <row r="95" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>885</v>
+        <v>764</v>
       </c>
       <c r="B95" s="4">
         <v>14</v>
@@ -7633,7 +7618,7 @@
     </row>
     <row r="96" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>886</v>
+        <v>765</v>
       </c>
       <c r="B96" s="4">
         <v>14</v>
@@ -7677,7 +7662,7 @@
     </row>
     <row r="97" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>887</v>
+        <v>766</v>
       </c>
       <c r="B97" s="4">
         <v>14</v>
@@ -7721,7 +7706,7 @@
     </row>
     <row r="98" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>888</v>
+        <v>767</v>
       </c>
       <c r="B98" s="4">
         <v>14</v>
@@ -7765,7 +7750,7 @@
     </row>
     <row r="99" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
-        <v>889</v>
+        <v>768</v>
       </c>
       <c r="B99" s="4">
         <v>14</v>
@@ -7809,7 +7794,7 @@
     </row>
     <row r="100" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>890</v>
+        <v>769</v>
       </c>
       <c r="B100" s="4">
         <v>14</v>
@@ -7853,7 +7838,7 @@
     </row>
     <row r="101" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>891</v>
+        <v>770</v>
       </c>
       <c r="B101" s="4">
         <v>14</v>
@@ -7897,7 +7882,7 @@
     </row>
     <row r="102" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>892</v>
+        <v>771</v>
       </c>
       <c r="B102" s="4">
         <v>14</v>
@@ -7941,7 +7926,7 @@
     </row>
     <row r="103" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
-        <v>893</v>
+        <v>772</v>
       </c>
       <c r="B103" s="4">
         <v>14</v>
@@ -7985,7 +7970,7 @@
     </row>
     <row r="104" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>894</v>
+        <v>773</v>
       </c>
       <c r="B104" s="4">
         <v>14</v>
@@ -8029,7 +8014,7 @@
     </row>
     <row r="105" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>895</v>
+        <v>774</v>
       </c>
       <c r="B105" s="4">
         <v>14</v>
@@ -8073,7 +8058,7 @@
     </row>
     <row r="106" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>896</v>
+        <v>775</v>
       </c>
       <c r="B106" s="4">
         <v>14</v>
@@ -8117,7 +8102,7 @@
     </row>
     <row r="107" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
-        <v>897</v>
+        <v>776</v>
       </c>
       <c r="B107" s="4">
         <v>14</v>
@@ -8161,7 +8146,7 @@
     </row>
     <row r="108" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>898</v>
+        <v>777</v>
       </c>
       <c r="B108" s="4">
         <v>14</v>
@@ -8205,7 +8190,7 @@
     </row>
     <row r="109" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
-        <v>899</v>
+        <v>778</v>
       </c>
       <c r="B109" s="4">
         <v>14</v>
@@ -8249,7 +8234,7 @@
     </row>
     <row r="110" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
-        <v>900</v>
+        <v>779</v>
       </c>
       <c r="B110" s="4">
         <v>14</v>
@@ -8293,7 +8278,7 @@
     </row>
     <row r="111" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
-        <v>901</v>
+        <v>780</v>
       </c>
       <c r="B111" s="4">
         <v>14</v>
@@ -8337,7 +8322,7 @@
     </row>
     <row r="112" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
-        <v>902</v>
+        <v>781</v>
       </c>
       <c r="B112" s="4">
         <v>14</v>
@@ -8381,7 +8366,7 @@
     </row>
     <row r="113" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A113" s="6" t="s">
-        <v>903</v>
+        <v>782</v>
       </c>
       <c r="B113" s="4">
         <v>14</v>
@@ -8425,7 +8410,7 @@
     </row>
     <row r="114" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
-        <v>904</v>
+        <v>783</v>
       </c>
       <c r="B114" s="4">
         <v>14</v>
@@ -8469,7 +8454,7 @@
     </row>
     <row r="115" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A115" s="6" t="s">
-        <v>905</v>
+        <v>784</v>
       </c>
       <c r="B115" s="4">
         <v>14</v>
@@ -8513,7 +8498,7 @@
     </row>
     <row r="116" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
-        <v>906</v>
+        <v>785</v>
       </c>
       <c r="B116" s="4">
         <v>14</v>
@@ -8557,7 +8542,7 @@
     </row>
     <row r="117" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
-        <v>907</v>
+        <v>786</v>
       </c>
       <c r="B117" s="4">
         <v>14</v>
@@ -8601,7 +8586,7 @@
     </row>
     <row r="118" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
-        <v>908</v>
+        <v>787</v>
       </c>
       <c r="B118" s="4">
         <v>14</v>
@@ -8645,7 +8630,7 @@
     </row>
     <row r="119" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
-        <v>909</v>
+        <v>788</v>
       </c>
       <c r="B119" s="4">
         <v>14</v>
@@ -8689,7 +8674,7 @@
     </row>
     <row r="120" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
-        <v>910</v>
+        <v>789</v>
       </c>
       <c r="B120" s="4">
         <v>14</v>
@@ -8733,7 +8718,7 @@
     </row>
     <row r="121" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A121" s="6" t="s">
-        <v>911</v>
+        <v>790</v>
       </c>
       <c r="B121" s="4">
         <v>14</v>
@@ -8777,7 +8762,7 @@
     </row>
     <row r="122" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
-        <v>912</v>
+        <v>791</v>
       </c>
       <c r="B122" s="4">
         <v>14</v>
@@ -8821,7 +8806,7 @@
     </row>
     <row r="123" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A123" s="6" t="s">
-        <v>913</v>
+        <v>792</v>
       </c>
       <c r="B123" s="4">
         <v>14</v>
@@ -8865,7 +8850,7 @@
     </row>
     <row r="124" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
-        <v>914</v>
+        <v>793</v>
       </c>
       <c r="B124" s="4">
         <v>14</v>
@@ -8909,7 +8894,7 @@
     </row>
     <row r="125" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A125" s="6" t="s">
-        <v>915</v>
+        <v>794</v>
       </c>
       <c r="B125" s="4">
         <v>14</v>
@@ -8953,7 +8938,7 @@
     </row>
     <row r="126" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
-        <v>916</v>
+        <v>795</v>
       </c>
       <c r="B126" s="4">
         <v>14</v>
@@ -8997,7 +8982,7 @@
     </row>
     <row r="127" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
-        <v>917</v>
+        <v>796</v>
       </c>
       <c r="B127" s="4">
         <v>14</v>
@@ -9041,7 +9026,7 @@
     </row>
     <row r="128" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
-        <v>918</v>
+        <v>797</v>
       </c>
       <c r="B128" s="4">
         <v>14</v>
@@ -9085,7 +9070,7 @@
     </row>
     <row r="129" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
-        <v>919</v>
+        <v>798</v>
       </c>
       <c r="B129" s="4">
         <v>14</v>
@@ -9129,7 +9114,7 @@
     </row>
     <row r="130" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
-        <v>920</v>
+        <v>799</v>
       </c>
       <c r="B130" s="4">
         <v>14</v>
@@ -9173,7 +9158,7 @@
     </row>
     <row r="131" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
-        <v>921</v>
+        <v>800</v>
       </c>
       <c r="B131" s="4">
         <v>14</v>
@@ -9217,7 +9202,7 @@
     </row>
     <row r="132" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
-        <v>922</v>
+        <v>801</v>
       </c>
       <c r="B132" s="4">
         <v>14</v>
@@ -9261,7 +9246,7 @@
     </row>
     <row r="133" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
-        <v>923</v>
+        <v>802</v>
       </c>
       <c r="B133" s="4">
         <v>14</v>
@@ -9305,7 +9290,7 @@
     </row>
     <row r="134" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
-        <v>924</v>
+        <v>803</v>
       </c>
       <c r="B134" s="4">
         <v>14</v>
@@ -9349,7 +9334,7 @@
     </row>
     <row r="135" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
-        <v>925</v>
+        <v>804</v>
       </c>
       <c r="B135" s="4">
         <v>14</v>
@@ -9393,7 +9378,7 @@
     </row>
     <row r="136" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
-        <v>926</v>
+        <v>805</v>
       </c>
       <c r="B136" s="4">
         <v>14</v>
@@ -9437,7 +9422,7 @@
     </row>
     <row r="137" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A137" s="6" t="s">
-        <v>927</v>
+        <v>806</v>
       </c>
       <c r="B137" s="4">
         <v>14</v>
@@ -9481,7 +9466,7 @@
     </row>
     <row r="138" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
-        <v>928</v>
+        <v>807</v>
       </c>
       <c r="B138" s="4">
         <v>14</v>
@@ -9525,7 +9510,7 @@
     </row>
     <row r="139" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
-        <v>929</v>
+        <v>808</v>
       </c>
       <c r="B139" s="4">
         <v>14</v>
@@ -9569,7 +9554,7 @@
     </row>
     <row r="140" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
-        <v>930</v>
+        <v>809</v>
       </c>
       <c r="B140" s="4">
         <v>14</v>
@@ -9613,7 +9598,7 @@
     </row>
     <row r="141" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
-        <v>931</v>
+        <v>810</v>
       </c>
       <c r="B141" s="4">
         <v>14</v>
@@ -9657,7 +9642,7 @@
     </row>
     <row r="142" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
-        <v>932</v>
+        <v>811</v>
       </c>
       <c r="B142" s="4">
         <v>14</v>
@@ -9701,7 +9686,7 @@
     </row>
     <row r="143" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
-        <v>933</v>
+        <v>812</v>
       </c>
       <c r="B143" s="4">
         <v>14</v>
@@ -9745,7 +9730,7 @@
     </row>
     <row r="144" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
-        <v>934</v>
+        <v>813</v>
       </c>
       <c r="B144" s="4">
         <v>14</v>
@@ -9789,7 +9774,7 @@
     </row>
     <row r="145" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A145" s="6" t="s">
-        <v>935</v>
+        <v>814</v>
       </c>
       <c r="B145" s="4">
         <v>14</v>
@@ -9833,7 +9818,7 @@
     </row>
     <row r="146" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
-        <v>936</v>
+        <v>815</v>
       </c>
       <c r="B146" s="4">
         <v>14</v>
@@ -9877,7 +9862,7 @@
     </row>
     <row r="147" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
-        <v>937</v>
+        <v>816</v>
       </c>
       <c r="B147" s="4">
         <v>14</v>
@@ -9921,7 +9906,7 @@
     </row>
     <row r="148" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
-        <v>938</v>
+        <v>817</v>
       </c>
       <c r="B148" s="4">
         <v>14</v>
@@ -9965,7 +9950,7 @@
     </row>
     <row r="149" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
-        <v>939</v>
+        <v>818</v>
       </c>
       <c r="B149" s="4">
         <v>14</v>
@@ -10009,7 +9994,7 @@
     </row>
     <row r="150" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
-        <v>940</v>
+        <v>819</v>
       </c>
       <c r="B150" s="4">
         <v>14</v>
@@ -10053,7 +10038,7 @@
     </row>
     <row r="151" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
-        <v>941</v>
+        <v>820</v>
       </c>
       <c r="B151" s="4">
         <v>14</v>
@@ -10097,7 +10082,7 @@
     </row>
     <row r="152" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
-        <v>942</v>
+        <v>821</v>
       </c>
       <c r="B152" s="4">
         <v>14</v>
@@ -10141,7 +10126,7 @@
     </row>
     <row r="153" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
-        <v>943</v>
+        <v>822</v>
       </c>
       <c r="B153" s="4">
         <v>14</v>
@@ -10185,7 +10170,7 @@
     </row>
     <row r="154" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
-        <v>944</v>
+        <v>823</v>
       </c>
       <c r="B154" s="4">
         <v>14</v>
@@ -10229,7 +10214,7 @@
     </row>
     <row r="155" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
-        <v>945</v>
+        <v>824</v>
       </c>
       <c r="B155" s="4">
         <v>14</v>
@@ -10273,7 +10258,7 @@
     </row>
     <row r="156" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
-        <v>946</v>
+        <v>825</v>
       </c>
       <c r="B156" s="4">
         <v>14</v>
@@ -10317,7 +10302,7 @@
     </row>
     <row r="157" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
-        <v>947</v>
+        <v>826</v>
       </c>
       <c r="B157" s="4">
         <v>14</v>
@@ -10361,7 +10346,7 @@
     </row>
     <row r="158" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
-        <v>948</v>
+        <v>827</v>
       </c>
       <c r="B158" s="4">
         <v>14</v>
@@ -10405,7 +10390,7 @@
     </row>
     <row r="159" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
-        <v>949</v>
+        <v>828</v>
       </c>
       <c r="B159" s="4">
         <v>14</v>
@@ -10449,7 +10434,7 @@
     </row>
     <row r="160" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
-        <v>950</v>
+        <v>829</v>
       </c>
       <c r="B160" s="4">
         <v>14</v>
@@ -10493,7 +10478,7 @@
     </row>
     <row r="161" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
-        <v>951</v>
+        <v>830</v>
       </c>
       <c r="B161" s="4">
         <v>14</v>
@@ -10537,7 +10522,7 @@
     </row>
     <row r="162" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
-        <v>952</v>
+        <v>831</v>
       </c>
       <c r="B162" s="4">
         <v>14</v>
@@ -10581,7 +10566,7 @@
     </row>
     <row r="163" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
-        <v>953</v>
+        <v>832</v>
       </c>
       <c r="B163" s="4">
         <v>14</v>
@@ -10623,129 +10608,185 @@
         <v>395</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A164" s="15" t="s">
-        <v>954</v>
+    <row r="164" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="13" t="s">
+        <v>833</v>
       </c>
       <c r="B164" s="11">
         <v>14</v>
       </c>
-      <c r="C164" s="13" t="s">
+      <c r="C164" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="D164" s="13" t="s">
+      <c r="D164" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="E164" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F164" s="17">
+      <c r="E164" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F164" s="14">
         <v>9.43</v>
       </c>
-      <c r="G164" s="17">
+      <c r="G164" s="14">
         <v>6267</v>
       </c>
-      <c r="H164" s="17">
+      <c r="H164" s="14">
         <v>34.61</v>
       </c>
-      <c r="I164" s="17">
+      <c r="I164" s="14">
         <v>861</v>
       </c>
-      <c r="J164" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="K164" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="L164" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="M164" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="N164" s="13" t="s">
+      <c r="J164" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K164" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="L164" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="M164" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="N164" s="12" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="165" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="16"/>
-      <c r="B165" s="12"/>
-      <c r="C165" s="14"/>
-      <c r="D165" s="14"/>
-      <c r="E165" s="14"/>
-      <c r="F165" s="18"/>
-      <c r="G165" s="18"/>
-      <c r="H165" s="18"/>
-      <c r="I165" s="18"/>
-      <c r="J165" s="20"/>
-      <c r="K165" s="20"/>
-      <c r="L165" s="20"/>
-      <c r="M165" s="20"/>
-      <c r="N165" s="14"/>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A166" s="15" t="s">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A165" s="13" t="s">
+        <v>839</v>
+      </c>
+      <c r="B165" s="11">
+        <v>14</v>
+      </c>
+      <c r="C165" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="D165" s="12" t="s">
         <v>398</v>
       </c>
-      <c r="B166" s="11">
-        <v>14</v>
-      </c>
-      <c r="C166" s="13" t="s">
+      <c r="E165" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F165" s="14">
+        <v>31.14</v>
+      </c>
+      <c r="G165" s="14">
+        <v>3523</v>
+      </c>
+      <c r="H165" s="14">
+        <v>70.650000000000006</v>
+      </c>
+      <c r="I165" s="14">
+        <v>477</v>
+      </c>
+      <c r="J165" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K165" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="L165" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="M165" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="N165" s="12" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="6" t="s">
+        <v>840</v>
+      </c>
+      <c r="B166" s="4">
+        <v>14</v>
+      </c>
+      <c r="C166" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="D166" s="13" t="s">
-        <v>399</v>
-      </c>
-      <c r="E166" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F166" s="17">
-        <v>31.14</v>
-      </c>
-      <c r="G166" s="17">
-        <v>3523</v>
-      </c>
-      <c r="H166" s="17">
-        <v>70.650000000000006</v>
-      </c>
-      <c r="I166" s="17">
-        <v>477</v>
-      </c>
-      <c r="J166" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="K166" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="L166" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="M166" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="N166" s="13" t="s">
+      <c r="D166" s="5" t="s">
         <v>400</v>
       </c>
+      <c r="E166" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F166" s="7">
+        <v>11.83</v>
+      </c>
+      <c r="G166" s="7">
+        <v>710</v>
+      </c>
+      <c r="H166" s="7">
+        <v>31.3</v>
+      </c>
+      <c r="I166" s="7">
+        <v>115</v>
+      </c>
+      <c r="J166" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K166" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L166" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M166" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N166" s="5" t="s">
+        <v>401</v>
+      </c>
     </row>
     <row r="167" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="16"/>
-      <c r="B167" s="12"/>
-      <c r="C167" s="14"/>
-      <c r="D167" s="14"/>
-      <c r="E167" s="14"/>
-      <c r="F167" s="18"/>
-      <c r="G167" s="18"/>
-      <c r="H167" s="18"/>
-      <c r="I167" s="18"/>
-      <c r="J167" s="20"/>
-      <c r="K167" s="20"/>
-      <c r="L167" s="20"/>
-      <c r="M167" s="20"/>
-      <c r="N167" s="14"/>
+      <c r="A167" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="B167" s="4">
+        <v>14</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="D167" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="E167" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F167" s="7">
+        <v>0.89</v>
+      </c>
+      <c r="G167" s="7">
+        <v>112</v>
+      </c>
+      <c r="H167" s="7">
+        <v>4.17</v>
+      </c>
+      <c r="I167" s="7">
+        <v>24</v>
+      </c>
+      <c r="J167" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K167" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L167" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M167" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N167" s="5" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="168" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
-        <v>401</v>
+        <v>842</v>
       </c>
       <c r="B168" s="4">
         <v>14</v>
@@ -10754,22 +10795,22 @@
         <v>389</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F168" s="7">
-        <v>11.83</v>
+        <v>14.74</v>
       </c>
       <c r="G168" s="7">
-        <v>710</v>
+        <v>251</v>
       </c>
       <c r="H168" s="7">
-        <v>31.3</v>
+        <v>40</v>
       </c>
       <c r="I168" s="7">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="J168" s="8" t="s">
         <v>13</v>
@@ -10784,12 +10825,12 @@
         <v>13</v>
       </c>
       <c r="N168" s="5" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="169" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A169" s="6" t="s">
-        <v>404</v>
+        <v>843</v>
       </c>
       <c r="B169" s="4">
         <v>14</v>
@@ -10798,121 +10839,121 @@
         <v>389</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F169" s="7">
-        <v>0.89</v>
+        <v>12.63</v>
       </c>
       <c r="G169" s="7">
-        <v>112</v>
+        <v>966</v>
       </c>
       <c r="H169" s="7">
-        <v>4.17</v>
+        <v>32</v>
       </c>
       <c r="I169" s="7">
-        <v>24</v>
-      </c>
-      <c r="J169" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K169" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L169" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M169" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="J169" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K169" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L169" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M169" s="7" t="s">
         <v>13</v>
       </c>
       <c r="N169" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="170" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A170" s="6" t="s">
-        <v>407</v>
+        <v>844</v>
       </c>
       <c r="B170" s="4">
         <v>14</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="F170" s="7">
-        <v>14.74</v>
+        <v>39.71</v>
       </c>
       <c r="G170" s="7">
-        <v>251</v>
+        <v>1234</v>
       </c>
       <c r="H170" s="7">
-        <v>40</v>
+        <v>49.48</v>
       </c>
       <c r="I170" s="7">
-        <v>40</v>
-      </c>
-      <c r="J170" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K170" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L170" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M170" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="J170" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K170" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L170" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M170" s="7" t="s">
         <v>13</v>
       </c>
       <c r="N170" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="171" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A171" s="6" t="s">
-        <v>410</v>
+        <v>845</v>
       </c>
       <c r="B171" s="4">
         <v>14</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="D171" s="5" t="s">
         <v>411</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="F171" s="7">
-        <v>12.63</v>
+        <v>47.37</v>
       </c>
       <c r="G171" s="7">
-        <v>966</v>
+        <v>95</v>
       </c>
       <c r="H171" s="7">
-        <v>32</v>
+        <v>60.61</v>
       </c>
       <c r="I171" s="7">
-        <v>172</v>
-      </c>
-      <c r="J171" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K171" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L171" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M171" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J171" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K171" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L171" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M171" s="8" t="s">
         <v>13</v>
       </c>
       <c r="N171" s="5" t="s">
@@ -10921,163 +10962,163 @@
     </row>
     <row r="172" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A172" s="6" t="s">
+        <v>846</v>
+      </c>
+      <c r="B172" s="4">
+        <v>14</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="E172" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F172" s="7">
+        <v>31</v>
+      </c>
+      <c r="G172" s="7">
+        <v>687</v>
+      </c>
+      <c r="H172" s="7">
+        <v>50.75</v>
+      </c>
+      <c r="I172" s="7">
+        <v>199</v>
+      </c>
+      <c r="J172" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K172" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L172" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M172" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N172" s="5" t="s">
         <v>414</v>
-      </c>
-      <c r="B172" s="4">
-        <v>14</v>
-      </c>
-      <c r="C172" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D172" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="E172" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="F172" s="7">
-        <v>39.71</v>
-      </c>
-      <c r="G172" s="7">
-        <v>1234</v>
-      </c>
-      <c r="H172" s="7">
-        <v>49.48</v>
-      </c>
-      <c r="I172" s="7">
-        <v>388</v>
-      </c>
-      <c r="J172" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K172" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L172" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M172" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="N172" s="5" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="173" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A173" s="6" t="s">
+        <v>847</v>
+      </c>
+      <c r="B173" s="4">
+        <v>14</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="D173" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="E173" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F173" s="7">
+        <v>19.57</v>
+      </c>
+      <c r="G173" s="7">
+        <v>690</v>
+      </c>
+      <c r="H173" s="7">
+        <v>45.83</v>
+      </c>
+      <c r="I173" s="7">
+        <v>120</v>
+      </c>
+      <c r="J173" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K173" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L173" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M173" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N173" s="5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A174" s="6" t="s">
+        <v>848</v>
+      </c>
+      <c r="B174" s="4">
+        <v>14</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="D174" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="B173" s="4">
-        <v>14</v>
-      </c>
-      <c r="C173" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D173" s="5" t="s">
+      <c r="E174" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F174" s="7">
+        <v>27.55</v>
+      </c>
+      <c r="G174" s="7">
+        <v>421</v>
+      </c>
+      <c r="H174" s="7">
+        <v>44.7</v>
+      </c>
+      <c r="I174" s="7">
+        <v>132</v>
+      </c>
+      <c r="J174" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K174" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L174" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M174" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N174" s="5" t="s">
         <v>418</v>
-      </c>
-      <c r="E173" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F173" s="7">
-        <v>47.37</v>
-      </c>
-      <c r="G173" s="7">
-        <v>95</v>
-      </c>
-      <c r="H173" s="7">
-        <v>60.61</v>
-      </c>
-      <c r="I173" s="7">
-        <v>33</v>
-      </c>
-      <c r="J173" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K173" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L173" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M173" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="N173" s="5" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="174" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="6" t="s">
-        <v>420</v>
-      </c>
-      <c r="B174" s="4">
-        <v>14</v>
-      </c>
-      <c r="C174" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D174" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="E174" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F174" s="7">
-        <v>31</v>
-      </c>
-      <c r="G174" s="7">
-        <v>687</v>
-      </c>
-      <c r="H174" s="7">
-        <v>50.75</v>
-      </c>
-      <c r="I174" s="7">
-        <v>199</v>
-      </c>
-      <c r="J174" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K174" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L174" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M174" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="N174" s="5" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="175" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A175" s="6" t="s">
-        <v>423</v>
+        <v>849</v>
       </c>
       <c r="B175" s="4">
         <v>14</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E175" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F175" s="7">
-        <v>19.57</v>
+        <v>29.35</v>
       </c>
       <c r="G175" s="7">
-        <v>690</v>
+        <v>460</v>
       </c>
       <c r="H175" s="7">
-        <v>45.83</v>
+        <v>37.5</v>
       </c>
       <c r="I175" s="7">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="J175" s="8" t="s">
         <v>13</v>
@@ -11092,36 +11133,36 @@
         <v>13</v>
       </c>
       <c r="N175" s="5" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="176" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
-        <v>426</v>
+        <v>850</v>
       </c>
       <c r="B176" s="4">
         <v>14</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="E176" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F176" s="7">
-        <v>27.55</v>
+        <v>16.48</v>
       </c>
       <c r="G176" s="7">
-        <v>421</v>
+        <v>5079</v>
       </c>
       <c r="H176" s="7">
-        <v>44.7</v>
+        <v>19.57</v>
       </c>
       <c r="I176" s="7">
-        <v>132</v>
+        <v>511</v>
       </c>
       <c r="J176" s="8" t="s">
         <v>13</v>
@@ -11136,36 +11177,36 @@
         <v>13</v>
       </c>
       <c r="N176" s="5" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="177" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A177" s="6" t="s">
-        <v>429</v>
+        <v>851</v>
       </c>
       <c r="B177" s="4">
         <v>14</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="E177" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F177" s="7">
-        <v>29.35</v>
+        <v>9.06</v>
       </c>
       <c r="G177" s="7">
-        <v>460</v>
+        <v>265</v>
       </c>
       <c r="H177" s="7">
-        <v>37.5</v>
+        <v>24</v>
       </c>
       <c r="I177" s="7">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="J177" s="8" t="s">
         <v>13</v>
@@ -11180,80 +11221,80 @@
         <v>13</v>
       </c>
       <c r="N177" s="5" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
     </row>
     <row r="178" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A178" s="6" t="s">
-        <v>433</v>
+        <v>852</v>
       </c>
       <c r="B178" s="4">
         <v>14</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="F178" s="7">
-        <v>16.48</v>
+        <v>32.04</v>
       </c>
       <c r="G178" s="7">
-        <v>5079</v>
+        <v>181</v>
       </c>
       <c r="H178" s="7">
-        <v>19.57</v>
+        <v>57.14</v>
       </c>
       <c r="I178" s="7">
-        <v>511</v>
-      </c>
-      <c r="J178" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K178" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L178" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M178" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J178" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K178" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L178" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M178" s="7" t="s">
         <v>13</v>
       </c>
       <c r="N178" s="5" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
     </row>
     <row r="179" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A179" s="6" t="s">
-        <v>436</v>
+        <v>853</v>
       </c>
       <c r="B179" s="4">
         <v>14</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="E179" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F179" s="7">
-        <v>9.06</v>
+        <v>0.77</v>
       </c>
       <c r="G179" s="7">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="H179" s="7">
-        <v>24</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I179" s="7">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="J179" s="8" t="s">
         <v>13</v>
@@ -11268,168 +11309,168 @@
         <v>13</v>
       </c>
       <c r="N179" s="5" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
     </row>
     <row r="180" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A180" s="6" t="s">
-        <v>439</v>
+        <v>854</v>
       </c>
       <c r="B180" s="4">
         <v>14</v>
       </c>
       <c r="C180" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="D180" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="E180" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F180" s="7">
+        <v>22.91</v>
+      </c>
+      <c r="G180" s="7">
+        <v>227</v>
+      </c>
+      <c r="H180" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I180" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J180" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K180" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L180" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M180" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N180" s="5" t="s">
         <v>432</v>
-      </c>
-      <c r="D180" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="E180" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="F180" s="7">
-        <v>32.04</v>
-      </c>
-      <c r="G180" s="7">
-        <v>181</v>
-      </c>
-      <c r="H180" s="7">
-        <v>57.14</v>
-      </c>
-      <c r="I180" s="7">
-        <v>42</v>
-      </c>
-      <c r="J180" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K180" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L180" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M180" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="N180" s="5" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="181" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A181" s="6" t="s">
-        <v>443</v>
+        <v>855</v>
       </c>
       <c r="B181" s="4">
         <v>14</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="F181" s="7">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="G181" s="7">
-        <v>260</v>
+        <v>447</v>
       </c>
       <c r="H181" s="7">
-        <v>1.1000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I181" s="7">
-        <v>91</v>
-      </c>
-      <c r="J181" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K181" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L181" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M181" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="J181" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K181" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L181" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M181" s="7" t="s">
         <v>13</v>
       </c>
       <c r="N181" s="5" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
     </row>
     <row r="182" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A182" s="6" t="s">
-        <v>446</v>
+        <v>856</v>
       </c>
       <c r="B182" s="4">
         <v>14</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="F182" s="7">
-        <v>22.91</v>
+        <v>22.12</v>
       </c>
       <c r="G182" s="7">
-        <v>227</v>
-      </c>
-      <c r="H182" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="I182" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J182" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K182" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L182" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M182" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="H182" s="7">
+        <v>37.18</v>
+      </c>
+      <c r="I182" s="7">
+        <v>234</v>
+      </c>
+      <c r="J182" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K182" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L182" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M182" s="7" t="s">
         <v>13</v>
       </c>
       <c r="N182" s="5" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
     <row r="183" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A183" s="6" t="s">
-        <v>450</v>
+        <v>857</v>
       </c>
       <c r="B183" s="4">
         <v>14</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="F183" s="7">
-        <v>0</v>
+        <v>12.67</v>
       </c>
       <c r="G183" s="7">
-        <v>447</v>
+        <v>292</v>
       </c>
       <c r="H183" s="7">
-        <v>0</v>
+        <v>13.89</v>
       </c>
       <c r="I183" s="7">
-        <v>253</v>
+        <v>180</v>
       </c>
       <c r="J183" s="7" t="s">
         <v>13</v>
@@ -11444,86 +11485,86 @@
         <v>13</v>
       </c>
       <c r="N183" s="5" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
     </row>
     <row r="184" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
-        <v>454</v>
+        <v>858</v>
       </c>
       <c r="B184" s="4">
         <v>14</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="F184" s="7">
-        <v>22.12</v>
+        <v>25</v>
       </c>
       <c r="G184" s="7">
-        <v>547</v>
-      </c>
-      <c r="H184" s="7">
-        <v>37.18</v>
-      </c>
-      <c r="I184" s="7">
-        <v>234</v>
-      </c>
-      <c r="J184" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K184" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L184" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M184" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H184" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I184" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J184" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K184" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L184" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M184" s="8" t="s">
         <v>13</v>
       </c>
       <c r="N184" s="5" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
     </row>
     <row r="185" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
-        <v>457</v>
+        <v>859</v>
       </c>
       <c r="B185" s="4">
         <v>14</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="F185" s="7">
-        <v>12.67</v>
+        <v>13.68</v>
       </c>
       <c r="G185" s="7">
-        <v>292</v>
+        <v>117</v>
       </c>
       <c r="H185" s="7">
-        <v>13.89</v>
+        <v>18.329999999999998</v>
       </c>
       <c r="I185" s="7">
-        <v>180</v>
-      </c>
-      <c r="J185" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K185" s="7" t="s">
-        <v>13</v>
+        <v>60</v>
+      </c>
+      <c r="J185" s="7">
+        <v>23.93</v>
+      </c>
+      <c r="K185" s="7">
+        <v>117</v>
       </c>
       <c r="L185" s="7" t="s">
         <v>13</v>
@@ -11532,209 +11573,209 @@
         <v>13</v>
       </c>
       <c r="N185" s="5" t="s">
-        <v>459</v>
+        <v>445</v>
       </c>
     </row>
     <row r="186" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
-        <v>460</v>
+        <v>860</v>
       </c>
       <c r="B186" s="4">
         <v>14</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>17</v>
+        <v>448</v>
       </c>
       <c r="F186" s="7">
-        <v>25</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="G186" s="7">
-        <v>56</v>
-      </c>
-      <c r="H186" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="I186" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J186" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K186" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L186" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M186" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="H186" s="7">
+        <v>0</v>
+      </c>
+      <c r="I186" s="7">
+        <v>38</v>
+      </c>
+      <c r="J186" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K186" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L186" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M186" s="7" t="s">
         <v>13</v>
       </c>
       <c r="N186" s="5" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A187" s="6" t="s">
-        <v>464</v>
+        <v>861</v>
       </c>
       <c r="B187" s="4">
         <v>14</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>463</v>
+        <v>446</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>47</v>
+        <v>451</v>
       </c>
       <c r="F187" s="7">
-        <v>13.68</v>
+        <v>19.71</v>
       </c>
       <c r="G187" s="7">
-        <v>117</v>
+        <v>421</v>
       </c>
       <c r="H187" s="7">
-        <v>18.329999999999998</v>
+        <v>18.88</v>
       </c>
       <c r="I187" s="7">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="J187" s="7">
-        <v>23.93</v>
+        <v>33.33</v>
       </c>
       <c r="K187" s="7">
-        <v>117</v>
-      </c>
-      <c r="L187" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M187" s="7" t="s">
-        <v>13</v>
+        <v>288</v>
+      </c>
+      <c r="L187" s="7">
+        <v>48.98</v>
+      </c>
+      <c r="M187" s="7">
+        <v>98</v>
       </c>
       <c r="N187" s="5" t="s">
-        <v>466</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A188" s="6" t="s">
-        <v>468</v>
+        <v>862</v>
       </c>
       <c r="B188" s="4">
         <v>14</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="F188" s="7">
-        <v>1.1000000000000001</v>
+        <v>0</v>
       </c>
       <c r="G188" s="7">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="H188" s="7">
         <v>0</v>
       </c>
       <c r="I188" s="7">
-        <v>38</v>
-      </c>
-      <c r="J188" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K188" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L188" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M188" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J188" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K188" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L188" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M188" s="8" t="s">
         <v>13</v>
       </c>
       <c r="N188" s="5" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
     </row>
     <row r="189" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A189" s="6" t="s">
-        <v>472</v>
+        <v>863</v>
       </c>
       <c r="B189" s="4">
         <v>14</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>474</v>
+        <v>448</v>
       </c>
       <c r="F189" s="7">
-        <v>19.71</v>
+        <v>17.440000000000001</v>
       </c>
       <c r="G189" s="7">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="H189" s="7">
-        <v>18.88</v>
+        <v>34.119999999999997</v>
       </c>
       <c r="I189" s="7">
-        <v>143</v>
-      </c>
-      <c r="J189" s="7">
-        <v>33.33</v>
-      </c>
-      <c r="K189" s="7">
-        <v>288</v>
-      </c>
-      <c r="L189" s="7">
-        <v>48.98</v>
-      </c>
-      <c r="M189" s="7">
-        <v>98</v>
+        <v>85</v>
+      </c>
+      <c r="J189" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K189" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L189" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M189" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="N189" s="5" t="s">
-        <v>475</v>
+        <v>458</v>
       </c>
     </row>
     <row r="190" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A190" s="6" t="s">
-        <v>477</v>
+        <v>864</v>
       </c>
       <c r="B190" s="4">
         <v>14</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="E190" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F190" s="7">
-        <v>0</v>
+        <v>55.1</v>
       </c>
       <c r="G190" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H190" s="7">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="I190" s="7">
         <v>25</v>
@@ -11752,36 +11793,36 @@
         <v>13</v>
       </c>
       <c r="N190" s="5" t="s">
-        <v>479</v>
+        <v>461</v>
       </c>
     </row>
     <row r="191" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A191" s="6" t="s">
-        <v>481</v>
+        <v>865</v>
       </c>
       <c r="B191" s="4">
         <v>14</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>482</v>
+        <v>463</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="F191" s="7">
-        <v>17.440000000000001</v>
-      </c>
-      <c r="G191" s="7">
-        <v>367</v>
+        <v>12</v>
+      </c>
+      <c r="F191" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G191" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="H191" s="7">
-        <v>34.119999999999997</v>
+        <v>37.29</v>
       </c>
       <c r="I191" s="7">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="J191" s="7" t="s">
         <v>13</v>
@@ -11789,219 +11830,219 @@
       <c r="K191" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="L191" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M191" s="7" t="s">
-        <v>13</v>
+      <c r="L191" s="7">
+        <v>40.68</v>
+      </c>
+      <c r="M191" s="7">
+        <v>59</v>
       </c>
       <c r="N191" s="5" t="s">
-        <v>483</v>
+        <v>464</v>
       </c>
     </row>
     <row r="192" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A192" s="6" t="s">
-        <v>485</v>
+        <v>866</v>
       </c>
       <c r="B192" s="4">
         <v>14</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>486</v>
+        <v>466</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F192" s="7">
-        <v>55.1</v>
+        <v>6.48</v>
       </c>
       <c r="G192" s="7">
-        <v>49</v>
+        <v>247</v>
       </c>
       <c r="H192" s="7">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="I192" s="7">
+        <v>100</v>
+      </c>
+      <c r="J192" s="7">
+        <v>13.77</v>
+      </c>
+      <c r="K192" s="7">
+        <v>247</v>
+      </c>
+      <c r="L192" s="7">
         <v>25</v>
       </c>
-      <c r="J192" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K192" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L192" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M192" s="8" t="s">
-        <v>13</v>
+      <c r="M192" s="7">
+        <v>100</v>
       </c>
       <c r="N192" s="5" t="s">
-        <v>487</v>
+        <v>467</v>
       </c>
     </row>
     <row r="193" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A193" s="6" t="s">
-        <v>489</v>
+        <v>867</v>
       </c>
       <c r="B193" s="4">
         <v>14</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>488</v>
+        <v>465</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>490</v>
+        <v>468</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F193" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G193" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F193" s="7">
+        <v>12.2</v>
+      </c>
+      <c r="G193" s="7">
+        <v>533</v>
       </c>
       <c r="H193" s="7">
-        <v>37.29</v>
+        <v>36.24</v>
       </c>
       <c r="I193" s="7">
-        <v>59</v>
-      </c>
-      <c r="J193" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K193" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L193" s="7">
-        <v>40.68</v>
-      </c>
-      <c r="M193" s="7">
-        <v>59</v>
+        <v>149</v>
+      </c>
+      <c r="J193" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K193" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L193" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M193" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="N193" s="5" t="s">
-        <v>491</v>
+        <v>469</v>
       </c>
     </row>
     <row r="194" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A194" s="6" t="s">
-        <v>493</v>
+        <v>868</v>
       </c>
       <c r="B194" s="4">
         <v>14</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>492</v>
+        <v>465</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>494</v>
+        <v>470</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>47</v>
+        <v>160</v>
       </c>
       <c r="F194" s="7">
-        <v>6.48</v>
+        <v>9.09</v>
       </c>
       <c r="G194" s="7">
-        <v>247</v>
+        <v>154</v>
       </c>
       <c r="H194" s="7">
-        <v>9</v>
+        <v>30.56</v>
       </c>
       <c r="I194" s="7">
-        <v>100</v>
-      </c>
-      <c r="J194" s="7">
-        <v>13.77</v>
-      </c>
-      <c r="K194" s="7">
-        <v>247</v>
-      </c>
-      <c r="L194" s="7">
-        <v>25</v>
-      </c>
-      <c r="M194" s="7">
-        <v>100</v>
+        <v>36</v>
+      </c>
+      <c r="J194" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K194" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L194" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M194" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="N194" s="5" t="s">
-        <v>495</v>
+        <v>471</v>
       </c>
     </row>
     <row r="195" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A195" s="6" t="s">
-        <v>496</v>
+        <v>869</v>
       </c>
       <c r="B195" s="4">
         <v>14</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>492</v>
+        <v>472</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>497</v>
+        <v>473</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="F195" s="7">
-        <v>12.2</v>
+        <v>4.99</v>
       </c>
       <c r="G195" s="7">
-        <v>533</v>
+        <v>841</v>
       </c>
       <c r="H195" s="7">
-        <v>36.24</v>
+        <v>7.19</v>
       </c>
       <c r="I195" s="7">
-        <v>149</v>
-      </c>
-      <c r="J195" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K195" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L195" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M195" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="J195" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K195" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L195" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M195" s="7" t="s">
         <v>13</v>
       </c>
       <c r="N195" s="5" t="s">
-        <v>498</v>
+        <v>474</v>
       </c>
     </row>
     <row r="196" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A196" s="6" t="s">
-        <v>499</v>
+        <v>870</v>
       </c>
       <c r="B196" s="4">
         <v>14</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>492</v>
+        <v>472</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="E196" s="5" t="s">
         <v>160</v>
       </c>
       <c r="F196" s="7">
-        <v>9.09</v>
+        <v>6.43</v>
       </c>
       <c r="G196" s="7">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="H196" s="7">
-        <v>30.56</v>
+        <v>13.51</v>
       </c>
       <c r="I196" s="7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J196" s="7" t="s">
         <v>13</v>
@@ -12016,212 +12057,212 @@
         <v>13</v>
       </c>
       <c r="N196" s="5" t="s">
-        <v>501</v>
+        <v>476</v>
       </c>
     </row>
     <row r="197" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A197" s="6" t="s">
-        <v>503</v>
+        <v>871</v>
       </c>
       <c r="B197" s="4">
         <v>14</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>502</v>
+        <v>472</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>504</v>
+        <v>477</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="F197" s="7">
-        <v>4.99</v>
+        <v>27.27</v>
       </c>
       <c r="G197" s="7">
-        <v>841</v>
+        <v>44</v>
       </c>
       <c r="H197" s="7">
-        <v>7.19</v>
+        <v>38.89</v>
       </c>
       <c r="I197" s="7">
-        <v>320</v>
-      </c>
-      <c r="J197" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K197" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L197" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M197" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J197" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K197" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L197" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M197" s="8" t="s">
         <v>13</v>
       </c>
       <c r="N197" s="5" t="s">
-        <v>505</v>
+        <v>478</v>
       </c>
     </row>
     <row r="198" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A198" s="6" t="s">
-        <v>506</v>
+        <v>872</v>
       </c>
       <c r="B198" s="4">
         <v>14</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>502</v>
+        <v>472</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>507</v>
+        <v>479</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="F198" s="7">
-        <v>6.43</v>
+        <v>38.54</v>
       </c>
       <c r="G198" s="7">
-        <v>140</v>
+        <v>410</v>
       </c>
       <c r="H198" s="7">
-        <v>13.51</v>
+        <v>70.97</v>
       </c>
       <c r="I198" s="7">
-        <v>37</v>
-      </c>
-      <c r="J198" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K198" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L198" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M198" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="J198" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K198" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L198" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M198" s="8" t="s">
         <v>13</v>
       </c>
       <c r="N198" s="5" t="s">
-        <v>508</v>
+        <v>480</v>
       </c>
     </row>
     <row r="199" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A199" s="6" t="s">
-        <v>509</v>
+        <v>873</v>
       </c>
       <c r="B199" s="4">
         <v>14</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>502</v>
+        <v>472</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>510</v>
+        <v>481</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="F199" s="7">
-        <v>27.27</v>
+        <v>3.05</v>
       </c>
       <c r="G199" s="7">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="H199" s="7">
-        <v>38.89</v>
+        <v>9.09</v>
       </c>
       <c r="I199" s="7">
-        <v>18</v>
-      </c>
-      <c r="J199" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K199" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L199" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M199" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J199" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K199" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L199" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M199" s="7" t="s">
         <v>13</v>
       </c>
       <c r="N199" s="5" t="s">
-        <v>511</v>
+        <v>482</v>
       </c>
     </row>
     <row r="200" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A200" s="6" t="s">
-        <v>512</v>
+        <v>874</v>
       </c>
       <c r="B200" s="4">
         <v>14</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>502</v>
+        <v>472</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>513</v>
+        <v>483</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="F200" s="7">
-        <v>38.54</v>
+        <v>8.11</v>
       </c>
       <c r="G200" s="7">
-        <v>410</v>
+        <v>604</v>
       </c>
       <c r="H200" s="7">
-        <v>70.97</v>
+        <v>20.51</v>
       </c>
       <c r="I200" s="7">
-        <v>93</v>
-      </c>
-      <c r="J200" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K200" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L200" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M200" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J200" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K200" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L200" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M200" s="7" t="s">
         <v>13</v>
       </c>
       <c r="N200" s="5" t="s">
-        <v>514</v>
+        <v>484</v>
       </c>
     </row>
     <row r="201" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
-        <v>515</v>
+        <v>875</v>
       </c>
       <c r="B201" s="4">
         <v>14</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>502</v>
+        <v>472</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>516</v>
+        <v>485</v>
       </c>
       <c r="E201" s="5" t="s">
         <v>160</v>
       </c>
       <c r="F201" s="7">
-        <v>3.05</v>
+        <v>5.26</v>
       </c>
       <c r="G201" s="7">
-        <v>131</v>
+        <v>57</v>
       </c>
       <c r="H201" s="7">
-        <v>9.09</v>
+        <v>18.75</v>
       </c>
       <c r="I201" s="7">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="J201" s="7" t="s">
         <v>13</v>
@@ -12236,36 +12277,36 @@
         <v>13</v>
       </c>
       <c r="N201" s="5" t="s">
-        <v>517</v>
+        <v>486</v>
       </c>
     </row>
     <row r="202" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A202" s="6" t="s">
-        <v>518</v>
+        <v>876</v>
       </c>
       <c r="B202" s="4">
         <v>14</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>502</v>
+        <v>472</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>519</v>
+        <v>487</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="F202" s="7">
-        <v>8.11</v>
+        <v>29.51</v>
       </c>
       <c r="G202" s="7">
-        <v>604</v>
+        <v>122</v>
       </c>
       <c r="H202" s="7">
-        <v>20.51</v>
+        <v>35.369999999999997</v>
       </c>
       <c r="I202" s="7">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="J202" s="7" t="s">
         <v>13</v>
@@ -12280,36 +12321,36 @@
         <v>13</v>
       </c>
       <c r="N202" s="5" t="s">
-        <v>520</v>
+        <v>488</v>
       </c>
     </row>
     <row r="203" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A203" s="6" t="s">
-        <v>521</v>
+        <v>877</v>
       </c>
       <c r="B203" s="4">
         <v>14</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>502</v>
+        <v>472</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>160</v>
+        <v>448</v>
       </c>
       <c r="F203" s="7">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="G203" s="7">
-        <v>57</v>
-      </c>
-      <c r="H203" s="7">
-        <v>18.75</v>
-      </c>
-      <c r="I203" s="7">
-        <v>16</v>
+        <v>23</v>
+      </c>
+      <c r="H203" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I203" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="J203" s="7" t="s">
         <v>13</v>
@@ -12324,80 +12365,80 @@
         <v>13</v>
       </c>
       <c r="N203" s="5" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
     </row>
     <row r="204" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A204" s="6" t="s">
-        <v>524</v>
+        <v>878</v>
       </c>
       <c r="B204" s="4">
         <v>14</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>502</v>
+        <v>472</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>525</v>
+        <v>491</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>223</v>
+        <v>17</v>
       </c>
       <c r="F204" s="7">
-        <v>29.51</v>
+        <v>3.83</v>
       </c>
       <c r="G204" s="7">
-        <v>122</v>
+        <v>392</v>
       </c>
       <c r="H204" s="7">
-        <v>35.369999999999997</v>
+        <v>5.88</v>
       </c>
       <c r="I204" s="7">
-        <v>82</v>
-      </c>
-      <c r="J204" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K204" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L204" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M204" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="J204" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K204" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L204" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M204" s="8" t="s">
         <v>13</v>
       </c>
       <c r="N204" s="5" t="s">
-        <v>526</v>
+        <v>492</v>
       </c>
     </row>
     <row r="205" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A205" s="6" t="s">
-        <v>527</v>
+        <v>879</v>
       </c>
       <c r="B205" s="4">
         <v>14</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>502</v>
+        <v>472</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>528</v>
+        <v>493</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>470</v>
+        <v>160</v>
       </c>
       <c r="F205" s="7">
-        <v>0</v>
+        <v>45.13</v>
       </c>
       <c r="G205" s="7">
-        <v>23</v>
-      </c>
-      <c r="H205" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="I205" s="7" t="s">
-        <v>13</v>
+        <v>195</v>
+      </c>
+      <c r="H205" s="7">
+        <v>59.26</v>
+      </c>
+      <c r="I205" s="7">
+        <v>27</v>
       </c>
       <c r="J205" s="7" t="s">
         <v>13</v>
@@ -12412,80 +12453,80 @@
         <v>13</v>
       </c>
       <c r="N205" s="5" t="s">
-        <v>529</v>
+        <v>494</v>
       </c>
     </row>
     <row r="206" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
-        <v>530</v>
+        <v>880</v>
       </c>
       <c r="B206" s="4">
         <v>14</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>502</v>
+        <v>472</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>531</v>
+        <v>495</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="F206" s="7">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="G206" s="7">
-        <v>392</v>
+        <v>56</v>
       </c>
       <c r="H206" s="7">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="I206" s="7">
-        <v>102</v>
-      </c>
-      <c r="J206" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K206" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L206" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M206" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J206" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K206" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L206" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M206" s="7" t="s">
         <v>13</v>
       </c>
       <c r="N206" s="5" t="s">
-        <v>532</v>
+        <v>496</v>
       </c>
     </row>
     <row r="207" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A207" s="6" t="s">
-        <v>533</v>
+        <v>881</v>
       </c>
       <c r="B207" s="4">
         <v>14</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>502</v>
+        <v>472</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>534</v>
+        <v>497</v>
       </c>
       <c r="E207" s="5" t="s">
         <v>160</v>
       </c>
       <c r="F207" s="7">
-        <v>45.13</v>
+        <v>19.829999999999998</v>
       </c>
       <c r="G207" s="7">
-        <v>195</v>
+        <v>474</v>
       </c>
       <c r="H207" s="7">
-        <v>59.26</v>
+        <v>37.5</v>
       </c>
       <c r="I207" s="7">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="J207" s="7" t="s">
         <v>13</v>
@@ -12500,124 +12541,124 @@
         <v>13</v>
       </c>
       <c r="N207" s="5" t="s">
-        <v>535</v>
+        <v>498</v>
       </c>
     </row>
     <row r="208" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A208" s="6" t="s">
-        <v>536</v>
+        <v>882</v>
       </c>
       <c r="B208" s="4">
         <v>14</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>537</v>
+        <v>500</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="F208" s="7">
         <v>0</v>
       </c>
       <c r="G208" s="7">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="H208" s="7">
         <v>0</v>
       </c>
       <c r="I208" s="7">
-        <v>13</v>
-      </c>
-      <c r="J208" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K208" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L208" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M208" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J208" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K208" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L208" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M208" s="8" t="s">
         <v>13</v>
       </c>
       <c r="N208" s="5" t="s">
-        <v>538</v>
+        <v>501</v>
       </c>
     </row>
     <row r="209" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A209" s="6" t="s">
-        <v>539</v>
+        <v>883</v>
       </c>
       <c r="B209" s="4">
         <v>14</v>
       </c>
       <c r="C209" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="D209" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="D209" s="5" t="s">
-        <v>540</v>
-      </c>
       <c r="E209" s="5" t="s">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="F209" s="7">
-        <v>19.829999999999998</v>
+        <v>3.37</v>
       </c>
       <c r="G209" s="7">
-        <v>474</v>
+        <v>89</v>
       </c>
       <c r="H209" s="7">
-        <v>37.5</v>
+        <v>4</v>
       </c>
       <c r="I209" s="7">
-        <v>80</v>
-      </c>
-      <c r="J209" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K209" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L209" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M209" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J209" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K209" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L209" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M209" s="8" t="s">
         <v>13</v>
       </c>
       <c r="N209" s="5" t="s">
-        <v>541</v>
+        <v>503</v>
       </c>
     </row>
     <row r="210" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A210" s="6" t="s">
-        <v>543</v>
+        <v>884</v>
       </c>
       <c r="B210" s="4">
         <v>14</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>542</v>
+        <v>504</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>544</v>
+        <v>505</v>
       </c>
       <c r="E210" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F210" s="7">
-        <v>0</v>
+        <v>41.46</v>
       </c>
       <c r="G210" s="7">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="H210" s="7">
-        <v>0</v>
+        <v>52.63</v>
       </c>
       <c r="I210" s="7">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J210" s="8" t="s">
         <v>13</v>
@@ -12632,36 +12673,36 @@
         <v>13</v>
       </c>
       <c r="N210" s="5" t="s">
-        <v>545</v>
+        <v>506</v>
       </c>
     </row>
     <row r="211" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A211" s="6" t="s">
-        <v>546</v>
+        <v>885</v>
       </c>
       <c r="B211" s="4">
         <v>14</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>542</v>
+        <v>504</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>547</v>
+        <v>507</v>
       </c>
       <c r="E211" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F211" s="7">
-        <v>3.37</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="G211" s="7">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="H211" s="7">
-        <v>4</v>
+        <v>29.41</v>
       </c>
       <c r="I211" s="7">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="J211" s="8" t="s">
         <v>13</v>
@@ -12676,36 +12717,36 @@
         <v>13</v>
       </c>
       <c r="N211" s="5" t="s">
-        <v>548</v>
+        <v>508</v>
       </c>
     </row>
     <row r="212" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A212" s="6" t="s">
-        <v>550</v>
+        <v>886</v>
       </c>
       <c r="B212" s="4">
         <v>14</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>549</v>
+        <v>504</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>551</v>
+        <v>509</v>
       </c>
       <c r="E212" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F212" s="7">
-        <v>41.46</v>
+        <v>49.09</v>
       </c>
       <c r="G212" s="7">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="H212" s="7">
-        <v>52.63</v>
+        <v>54.84</v>
       </c>
       <c r="I212" s="7">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J212" s="8" t="s">
         <v>13</v>
@@ -12720,118 +12761,118 @@
         <v>13</v>
       </c>
       <c r="N212" s="5" t="s">
-        <v>552</v>
+        <v>510</v>
       </c>
     </row>
     <row r="213" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A213" s="6" t="s">
-        <v>553</v>
+        <v>887</v>
       </c>
       <c r="B213" s="4">
         <v>14</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>549</v>
+        <v>511</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>554</v>
+        <v>512</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F213" s="7">
-        <v>16.670000000000002</v>
+        <v>0</v>
       </c>
       <c r="G213" s="7">
-        <v>54</v>
-      </c>
-      <c r="H213" s="7">
-        <v>29.41</v>
-      </c>
-      <c r="I213" s="7">
-        <v>17</v>
-      </c>
-      <c r="J213" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K213" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L213" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M213" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="H213" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I213" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J213" s="7">
+        <v>4.83</v>
+      </c>
+      <c r="K213" s="7">
+        <v>145</v>
+      </c>
+      <c r="L213" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M213" s="7" t="s">
         <v>13</v>
       </c>
       <c r="N213" s="5" t="s">
-        <v>555</v>
+        <v>513</v>
       </c>
     </row>
     <row r="214" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A214" s="6" t="s">
-        <v>556</v>
+        <v>888</v>
       </c>
       <c r="B214" s="4">
         <v>14</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>549</v>
+        <v>511</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>557</v>
+        <v>514</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F214" s="7">
-        <v>49.09</v>
+        <v>0</v>
       </c>
       <c r="G214" s="7">
-        <v>55</v>
+        <v>186</v>
       </c>
       <c r="H214" s="7">
-        <v>54.84</v>
+        <v>0</v>
       </c>
       <c r="I214" s="7">
-        <v>31</v>
-      </c>
-      <c r="J214" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K214" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L214" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M214" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J214" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K214" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L214" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M214" s="7" t="s">
         <v>13</v>
       </c>
       <c r="N214" s="5" t="s">
-        <v>558</v>
+        <v>515</v>
       </c>
     </row>
     <row r="215" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A215" s="6" t="s">
-        <v>560</v>
+        <v>889</v>
       </c>
       <c r="B215" s="4">
         <v>14</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>559</v>
+        <v>516</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>561</v>
+        <v>517</v>
       </c>
       <c r="E215" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F215" s="7">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="G215" s="7">
-        <v>145</v>
+        <v>222</v>
       </c>
       <c r="H215" s="7" t="s">
         <v>13</v>
@@ -12839,11 +12880,11 @@
       <c r="I215" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J215" s="7">
-        <v>4.83</v>
-      </c>
-      <c r="K215" s="7">
-        <v>145</v>
+      <c r="J215" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K215" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="L215" s="7" t="s">
         <v>13</v>
@@ -12852,36 +12893,36 @@
         <v>13</v>
       </c>
       <c r="N215" s="5" t="s">
-        <v>562</v>
+        <v>518</v>
       </c>
     </row>
     <row r="216" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A216" s="6" t="s">
-        <v>563</v>
+        <v>890</v>
       </c>
       <c r="B216" s="4">
         <v>14</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>559</v>
+        <v>516</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>564</v>
+        <v>519</v>
       </c>
       <c r="E216" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F216" s="7">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="G216" s="7">
-        <v>186</v>
+        <v>69</v>
       </c>
       <c r="H216" s="7">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="I216" s="7">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="J216" s="7" t="s">
         <v>13</v>
@@ -12896,124 +12937,124 @@
         <v>13</v>
       </c>
       <c r="N216" s="5" t="s">
-        <v>565</v>
+        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A217" s="6" t="s">
-        <v>567</v>
+        <v>891</v>
       </c>
       <c r="B217" s="4">
         <v>14</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>566</v>
+        <v>516</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>568</v>
+        <v>521</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F217" s="7">
-        <v>2.25</v>
+        <v>3.77</v>
       </c>
       <c r="G217" s="7">
-        <v>222</v>
-      </c>
-      <c r="H217" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="I217" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J217" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K217" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L217" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M217" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H217" s="7">
+        <v>3.23</v>
+      </c>
+      <c r="I217" s="7">
+        <v>31</v>
+      </c>
+      <c r="J217" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K217" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L217" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M217" s="8" t="s">
         <v>13</v>
       </c>
       <c r="N217" s="5" t="s">
-        <v>569</v>
+        <v>522</v>
       </c>
     </row>
     <row r="218" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A218" s="6" t="s">
-        <v>570</v>
+        <v>892</v>
       </c>
       <c r="B218" s="4">
         <v>14</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>566</v>
+        <v>516</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>571</v>
+        <v>523</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F218" s="7">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="G218" s="7">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="H218" s="7">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="I218" s="7">
-        <v>22</v>
-      </c>
-      <c r="J218" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K218" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L218" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M218" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J218" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K218" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L218" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M218" s="8" t="s">
         <v>13</v>
       </c>
       <c r="N218" s="5" t="s">
-        <v>572</v>
+        <v>524</v>
       </c>
     </row>
     <row r="219" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A219" s="6" t="s">
-        <v>573</v>
+        <v>893</v>
       </c>
       <c r="B219" s="4">
         <v>14</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>566</v>
+        <v>516</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>574</v>
+        <v>525</v>
       </c>
       <c r="E219" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F219" s="7">
-        <v>3.77</v>
+        <v>4.49</v>
       </c>
       <c r="G219" s="7">
-        <v>53</v>
+        <v>156</v>
       </c>
       <c r="H219" s="7">
-        <v>3.23</v>
+        <v>10</v>
       </c>
       <c r="I219" s="7">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="J219" s="8" t="s">
         <v>13</v>
@@ -13028,36 +13069,36 @@
         <v>13</v>
       </c>
       <c r="N219" s="5" t="s">
-        <v>575</v>
+        <v>526</v>
       </c>
     </row>
     <row r="220" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
-        <v>576</v>
+        <v>894</v>
       </c>
       <c r="B220" s="4">
         <v>14</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>566</v>
+        <v>516</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>577</v>
+        <v>527</v>
       </c>
       <c r="E220" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F220" s="7">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="G220" s="7">
-        <v>84</v>
+        <v>158</v>
       </c>
       <c r="H220" s="7">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="I220" s="7">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="J220" s="8" t="s">
         <v>13</v>
@@ -13072,36 +13113,36 @@
         <v>13</v>
       </c>
       <c r="N220" s="5" t="s">
-        <v>578</v>
+        <v>528</v>
       </c>
     </row>
     <row r="221" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A221" s="6" t="s">
-        <v>579</v>
+        <v>895</v>
       </c>
       <c r="B221" s="4">
         <v>14</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>566</v>
+        <v>516</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>580</v>
+        <v>529</v>
       </c>
       <c r="E221" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F221" s="7">
-        <v>4.49</v>
+        <v>15.05</v>
       </c>
       <c r="G221" s="7">
-        <v>156</v>
+        <v>4558</v>
       </c>
       <c r="H221" s="7">
-        <v>10</v>
+        <v>37.1</v>
       </c>
       <c r="I221" s="7">
-        <v>50</v>
+        <v>973</v>
       </c>
       <c r="J221" s="8" t="s">
         <v>13</v>
@@ -13116,80 +13157,80 @@
         <v>13</v>
       </c>
       <c r="N221" s="5" t="s">
-        <v>581</v>
+        <v>530</v>
       </c>
     </row>
     <row r="222" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A222" s="6" t="s">
-        <v>582</v>
+        <v>896</v>
       </c>
       <c r="B222" s="4">
         <v>14</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>566</v>
+        <v>531</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>583</v>
+        <v>532</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F222" s="7">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="G222" s="7">
-        <v>158</v>
+        <v>33</v>
       </c>
       <c r="H222" s="7">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="I222" s="7">
-        <v>51</v>
-      </c>
-      <c r="J222" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K222" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L222" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M222" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="J222" s="7">
+        <v>18.18</v>
+      </c>
+      <c r="K222" s="7">
+        <v>33</v>
+      </c>
+      <c r="L222" s="7">
+        <v>33.33</v>
+      </c>
+      <c r="M222" s="7">
+        <v>12</v>
       </c>
       <c r="N222" s="5" t="s">
-        <v>584</v>
+        <v>533</v>
       </c>
     </row>
     <row r="223" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A223" s="6" t="s">
-        <v>585</v>
+        <v>897</v>
       </c>
       <c r="B223" s="4">
         <v>14</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>566</v>
+        <v>531</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>586</v>
+        <v>534</v>
       </c>
       <c r="E223" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F223" s="7">
-        <v>15.05</v>
+        <v>5.96</v>
       </c>
       <c r="G223" s="7">
-        <v>4558</v>
+        <v>151</v>
       </c>
       <c r="H223" s="7">
-        <v>37.1</v>
+        <v>13.73</v>
       </c>
       <c r="I223" s="7">
-        <v>973</v>
+        <v>51</v>
       </c>
       <c r="J223" s="8" t="s">
         <v>13</v>
@@ -13204,80 +13245,80 @@
         <v>13</v>
       </c>
       <c r="N223" s="5" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="224" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A224" s="6" t="s">
-        <v>589</v>
-      </c>
-      <c r="B224" s="4">
-        <v>14</v>
-      </c>
-      <c r="C224" s="5" t="s">
-        <v>588</v>
-      </c>
-      <c r="D224" s="5" t="s">
-        <v>590</v>
-      </c>
-      <c r="E224" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F224" s="7">
-        <v>0</v>
-      </c>
-      <c r="G224" s="7">
-        <v>33</v>
-      </c>
-      <c r="H224" s="7">
-        <v>0</v>
-      </c>
-      <c r="I224" s="7">
-        <v>12</v>
-      </c>
-      <c r="J224" s="7">
-        <v>18.18</v>
-      </c>
-      <c r="K224" s="7">
-        <v>33</v>
-      </c>
-      <c r="L224" s="7">
-        <v>33.33</v>
-      </c>
-      <c r="M224" s="7">
-        <v>12</v>
-      </c>
-      <c r="N224" s="5" t="s">
-        <v>591</v>
+        <v>535</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A224" s="13" t="s">
+        <v>898</v>
+      </c>
+      <c r="B224" s="11">
+        <v>14</v>
+      </c>
+      <c r="C224" s="12" t="s">
+        <v>531</v>
+      </c>
+      <c r="D224" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="E224" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F224" s="14">
+        <v>26.46</v>
+      </c>
+      <c r="G224" s="14">
+        <v>2392</v>
+      </c>
+      <c r="H224" s="14">
+        <v>50.21</v>
+      </c>
+      <c r="I224" s="14">
+        <v>472</v>
+      </c>
+      <c r="J224" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K224" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="L224" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="M224" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="N224" s="10" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="225" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A225" s="6" t="s">
-        <v>592</v>
+        <v>899</v>
       </c>
       <c r="B225" s="4">
         <v>14</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>588</v>
+        <v>531</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>593</v>
+        <v>537</v>
       </c>
       <c r="E225" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F225" s="7">
-        <v>5.96</v>
+        <v>16.48</v>
       </c>
       <c r="G225" s="7">
-        <v>151</v>
+        <v>267</v>
       </c>
       <c r="H225" s="7">
-        <v>13.73</v>
+        <v>34.549999999999997</v>
       </c>
       <c r="I225" s="7">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J225" s="8" t="s">
         <v>13</v>
@@ -13292,98 +13333,124 @@
         <v>13</v>
       </c>
       <c r="N225" s="5" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A226" s="15" t="s">
-        <v>595</v>
-      </c>
-      <c r="B226" s="11">
-        <v>14</v>
-      </c>
-      <c r="C226" s="13" t="s">
-        <v>588</v>
-      </c>
-      <c r="D226" s="13" t="s">
-        <v>596</v>
-      </c>
-      <c r="E226" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F226" s="17">
-        <v>26.46</v>
-      </c>
-      <c r="G226" s="17">
-        <v>2392</v>
-      </c>
-      <c r="H226" s="17">
-        <v>50.21</v>
-      </c>
-      <c r="I226" s="17">
-        <v>472</v>
-      </c>
-      <c r="J226" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="K226" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="L226" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="M226" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="N226" s="10" t="s">
-        <v>13</v>
+        <v>538</v>
+      </c>
+    </row>
+    <row r="226" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A226" s="6" t="s">
+        <v>900</v>
+      </c>
+      <c r="B226" s="4">
+        <v>14</v>
+      </c>
+      <c r="C226" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="D226" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="E226" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F226" s="7">
+        <v>28.83</v>
+      </c>
+      <c r="G226" s="7">
+        <v>222</v>
+      </c>
+      <c r="H226" s="7">
+        <v>30.19</v>
+      </c>
+      <c r="I226" s="7">
+        <v>53</v>
+      </c>
+      <c r="J226" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K226" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L226" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M226" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N226" s="5" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="227" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="16"/>
-      <c r="B227" s="12"/>
-      <c r="C227" s="14"/>
-      <c r="D227" s="14"/>
-      <c r="E227" s="14"/>
-      <c r="F227" s="18"/>
-      <c r="G227" s="18"/>
-      <c r="H227" s="18"/>
-      <c r="I227" s="18"/>
-      <c r="J227" s="20"/>
-      <c r="K227" s="20"/>
-      <c r="L227" s="20"/>
-      <c r="M227" s="20"/>
+      <c r="A227" s="6" t="s">
+        <v>901</v>
+      </c>
+      <c r="B227" s="4">
+        <v>14</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="D227" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="E227" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F227" s="7">
+        <v>1.98</v>
+      </c>
+      <c r="G227" s="7">
+        <v>253</v>
+      </c>
+      <c r="H227" s="7">
+        <v>10.53</v>
+      </c>
+      <c r="I227" s="7">
+        <v>38</v>
+      </c>
+      <c r="J227" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K227" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L227" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M227" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="N227" s="5" t="s">
-        <v>597</v>
+        <v>542</v>
       </c>
     </row>
     <row r="228" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A228" s="6" t="s">
-        <v>598</v>
+        <v>902</v>
       </c>
       <c r="B228" s="4">
         <v>14</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>588</v>
+        <v>531</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>599</v>
+        <v>543</v>
       </c>
       <c r="E228" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F228" s="7">
-        <v>16.48</v>
+        <v>33.03</v>
       </c>
       <c r="G228" s="7">
-        <v>267</v>
+        <v>1635</v>
       </c>
       <c r="H228" s="7">
-        <v>34.549999999999997</v>
+        <v>65.05</v>
       </c>
       <c r="I228" s="7">
-        <v>55</v>
+        <v>329</v>
       </c>
       <c r="J228" s="8" t="s">
         <v>13</v>
@@ -13398,80 +13465,80 @@
         <v>13</v>
       </c>
       <c r="N228" s="5" t="s">
-        <v>600</v>
+        <v>544</v>
       </c>
     </row>
     <row r="229" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A229" s="6" t="s">
-        <v>601</v>
+        <v>903</v>
       </c>
       <c r="B229" s="4">
         <v>14</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>588</v>
+        <v>531</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>602</v>
+        <v>545</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F229" s="7">
-        <v>28.83</v>
+        <v>24.35</v>
       </c>
       <c r="G229" s="7">
-        <v>222</v>
+        <v>1577</v>
       </c>
       <c r="H229" s="7">
-        <v>30.19</v>
+        <v>49.35</v>
       </c>
       <c r="I229" s="7">
-        <v>53</v>
-      </c>
-      <c r="J229" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K229" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L229" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M229" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="J229" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K229" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L229" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M229" s="7" t="s">
         <v>13</v>
       </c>
       <c r="N229" s="5" t="s">
-        <v>603</v>
+        <v>546</v>
       </c>
     </row>
     <row r="230" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A230" s="6" t="s">
-        <v>604</v>
+        <v>904</v>
       </c>
       <c r="B230" s="4">
         <v>14</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>588</v>
+        <v>531</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>605</v>
+        <v>547</v>
       </c>
       <c r="E230" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F230" s="7">
-        <v>1.98</v>
+        <v>8.43</v>
       </c>
       <c r="G230" s="7">
-        <v>253</v>
+        <v>83</v>
       </c>
       <c r="H230" s="7">
-        <v>10.53</v>
+        <v>23.81</v>
       </c>
       <c r="I230" s="7">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="J230" s="8" t="s">
         <v>13</v>
@@ -13486,36 +13553,36 @@
         <v>13</v>
       </c>
       <c r="N230" s="5" t="s">
-        <v>606</v>
+        <v>548</v>
       </c>
     </row>
     <row r="231" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A231" s="6" t="s">
-        <v>607</v>
+        <v>905</v>
       </c>
       <c r="B231" s="4">
         <v>14</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>588</v>
+        <v>531</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>608</v>
+        <v>549</v>
       </c>
       <c r="E231" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F231" s="7">
-        <v>33.03</v>
-      </c>
-      <c r="G231" s="7">
-        <v>1635</v>
+      <c r="F231" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G231" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="H231" s="7">
-        <v>65.05</v>
+        <v>36.36</v>
       </c>
       <c r="I231" s="7">
-        <v>329</v>
+        <v>11</v>
       </c>
       <c r="J231" s="8" t="s">
         <v>13</v>
@@ -13530,80 +13597,80 @@
         <v>13</v>
       </c>
       <c r="N231" s="5" t="s">
-        <v>609</v>
+        <v>550</v>
       </c>
     </row>
     <row r="232" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A232" s="6" t="s">
-        <v>610</v>
+        <v>906</v>
       </c>
       <c r="B232" s="4">
         <v>14</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>588</v>
+        <v>531</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>611</v>
+        <v>551</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="F232" s="7">
-        <v>24.35</v>
+        <v>37.840000000000003</v>
       </c>
       <c r="G232" s="7">
-        <v>1577</v>
+        <v>37</v>
       </c>
       <c r="H232" s="7">
-        <v>49.35</v>
+        <v>52.63</v>
       </c>
       <c r="I232" s="7">
-        <v>383</v>
-      </c>
-      <c r="J232" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K232" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L232" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M232" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J232" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K232" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L232" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M232" s="8" t="s">
         <v>13</v>
       </c>
       <c r="N232" s="5" t="s">
-        <v>612</v>
+        <v>552</v>
       </c>
     </row>
     <row r="233" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A233" s="6" t="s">
-        <v>613</v>
+        <v>907</v>
       </c>
       <c r="B233" s="4">
         <v>14</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>588</v>
+        <v>531</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>614</v>
+        <v>553</v>
       </c>
       <c r="E233" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F233" s="7">
-        <v>8.43</v>
+        <v>48.13</v>
       </c>
       <c r="G233" s="7">
-        <v>83</v>
+        <v>187</v>
       </c>
       <c r="H233" s="7">
-        <v>23.81</v>
+        <v>62.16</v>
       </c>
       <c r="I233" s="7">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="J233" s="8" t="s">
         <v>13</v>
@@ -13618,36 +13685,36 @@
         <v>13</v>
       </c>
       <c r="N233" s="5" t="s">
-        <v>615</v>
+        <v>554</v>
       </c>
     </row>
     <row r="234" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A234" s="6" t="s">
-        <v>616</v>
+        <v>908</v>
       </c>
       <c r="B234" s="4">
         <v>14</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>588</v>
+        <v>555</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>617</v>
+        <v>556</v>
       </c>
       <c r="E234" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F234" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G234" s="7" t="s">
-        <v>13</v>
+      <c r="F234" s="7">
+        <v>36.840000000000003</v>
+      </c>
+      <c r="G234" s="7">
+        <v>38</v>
       </c>
       <c r="H234" s="7">
-        <v>36.36</v>
+        <v>66.67</v>
       </c>
       <c r="I234" s="7">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J234" s="8" t="s">
         <v>13</v>
@@ -13662,36 +13729,36 @@
         <v>13</v>
       </c>
       <c r="N234" s="5" t="s">
-        <v>618</v>
+        <v>557</v>
       </c>
     </row>
     <row r="235" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A235" s="6" t="s">
-        <v>619</v>
+        <v>909</v>
       </c>
       <c r="B235" s="4">
         <v>14</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>588</v>
+        <v>555</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>620</v>
+        <v>558</v>
       </c>
       <c r="E235" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F235" s="7">
-        <v>37.840000000000003</v>
+        <v>4.17</v>
       </c>
       <c r="G235" s="7">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="H235" s="7">
-        <v>52.63</v>
+        <v>7.69</v>
       </c>
       <c r="I235" s="7">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J235" s="8" t="s">
         <v>13</v>
@@ -13706,36 +13773,36 @@
         <v>13</v>
       </c>
       <c r="N235" s="5" t="s">
-        <v>621</v>
+        <v>557</v>
       </c>
     </row>
     <row r="236" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A236" s="6" t="s">
-        <v>622</v>
+        <v>910</v>
       </c>
       <c r="B236" s="4">
         <v>14</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>588</v>
+        <v>555</v>
       </c>
       <c r="D236" s="5" t="s">
-        <v>623</v>
+        <v>559</v>
       </c>
       <c r="E236" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F236" s="7">
-        <v>48.13</v>
+        <v>38.46</v>
       </c>
       <c r="G236" s="7">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="H236" s="7">
-        <v>62.16</v>
+        <v>48.72</v>
       </c>
       <c r="I236" s="7">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="J236" s="8" t="s">
         <v>13</v>
@@ -13750,80 +13817,80 @@
         <v>13</v>
       </c>
       <c r="N236" s="5" t="s">
-        <v>624</v>
+        <v>560</v>
       </c>
     </row>
     <row r="237" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
-        <v>626</v>
+        <v>911</v>
       </c>
       <c r="B237" s="4">
         <v>14</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>625</v>
+        <v>555</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>627</v>
+        <v>561</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="F237" s="7">
-        <v>36.840000000000003</v>
+        <v>14.29</v>
       </c>
       <c r="G237" s="7">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="H237" s="7">
-        <v>66.67</v>
+        <v>21.43</v>
       </c>
       <c r="I237" s="7">
-        <v>15</v>
-      </c>
-      <c r="J237" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K237" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L237" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M237" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="J237" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K237" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L237" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M237" s="7" t="s">
         <v>13</v>
       </c>
       <c r="N237" s="5" t="s">
-        <v>628</v>
+        <v>562</v>
       </c>
     </row>
     <row r="238" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A238" s="6" t="s">
-        <v>629</v>
+        <v>912</v>
       </c>
       <c r="B238" s="4">
         <v>14</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>625</v>
+        <v>555</v>
       </c>
       <c r="D238" s="5" t="s">
-        <v>630</v>
+        <v>563</v>
       </c>
       <c r="E238" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F238" s="7">
-        <v>4.17</v>
+        <v>43.48</v>
       </c>
       <c r="G238" s="7">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="H238" s="7">
-        <v>7.69</v>
+        <v>59.7</v>
       </c>
       <c r="I238" s="7">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="J238" s="8" t="s">
         <v>13</v>
@@ -13838,36 +13905,36 @@
         <v>13</v>
       </c>
       <c r="N238" s="5" t="s">
-        <v>628</v>
+        <v>564</v>
       </c>
     </row>
     <row r="239" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A239" s="6" t="s">
-        <v>631</v>
+        <v>913</v>
       </c>
       <c r="B239" s="4">
         <v>14</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>625</v>
+        <v>555</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>632</v>
+        <v>565</v>
       </c>
       <c r="E239" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F239" s="7">
-        <v>38.46</v>
+        <v>51.35</v>
       </c>
       <c r="G239" s="7">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="H239" s="7">
-        <v>48.72</v>
+        <v>62.5</v>
       </c>
       <c r="I239" s="7">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="J239" s="8" t="s">
         <v>13</v>
@@ -13882,80 +13949,80 @@
         <v>13</v>
       </c>
       <c r="N239" s="5" t="s">
-        <v>633</v>
+        <v>566</v>
       </c>
     </row>
     <row r="240" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
-        <v>634</v>
+        <v>914</v>
       </c>
       <c r="B240" s="4">
         <v>14</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>625</v>
+        <v>555</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>635</v>
+        <v>567</v>
       </c>
       <c r="E240" s="5" t="s">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="F240" s="7">
-        <v>14.29</v>
+        <v>11.84</v>
       </c>
       <c r="G240" s="7">
-        <v>140</v>
+        <v>76</v>
       </c>
       <c r="H240" s="7">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="I240" s="7">
-        <v>56</v>
-      </c>
-      <c r="J240" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K240" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L240" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M240" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J240" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K240" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L240" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M240" s="8" t="s">
         <v>13</v>
       </c>
       <c r="N240" s="5" t="s">
-        <v>636</v>
+        <v>568</v>
       </c>
     </row>
     <row r="241" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A241" s="6" t="s">
-        <v>637</v>
+        <v>915</v>
       </c>
       <c r="B241" s="4">
         <v>14</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>625</v>
+        <v>555</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>638</v>
+        <v>569</v>
       </c>
       <c r="E241" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F241" s="7">
-        <v>43.48</v>
+        <v>48.81</v>
       </c>
       <c r="G241" s="7">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="H241" s="7">
-        <v>59.7</v>
+        <v>66.67</v>
       </c>
       <c r="I241" s="7">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="J241" s="8" t="s">
         <v>13</v>
@@ -13970,36 +14037,36 @@
         <v>13</v>
       </c>
       <c r="N241" s="5" t="s">
-        <v>639</v>
+        <v>570</v>
       </c>
     </row>
     <row r="242" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A242" s="6" t="s">
-        <v>640</v>
+        <v>916</v>
       </c>
       <c r="B242" s="4">
         <v>14</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>625</v>
+        <v>555</v>
       </c>
       <c r="D242" s="5" t="s">
-        <v>641</v>
+        <v>571</v>
       </c>
       <c r="E242" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F242" s="7">
-        <v>51.35</v>
+        <v>46.04</v>
       </c>
       <c r="G242" s="7">
-        <v>37</v>
+        <v>328</v>
       </c>
       <c r="H242" s="7">
-        <v>62.5</v>
+        <v>60.55</v>
       </c>
       <c r="I242" s="7">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="J242" s="8" t="s">
         <v>13</v>
@@ -14014,36 +14081,36 @@
         <v>13</v>
       </c>
       <c r="N242" s="5" t="s">
-        <v>642</v>
+        <v>572</v>
       </c>
     </row>
     <row r="243" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A243" s="6" t="s">
-        <v>643</v>
+        <v>917</v>
       </c>
       <c r="B243" s="4">
         <v>14</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>625</v>
+        <v>573</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>644</v>
+        <v>574</v>
       </c>
       <c r="E243" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F243" s="7">
-        <v>11.84</v>
+        <v>1.96</v>
       </c>
       <c r="G243" s="7">
-        <v>76</v>
-      </c>
-      <c r="H243" s="7">
-        <v>20</v>
-      </c>
-      <c r="I243" s="7">
-        <v>20</v>
+        <v>102</v>
+      </c>
+      <c r="H243" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I243" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="J243" s="8" t="s">
         <v>13</v>
@@ -14058,36 +14125,36 @@
         <v>13</v>
       </c>
       <c r="N243" s="5" t="s">
-        <v>645</v>
+        <v>575</v>
       </c>
     </row>
     <row r="244" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A244" s="6" t="s">
-        <v>646</v>
+        <v>918</v>
       </c>
       <c r="B244" s="4">
         <v>14</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>625</v>
+        <v>573</v>
       </c>
       <c r="D244" s="5" t="s">
-        <v>647</v>
+        <v>576</v>
       </c>
       <c r="E244" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F244" s="7">
-        <v>48.81</v>
+        <v>57.89</v>
       </c>
       <c r="G244" s="7">
-        <v>168</v>
+        <v>19</v>
       </c>
       <c r="H244" s="7">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="I244" s="7">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="J244" s="8" t="s">
         <v>13</v>
@@ -14102,36 +14169,36 @@
         <v>13</v>
       </c>
       <c r="N244" s="5" t="s">
-        <v>648</v>
+        <v>577</v>
       </c>
     </row>
     <row r="245" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A245" s="6" t="s">
-        <v>649</v>
+        <v>919</v>
       </c>
       <c r="B245" s="4">
         <v>14</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>625</v>
+        <v>573</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>650</v>
+        <v>578</v>
       </c>
       <c r="E245" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F245" s="7">
-        <v>46.04</v>
+        <v>2.7</v>
       </c>
       <c r="G245" s="7">
-        <v>328</v>
+        <v>37</v>
       </c>
       <c r="H245" s="7">
-        <v>60.55</v>
+        <v>6.25</v>
       </c>
       <c r="I245" s="7">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="J245" s="8" t="s">
         <v>13</v>
@@ -14146,36 +14213,36 @@
         <v>13</v>
       </c>
       <c r="N245" s="5" t="s">
-        <v>651</v>
+        <v>577</v>
       </c>
     </row>
     <row r="246" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A246" s="6" t="s">
-        <v>653</v>
+        <v>920</v>
       </c>
       <c r="B246" s="4">
         <v>14</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>652</v>
+        <v>579</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>654</v>
+        <v>580</v>
       </c>
       <c r="E246" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F246" s="7">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="G246" s="7">
-        <v>102</v>
-      </c>
-      <c r="H246" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="I246" s="7" t="s">
-        <v>13</v>
+        <v>122</v>
+      </c>
+      <c r="H246" s="7">
+        <v>0</v>
+      </c>
+      <c r="I246" s="7">
+        <v>53</v>
       </c>
       <c r="J246" s="8" t="s">
         <v>13</v>
@@ -14190,124 +14257,124 @@
         <v>13</v>
       </c>
       <c r="N246" s="5" t="s">
-        <v>655</v>
+        <v>581</v>
       </c>
     </row>
     <row r="247" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A247" s="6" t="s">
-        <v>656</v>
+        <v>921</v>
       </c>
       <c r="B247" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>652</v>
+        <v>582</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>657</v>
+        <v>583</v>
       </c>
       <c r="E247" s="5" t="s">
-        <v>17</v>
+        <v>191</v>
       </c>
       <c r="F247" s="7">
-        <v>57.89</v>
+        <v>0</v>
       </c>
       <c r="G247" s="7">
-        <v>19</v>
+        <v>367</v>
       </c>
       <c r="H247" s="7">
-        <v>57.14</v>
+        <v>0</v>
       </c>
       <c r="I247" s="7">
-        <v>7</v>
-      </c>
-      <c r="J247" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K247" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L247" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M247" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J247" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K247" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L247" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M247" s="7" t="s">
         <v>13</v>
       </c>
       <c r="N247" s="5" t="s">
-        <v>658</v>
+        <v>584</v>
       </c>
     </row>
     <row r="248" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A248" s="6" t="s">
-        <v>659</v>
+        <v>922</v>
       </c>
       <c r="B248" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>652</v>
+        <v>582</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>660</v>
+        <v>585</v>
       </c>
       <c r="E248" s="5" t="s">
-        <v>17</v>
+        <v>586</v>
       </c>
       <c r="F248" s="7">
-        <v>2.7</v>
+        <v>6.59</v>
       </c>
       <c r="G248" s="7">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="H248" s="7">
-        <v>6.25</v>
+        <v>6.06</v>
       </c>
       <c r="I248" s="7">
-        <v>16</v>
-      </c>
-      <c r="J248" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K248" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L248" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M248" s="8" t="s">
-        <v>13</v>
+        <v>33</v>
+      </c>
+      <c r="J248" s="7">
+        <v>14.29</v>
+      </c>
+      <c r="K248" s="7">
+        <v>91</v>
+      </c>
+      <c r="L248" s="7">
+        <v>21.21</v>
+      </c>
+      <c r="M248" s="7">
+        <v>33</v>
       </c>
       <c r="N248" s="5" t="s">
-        <v>658</v>
+        <v>587</v>
       </c>
     </row>
     <row r="249" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A249" s="6" t="s">
-        <v>662</v>
+        <v>923</v>
       </c>
       <c r="B249" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>661</v>
+        <v>582</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>663</v>
+        <v>588</v>
       </c>
       <c r="E249" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F249" s="7">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="G249" s="7">
-        <v>122</v>
+        <v>292</v>
       </c>
       <c r="H249" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I249" s="7">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J249" s="8" t="s">
         <v>13</v>
@@ -14322,36 +14389,36 @@
         <v>13</v>
       </c>
       <c r="N249" s="5" t="s">
-        <v>664</v>
+        <v>589</v>
       </c>
     </row>
     <row r="250" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A250" s="6" t="s">
-        <v>666</v>
+        <v>924</v>
       </c>
       <c r="B250" s="4">
         <v>15</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>665</v>
+        <v>582</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>667</v>
+        <v>590</v>
       </c>
       <c r="E250" s="5" t="s">
-        <v>191</v>
+        <v>12</v>
       </c>
       <c r="F250" s="7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="G250" s="7">
-        <v>367</v>
+        <v>80</v>
       </c>
       <c r="H250" s="7">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="I250" s="7">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="J250" s="7" t="s">
         <v>13</v>
@@ -14366,256 +14433,256 @@
         <v>13</v>
       </c>
       <c r="N250" s="5" t="s">
-        <v>668</v>
+        <v>591</v>
       </c>
     </row>
     <row r="251" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A251" s="6" t="s">
-        <v>669</v>
+        <v>925</v>
       </c>
       <c r="B251" s="4">
         <v>15</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>665</v>
+        <v>582</v>
       </c>
       <c r="D251" s="5" t="s">
-        <v>670</v>
+        <v>592</v>
       </c>
       <c r="E251" s="5" t="s">
-        <v>671</v>
+        <v>12</v>
       </c>
       <c r="F251" s="7">
-        <v>6.59</v>
+        <v>0</v>
       </c>
       <c r="G251" s="7">
-        <v>91</v>
+        <v>400</v>
       </c>
       <c r="H251" s="7">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="I251" s="7">
-        <v>33</v>
-      </c>
-      <c r="J251" s="7">
-        <v>14.29</v>
-      </c>
-      <c r="K251" s="7">
-        <v>91</v>
-      </c>
-      <c r="L251" s="7">
-        <v>21.21</v>
-      </c>
-      <c r="M251" s="7">
-        <v>33</v>
+        <v>131</v>
+      </c>
+      <c r="J251" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K251" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L251" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M251" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="N251" s="5" t="s">
-        <v>672</v>
+        <v>593</v>
       </c>
     </row>
     <row r="252" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A252" s="6" t="s">
-        <v>673</v>
+        <v>926</v>
       </c>
       <c r="B252" s="4">
         <v>15</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>665</v>
+        <v>582</v>
       </c>
       <c r="D252" s="5" t="s">
-        <v>674</v>
+        <v>594</v>
       </c>
       <c r="E252" s="5" t="s">
-        <v>17</v>
+        <v>191</v>
       </c>
       <c r="F252" s="7">
-        <v>0.68</v>
+        <v>5.19</v>
       </c>
       <c r="G252" s="7">
-        <v>292</v>
+        <v>135</v>
       </c>
       <c r="H252" s="7">
-        <v>2</v>
+        <v>11.54</v>
       </c>
       <c r="I252" s="7">
-        <v>50</v>
-      </c>
-      <c r="J252" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K252" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L252" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M252" s="8" t="s">
-        <v>13</v>
+        <v>52</v>
+      </c>
+      <c r="J252" s="7">
+        <v>7.27</v>
+      </c>
+      <c r="K252" s="7">
+        <v>55</v>
+      </c>
+      <c r="L252" s="7">
+        <v>15.38</v>
+      </c>
+      <c r="M252" s="7">
+        <v>26</v>
       </c>
       <c r="N252" s="5" t="s">
-        <v>675</v>
+        <v>595</v>
       </c>
     </row>
     <row r="253" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A253" s="6" t="s">
-        <v>676</v>
+        <v>927</v>
       </c>
       <c r="B253" s="4">
+        <v>16</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="D253" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="E253" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F253" s="7">
         <v>15</v>
       </c>
-      <c r="C253" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="D253" s="5" t="s">
-        <v>677</v>
-      </c>
-      <c r="E253" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F253" s="7">
-        <v>1.25</v>
-      </c>
       <c r="G253" s="7">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="H253" s="7">
-        <v>9.09</v>
+        <v>15.48</v>
       </c>
       <c r="I253" s="7">
-        <v>44</v>
-      </c>
-      <c r="J253" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K253" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L253" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M253" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="J253" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K253" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L253" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M253" s="8" t="s">
         <v>13</v>
       </c>
       <c r="N253" s="5" t="s">
-        <v>678</v>
+        <v>598</v>
       </c>
     </row>
     <row r="254" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A254" s="6" t="s">
-        <v>679</v>
+        <v>928</v>
       </c>
       <c r="B254" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>665</v>
+        <v>596</v>
       </c>
       <c r="D254" s="5" t="s">
-        <v>680</v>
+        <v>599</v>
       </c>
       <c r="E254" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F254" s="7">
-        <v>0</v>
+        <v>17.649999999999999</v>
       </c>
       <c r="G254" s="7">
-        <v>400</v>
+        <v>170</v>
       </c>
       <c r="H254" s="7">
-        <v>0</v>
+        <v>17.649999999999999</v>
       </c>
       <c r="I254" s="7">
-        <v>131</v>
-      </c>
-      <c r="J254" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K254" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L254" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M254" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="J254" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K254" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L254" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M254" s="8" t="s">
         <v>13</v>
       </c>
       <c r="N254" s="5" t="s">
-        <v>681</v>
+        <v>600</v>
       </c>
     </row>
     <row r="255" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
-        <v>682</v>
+        <v>929</v>
       </c>
       <c r="B255" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>665</v>
+        <v>596</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>683</v>
+        <v>601</v>
       </c>
       <c r="E255" s="5" t="s">
-        <v>191</v>
+        <v>17</v>
       </c>
       <c r="F255" s="7">
-        <v>5.19</v>
+        <v>10.34</v>
       </c>
       <c r="G255" s="7">
-        <v>135</v>
+        <v>29</v>
       </c>
       <c r="H255" s="7">
-        <v>11.54</v>
+        <v>10.34</v>
       </c>
       <c r="I255" s="7">
-        <v>52</v>
-      </c>
-      <c r="J255" s="7">
-        <v>7.27</v>
-      </c>
-      <c r="K255" s="7">
-        <v>55</v>
-      </c>
-      <c r="L255" s="7">
-        <v>15.38</v>
-      </c>
-      <c r="M255" s="7">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="J255" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K255" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L255" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M255" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="N255" s="5" t="s">
-        <v>684</v>
+        <v>602</v>
       </c>
     </row>
     <row r="256" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
-        <v>686</v>
+        <v>930</v>
       </c>
       <c r="B256" s="4">
         <v>16</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>685</v>
+        <v>596</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>687</v>
+        <v>603</v>
       </c>
       <c r="E256" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F256" s="7">
-        <v>15</v>
+        <v>7.23</v>
       </c>
       <c r="G256" s="7">
-        <v>460</v>
+        <v>83</v>
       </c>
       <c r="H256" s="7">
-        <v>15.48</v>
+        <v>7.23</v>
       </c>
       <c r="I256" s="7">
-        <v>407</v>
+        <v>83</v>
       </c>
       <c r="J256" s="8" t="s">
         <v>13</v>
@@ -14630,36 +14697,36 @@
         <v>13</v>
       </c>
       <c r="N256" s="5" t="s">
-        <v>688</v>
+        <v>604</v>
       </c>
     </row>
     <row r="257" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A257" s="6" t="s">
-        <v>689</v>
+        <v>931</v>
       </c>
       <c r="B257" s="4">
         <v>16</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>685</v>
+        <v>596</v>
       </c>
       <c r="D257" s="5" t="s">
-        <v>690</v>
+        <v>605</v>
       </c>
       <c r="E257" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F257" s="7">
-        <v>17.649999999999999</v>
+        <v>5.75</v>
       </c>
       <c r="G257" s="7">
-        <v>170</v>
+        <v>87</v>
       </c>
       <c r="H257" s="7">
-        <v>17.649999999999999</v>
+        <v>5.75</v>
       </c>
       <c r="I257" s="7">
-        <v>170</v>
+        <v>87</v>
       </c>
       <c r="J257" s="8" t="s">
         <v>13</v>
@@ -14674,36 +14741,36 @@
         <v>13</v>
       </c>
       <c r="N257" s="5" t="s">
-        <v>691</v>
+        <v>604</v>
       </c>
     </row>
     <row r="258" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A258" s="6" t="s">
-        <v>692</v>
+        <v>932</v>
       </c>
       <c r="B258" s="4">
         <v>16</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>685</v>
+        <v>606</v>
       </c>
       <c r="D258" s="5" t="s">
-        <v>693</v>
+        <v>607</v>
       </c>
       <c r="E258" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F258" s="7">
-        <v>10.34</v>
+        <v>0</v>
       </c>
       <c r="G258" s="7">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="H258" s="7">
-        <v>10.34</v>
+        <v>0</v>
       </c>
       <c r="I258" s="7">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="J258" s="8" t="s">
         <v>13</v>
@@ -14718,36 +14785,36 @@
         <v>13</v>
       </c>
       <c r="N258" s="5" t="s">
-        <v>694</v>
+        <v>608</v>
       </c>
     </row>
     <row r="259" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A259" s="6" t="s">
-        <v>695</v>
+        <v>933</v>
       </c>
       <c r="B259" s="4">
         <v>16</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>685</v>
+        <v>609</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>696</v>
+        <v>610</v>
       </c>
       <c r="E259" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F259" s="7">
-        <v>7.23</v>
+        <v>0</v>
       </c>
       <c r="G259" s="7">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H259" s="7">
-        <v>7.23</v>
+        <v>0</v>
       </c>
       <c r="I259" s="7">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="J259" s="8" t="s">
         <v>13</v>
@@ -14762,36 +14829,36 @@
         <v>13</v>
       </c>
       <c r="N259" s="5" t="s">
-        <v>697</v>
+        <v>611</v>
       </c>
     </row>
     <row r="260" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A260" s="6" t="s">
-        <v>698</v>
+        <v>934</v>
       </c>
       <c r="B260" s="4">
         <v>16</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>685</v>
+        <v>612</v>
       </c>
       <c r="D260" s="5" t="s">
-        <v>699</v>
+        <v>613</v>
       </c>
       <c r="E260" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F260" s="7">
-        <v>5.75</v>
+        <v>10.84</v>
       </c>
       <c r="G260" s="7">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H260" s="7">
-        <v>5.75</v>
+        <v>10.84</v>
       </c>
       <c r="I260" s="7">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="J260" s="8" t="s">
         <v>13</v>
@@ -14806,36 +14873,36 @@
         <v>13</v>
       </c>
       <c r="N260" s="5" t="s">
-        <v>697</v>
+        <v>614</v>
       </c>
     </row>
     <row r="261" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A261" s="6" t="s">
-        <v>701</v>
+        <v>935</v>
       </c>
       <c r="B261" s="4">
         <v>16</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>700</v>
+        <v>612</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>702</v>
+        <v>615</v>
       </c>
       <c r="E261" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F261" s="7">
-        <v>0</v>
+        <v>6.96</v>
       </c>
       <c r="G261" s="7">
-        <v>42</v>
+        <v>115</v>
       </c>
       <c r="H261" s="7">
-        <v>0</v>
+        <v>8.16</v>
       </c>
       <c r="I261" s="7">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="J261" s="8" t="s">
         <v>13</v>
@@ -14850,21 +14917,21 @@
         <v>13</v>
       </c>
       <c r="N261" s="5" t="s">
-        <v>703</v>
+        <v>616</v>
       </c>
     </row>
     <row r="262" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A262" s="6" t="s">
-        <v>705</v>
+        <v>936</v>
       </c>
       <c r="B262" s="4">
         <v>16</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>704</v>
+        <v>612</v>
       </c>
       <c r="D262" s="5" t="s">
-        <v>706</v>
+        <v>617</v>
       </c>
       <c r="E262" s="5" t="s">
         <v>17</v>
@@ -14873,13 +14940,13 @@
         <v>0</v>
       </c>
       <c r="G262" s="7">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="H262" s="7">
         <v>0</v>
       </c>
       <c r="I262" s="7">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="J262" s="8" t="s">
         <v>13</v>
@@ -14894,36 +14961,36 @@
         <v>13</v>
       </c>
       <c r="N262" s="5" t="s">
-        <v>707</v>
+        <v>618</v>
       </c>
     </row>
     <row r="263" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A263" s="6" t="s">
-        <v>709</v>
+        <v>937</v>
       </c>
       <c r="B263" s="4">
         <v>16</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>708</v>
+        <v>612</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>710</v>
+        <v>619</v>
       </c>
       <c r="E263" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F263" s="7">
-        <v>10.84</v>
+        <v>20.59</v>
       </c>
       <c r="G263" s="7">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="H263" s="7">
-        <v>10.84</v>
+        <v>20.59</v>
       </c>
       <c r="I263" s="7">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="J263" s="8" t="s">
         <v>13</v>
@@ -14938,36 +15005,36 @@
         <v>13</v>
       </c>
       <c r="N263" s="5" t="s">
-        <v>711</v>
+        <v>620</v>
       </c>
     </row>
     <row r="264" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A264" s="6" t="s">
-        <v>712</v>
+        <v>938</v>
       </c>
       <c r="B264" s="4">
         <v>16</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>708</v>
+        <v>612</v>
       </c>
       <c r="D264" s="5" t="s">
-        <v>713</v>
+        <v>621</v>
       </c>
       <c r="E264" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F264" s="7">
-        <v>6.96</v>
+        <v>7.32</v>
       </c>
       <c r="G264" s="7">
-        <v>115</v>
+        <v>41</v>
       </c>
       <c r="H264" s="7">
-        <v>8.16</v>
+        <v>7.32</v>
       </c>
       <c r="I264" s="7">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="J264" s="8" t="s">
         <v>13</v>
@@ -14982,21 +15049,21 @@
         <v>13</v>
       </c>
       <c r="N264" s="5" t="s">
-        <v>714</v>
+        <v>622</v>
       </c>
     </row>
     <row r="265" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A265" s="6" t="s">
-        <v>715</v>
+        <v>939</v>
       </c>
       <c r="B265" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>708</v>
+        <v>623</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>716</v>
+        <v>624</v>
       </c>
       <c r="E265" s="5" t="s">
         <v>17</v>
@@ -15005,13 +15072,13 @@
         <v>0</v>
       </c>
       <c r="G265" s="7">
-        <v>28</v>
+        <v>166</v>
       </c>
       <c r="H265" s="7">
         <v>0</v>
       </c>
       <c r="I265" s="7">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="J265" s="8" t="s">
         <v>13</v>
@@ -15026,36 +15093,36 @@
         <v>13</v>
       </c>
       <c r="N265" s="5" t="s">
-        <v>717</v>
+        <v>625</v>
       </c>
     </row>
     <row r="266" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A266" s="6" t="s">
-        <v>718</v>
+        <v>940</v>
       </c>
       <c r="B266" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>708</v>
+        <v>626</v>
       </c>
       <c r="D266" s="5" t="s">
-        <v>719</v>
+        <v>627</v>
       </c>
       <c r="E266" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F266" s="7">
-        <v>20.59</v>
+        <v>3.85</v>
       </c>
       <c r="G266" s="7">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H266" s="7">
-        <v>20.59</v>
+        <v>7.69</v>
       </c>
       <c r="I266" s="7">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="J266" s="8" t="s">
         <v>13</v>
@@ -15070,36 +15137,36 @@
         <v>13</v>
       </c>
       <c r="N266" s="5" t="s">
-        <v>720</v>
+        <v>628</v>
       </c>
     </row>
     <row r="267" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A267" s="6" t="s">
-        <v>721</v>
+        <v>941</v>
       </c>
       <c r="B267" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>708</v>
+        <v>626</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>722</v>
+        <v>629</v>
       </c>
       <c r="E267" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F267" s="7">
-        <v>7.32</v>
+        <v>9.09</v>
       </c>
       <c r="G267" s="7">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="H267" s="7">
-        <v>7.32</v>
+        <v>11.11</v>
       </c>
       <c r="I267" s="7">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="J267" s="8" t="s">
         <v>13</v>
@@ -15114,21 +15181,21 @@
         <v>13</v>
       </c>
       <c r="N267" s="5" t="s">
-        <v>723</v>
+        <v>630</v>
       </c>
     </row>
     <row r="268" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A268" s="6" t="s">
-        <v>725</v>
+        <v>942</v>
       </c>
       <c r="B268" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>724</v>
+        <v>626</v>
       </c>
       <c r="D268" s="5" t="s">
-        <v>726</v>
+        <v>631</v>
       </c>
       <c r="E268" s="5" t="s">
         <v>17</v>
@@ -15137,13 +15204,13 @@
         <v>0</v>
       </c>
       <c r="G268" s="7">
-        <v>166</v>
+        <v>76</v>
       </c>
       <c r="H268" s="7">
         <v>0</v>
       </c>
       <c r="I268" s="7">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="J268" s="8" t="s">
         <v>13</v>
@@ -15158,36 +15225,36 @@
         <v>13</v>
       </c>
       <c r="N268" s="5" t="s">
-        <v>727</v>
+        <v>632</v>
       </c>
     </row>
     <row r="269" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A269" s="6" t="s">
-        <v>729</v>
+        <v>943</v>
       </c>
       <c r="B269" s="4">
         <v>18</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>728</v>
+        <v>626</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>730</v>
+        <v>633</v>
       </c>
       <c r="E269" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F269" s="7">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="G269" s="7">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="H269" s="7">
-        <v>7.69</v>
+        <v>0</v>
       </c>
       <c r="I269" s="7">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J269" s="8" t="s">
         <v>13</v>
@@ -15202,36 +15269,36 @@
         <v>13</v>
       </c>
       <c r="N269" s="5" t="s">
-        <v>731</v>
+        <v>634</v>
       </c>
     </row>
     <row r="270" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A270" s="6" t="s">
-        <v>732</v>
+        <v>944</v>
       </c>
       <c r="B270" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>728</v>
+        <v>635</v>
       </c>
       <c r="D270" s="5" t="s">
-        <v>733</v>
+        <v>636</v>
       </c>
       <c r="E270" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F270" s="7">
-        <v>9.09</v>
+        <v>0</v>
       </c>
       <c r="G270" s="7">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="H270" s="7">
-        <v>11.11</v>
+        <v>0</v>
       </c>
       <c r="I270" s="7">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J270" s="8" t="s">
         <v>13</v>
@@ -15246,36 +15313,36 @@
         <v>13</v>
       </c>
       <c r="N270" s="5" t="s">
-        <v>734</v>
+        <v>637</v>
       </c>
     </row>
     <row r="271" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A271" s="6" t="s">
-        <v>735</v>
+        <v>945</v>
       </c>
       <c r="B271" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>728</v>
+        <v>635</v>
       </c>
       <c r="D271" s="5" t="s">
-        <v>736</v>
+        <v>638</v>
       </c>
       <c r="E271" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F271" s="7">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="G271" s="7">
-        <v>76</v>
-      </c>
-      <c r="H271" s="7">
-        <v>0</v>
-      </c>
-      <c r="I271" s="7">
-        <v>38</v>
+        <v>116</v>
+      </c>
+      <c r="H271" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I271" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="J271" s="8" t="s">
         <v>13</v>
@@ -15290,21 +15357,21 @@
         <v>13</v>
       </c>
       <c r="N271" s="5" t="s">
-        <v>737</v>
+        <v>639</v>
       </c>
     </row>
     <row r="272" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A272" s="6" t="s">
-        <v>738</v>
+        <v>946</v>
       </c>
       <c r="B272" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>728</v>
+        <v>635</v>
       </c>
       <c r="D272" s="5" t="s">
-        <v>739</v>
+        <v>640</v>
       </c>
       <c r="E272" s="5" t="s">
         <v>17</v>
@@ -15313,13 +15380,13 @@
         <v>0</v>
       </c>
       <c r="G272" s="7">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H272" s="7">
         <v>0</v>
       </c>
       <c r="I272" s="7">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J272" s="8" t="s">
         <v>13</v>
@@ -15334,21 +15401,21 @@
         <v>13</v>
       </c>
       <c r="N272" s="5" t="s">
-        <v>740</v>
+        <v>641</v>
       </c>
     </row>
     <row r="273" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A273" s="6" t="s">
-        <v>742</v>
+        <v>947</v>
       </c>
       <c r="B273" s="4">
         <v>19</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>741</v>
+        <v>635</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>743</v>
+        <v>642</v>
       </c>
       <c r="E273" s="5" t="s">
         <v>17</v>
@@ -15357,13 +15424,13 @@
         <v>0</v>
       </c>
       <c r="G273" s="7">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="H273" s="7">
         <v>0</v>
       </c>
       <c r="I273" s="7">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J273" s="8" t="s">
         <v>13</v>
@@ -15378,36 +15445,36 @@
         <v>13</v>
       </c>
       <c r="N273" s="5" t="s">
-        <v>744</v>
+        <v>643</v>
       </c>
     </row>
     <row r="274" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
-        <v>745</v>
+        <v>948</v>
       </c>
       <c r="B274" s="4">
         <v>19</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>741</v>
+        <v>635</v>
       </c>
       <c r="D274" s="5" t="s">
-        <v>746</v>
+        <v>644</v>
       </c>
       <c r="E274" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F274" s="7">
-        <v>3.45</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="G274" s="7">
-        <v>116</v>
-      </c>
-      <c r="H274" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="I274" s="7" t="s">
-        <v>13</v>
+        <v>179</v>
+      </c>
+      <c r="H274" s="7">
+        <v>1.92</v>
+      </c>
+      <c r="I274" s="7">
+        <v>52</v>
       </c>
       <c r="J274" s="8" t="s">
         <v>13</v>
@@ -15422,21 +15489,21 @@
         <v>13</v>
       </c>
       <c r="N274" s="5" t="s">
-        <v>747</v>
+        <v>645</v>
       </c>
     </row>
     <row r="275" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A275" s="6" t="s">
-        <v>748</v>
+        <v>949</v>
       </c>
       <c r="B275" s="4">
         <v>19</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>741</v>
+        <v>635</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>749</v>
+        <v>646</v>
       </c>
       <c r="E275" s="5" t="s">
         <v>17</v>
@@ -15445,13 +15512,13 @@
         <v>0</v>
       </c>
       <c r="G275" s="7">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="H275" s="7">
         <v>0</v>
       </c>
       <c r="I275" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J275" s="8" t="s">
         <v>13</v>
@@ -15466,36 +15533,36 @@
         <v>13</v>
       </c>
       <c r="N275" s="5" t="s">
-        <v>750</v>
+        <v>647</v>
       </c>
     </row>
     <row r="276" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A276" s="6" t="s">
-        <v>751</v>
+        <v>950</v>
       </c>
       <c r="B276" s="4">
         <v>19</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>741</v>
+        <v>635</v>
       </c>
       <c r="D276" s="5" t="s">
-        <v>752</v>
+        <v>648</v>
       </c>
       <c r="E276" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F276" s="7">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="G276" s="7">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="H276" s="7">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="I276" s="7">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J276" s="8" t="s">
         <v>13</v>
@@ -15510,36 +15577,36 @@
         <v>13</v>
       </c>
       <c r="N276" s="5" t="s">
-        <v>753</v>
+        <v>649</v>
       </c>
     </row>
     <row r="277" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A277" s="6" t="s">
-        <v>754</v>
+        <v>951</v>
       </c>
       <c r="B277" s="4">
         <v>19</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>741</v>
+        <v>650</v>
       </c>
       <c r="D277" s="5" t="s">
-        <v>755</v>
+        <v>651</v>
       </c>
       <c r="E277" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F277" s="7">
-        <v>0.56000000000000005</v>
+        <v>1.32</v>
       </c>
       <c r="G277" s="7">
-        <v>179</v>
+        <v>455</v>
       </c>
       <c r="H277" s="7">
-        <v>1.92</v>
+        <v>2.11</v>
       </c>
       <c r="I277" s="7">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="J277" s="8" t="s">
         <v>13</v>
@@ -15554,80 +15621,80 @@
         <v>13</v>
       </c>
       <c r="N277" s="5" t="s">
-        <v>756</v>
+        <v>652</v>
       </c>
     </row>
     <row r="278" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A278" s="6" t="s">
-        <v>757</v>
+        <v>952</v>
       </c>
       <c r="B278" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>741</v>
+        <v>653</v>
       </c>
       <c r="D278" s="5" t="s">
-        <v>758</v>
+        <v>654</v>
       </c>
       <c r="E278" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F278" s="7">
-        <v>0</v>
-      </c>
-      <c r="G278" s="7">
-        <v>37</v>
-      </c>
-      <c r="H278" s="7">
-        <v>0</v>
-      </c>
-      <c r="I278" s="7">
-        <v>17</v>
-      </c>
-      <c r="J278" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K278" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L278" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M278" s="8" t="s">
-        <v>13</v>
+        <v>116</v>
+      </c>
+      <c r="F278" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G278" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H278" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I278" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J278" s="7">
+        <v>22.11</v>
+      </c>
+      <c r="K278" s="7">
+        <v>95</v>
+      </c>
+      <c r="L278" s="7">
+        <v>60</v>
+      </c>
+      <c r="M278" s="7">
+        <v>20</v>
       </c>
       <c r="N278" s="5" t="s">
-        <v>759</v>
+        <v>655</v>
       </c>
     </row>
     <row r="279" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A279" s="6" t="s">
-        <v>760</v>
+        <v>953</v>
       </c>
       <c r="B279" s="4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>741</v>
+        <v>656</v>
       </c>
       <c r="D279" s="5" t="s">
-        <v>761</v>
+        <v>657</v>
       </c>
       <c r="E279" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F279" s="7">
-        <v>0.73</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="G279" s="7">
-        <v>137</v>
+        <v>92</v>
       </c>
       <c r="H279" s="7">
-        <v>2.7</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="I279" s="7">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="J279" s="8" t="s">
         <v>13</v>
@@ -15642,36 +15709,36 @@
         <v>13</v>
       </c>
       <c r="N279" s="5" t="s">
-        <v>762</v>
+        <v>658</v>
       </c>
     </row>
     <row r="280" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A280" s="6" t="s">
-        <v>764</v>
+        <v>954</v>
       </c>
       <c r="B280" s="4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>763</v>
+        <v>659</v>
       </c>
       <c r="D280" s="5" t="s">
-        <v>765</v>
+        <v>660</v>
       </c>
       <c r="E280" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F280" s="7">
-        <v>1.32</v>
+        <v>5.54</v>
       </c>
       <c r="G280" s="7">
-        <v>455</v>
+        <v>271</v>
       </c>
       <c r="H280" s="7">
-        <v>2.11</v>
+        <v>8.8699999999999992</v>
       </c>
       <c r="I280" s="7">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="J280" s="8" t="s">
         <v>13</v>
@@ -15686,80 +15753,80 @@
         <v>13</v>
       </c>
       <c r="N280" s="5" t="s">
-        <v>766</v>
+        <v>661</v>
       </c>
     </row>
     <row r="281" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A281" s="6" t="s">
-        <v>768</v>
+        <v>955</v>
       </c>
       <c r="B281" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>767</v>
+        <v>659</v>
       </c>
       <c r="D281" s="5" t="s">
-        <v>769</v>
+        <v>662</v>
       </c>
       <c r="E281" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F281" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G281" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H281" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="I281" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J281" s="7">
-        <v>22.11</v>
-      </c>
-      <c r="K281" s="7">
-        <v>95</v>
-      </c>
-      <c r="L281" s="7">
-        <v>60</v>
-      </c>
-      <c r="M281" s="7">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="F281" s="7">
+        <v>10.48</v>
+      </c>
+      <c r="G281" s="7">
+        <v>124</v>
+      </c>
+      <c r="H281" s="7">
+        <v>30</v>
+      </c>
+      <c r="I281" s="7">
+        <v>30</v>
+      </c>
+      <c r="J281" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K281" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L281" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M281" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="N281" s="5" t="s">
-        <v>770</v>
+        <v>663</v>
       </c>
     </row>
     <row r="282" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A282" s="6" t="s">
-        <v>772</v>
+        <v>956</v>
       </c>
       <c r="B282" s="4">
         <v>21</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>771</v>
+        <v>664</v>
       </c>
       <c r="D282" s="5" t="s">
-        <v>773</v>
+        <v>665</v>
       </c>
       <c r="E282" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F282" s="7">
-        <v>1.0900000000000001</v>
+        <v>0</v>
       </c>
       <c r="G282" s="7">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="H282" s="7">
-        <v>1.0900000000000001</v>
+        <v>0</v>
       </c>
       <c r="I282" s="7">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="J282" s="8" t="s">
         <v>13</v>
@@ -15774,36 +15841,36 @@
         <v>13</v>
       </c>
       <c r="N282" s="5" t="s">
-        <v>774</v>
+        <v>666</v>
       </c>
     </row>
     <row r="283" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A283" s="6" t="s">
-        <v>776</v>
+        <v>957</v>
       </c>
       <c r="B283" s="4">
         <v>21</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>775</v>
+        <v>664</v>
       </c>
       <c r="D283" s="5" t="s">
-        <v>777</v>
+        <v>667</v>
       </c>
       <c r="E283" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F283" s="7">
-        <v>5.54</v>
+        <v>7.15</v>
       </c>
       <c r="G283" s="7">
-        <v>271</v>
+        <v>727</v>
       </c>
       <c r="H283" s="7">
-        <v>8.8699999999999992</v>
+        <v>10.3</v>
       </c>
       <c r="I283" s="7">
-        <v>124</v>
+        <v>398</v>
       </c>
       <c r="J283" s="8" t="s">
         <v>13</v>
@@ -15818,36 +15885,36 @@
         <v>13</v>
       </c>
       <c r="N283" s="5" t="s">
-        <v>778</v>
+        <v>668</v>
       </c>
     </row>
     <row r="284" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A284" s="6" t="s">
-        <v>779</v>
+        <v>838</v>
       </c>
       <c r="B284" s="4">
         <v>21</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>775</v>
+        <v>664</v>
       </c>
       <c r="D284" s="5" t="s">
-        <v>780</v>
+        <v>669</v>
       </c>
       <c r="E284" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F284" s="7">
-        <v>10.48</v>
+        <v>0</v>
       </c>
       <c r="G284" s="7">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="H284" s="7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I284" s="7">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J284" s="8" t="s">
         <v>13</v>
@@ -15862,185 +15929,10 @@
         <v>13</v>
       </c>
       <c r="N284" s="5" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="285" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A285" s="6" t="s">
-        <v>783</v>
-      </c>
-      <c r="B285" s="4">
-        <v>21</v>
-      </c>
-      <c r="C285" s="5" t="s">
-        <v>782</v>
-      </c>
-      <c r="D285" s="5" t="s">
-        <v>784</v>
-      </c>
-      <c r="E285" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F285" s="7">
-        <v>0</v>
-      </c>
-      <c r="G285" s="7">
-        <v>32</v>
-      </c>
-      <c r="H285" s="7">
-        <v>0</v>
-      </c>
-      <c r="I285" s="7">
-        <v>21</v>
-      </c>
-      <c r="J285" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K285" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L285" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M285" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="N285" s="5" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="286" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A286" s="6" t="s">
-        <v>786</v>
-      </c>
-      <c r="B286" s="4">
-        <v>21</v>
-      </c>
-      <c r="C286" s="5" t="s">
-        <v>782</v>
-      </c>
-      <c r="D286" s="5" t="s">
-        <v>787</v>
-      </c>
-      <c r="E286" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F286" s="7">
-        <v>7.15</v>
-      </c>
-      <c r="G286" s="7">
-        <v>727</v>
-      </c>
-      <c r="H286" s="7">
-        <v>10.3</v>
-      </c>
-      <c r="I286" s="7">
-        <v>398</v>
-      </c>
-      <c r="J286" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K286" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L286" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M286" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="N286" s="5" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="287" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="6" t="s">
-        <v>789</v>
-      </c>
-      <c r="B287" s="4">
-        <v>21</v>
-      </c>
-      <c r="C287" s="5" t="s">
-        <v>782</v>
-      </c>
-      <c r="D287" s="5" t="s">
-        <v>790</v>
-      </c>
-      <c r="E287" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F287" s="7">
-        <v>0</v>
-      </c>
-      <c r="G287" s="7">
-        <v>14</v>
-      </c>
-      <c r="H287" s="7">
-        <v>0</v>
-      </c>
-      <c r="I287" s="7">
-        <v>14</v>
-      </c>
-      <c r="J287" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K287" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L287" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M287" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="N287" s="5" t="s">
-        <v>791</v>
+        <v>670</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="41">
-    <mergeCell ref="M226:M227"/>
-    <mergeCell ref="G226:G227"/>
-    <mergeCell ref="H226:H227"/>
-    <mergeCell ref="I226:I227"/>
-    <mergeCell ref="J226:J227"/>
-    <mergeCell ref="K226:K227"/>
-    <mergeCell ref="L226:L227"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="C226:C227"/>
-    <mergeCell ref="A226:A227"/>
-    <mergeCell ref="D226:D227"/>
-    <mergeCell ref="E226:E227"/>
-    <mergeCell ref="F226:F227"/>
-    <mergeCell ref="I166:I167"/>
-    <mergeCell ref="J166:J167"/>
-    <mergeCell ref="K166:K167"/>
-    <mergeCell ref="L166:L167"/>
-    <mergeCell ref="M166:M167"/>
-    <mergeCell ref="N166:N167"/>
-    <mergeCell ref="M164:M165"/>
-    <mergeCell ref="N164:N165"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="C166:C167"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="D166:D167"/>
-    <mergeCell ref="E166:E167"/>
-    <mergeCell ref="F166:F167"/>
-    <mergeCell ref="G166:G167"/>
-    <mergeCell ref="H166:H167"/>
-    <mergeCell ref="G164:G165"/>
-    <mergeCell ref="H164:H165"/>
-    <mergeCell ref="I164:I165"/>
-    <mergeCell ref="J164:J165"/>
-    <mergeCell ref="K164:K165"/>
-    <mergeCell ref="L164:L165"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="C164:C165"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="D164:D165"/>
-    <mergeCell ref="E164:E165"/>
-    <mergeCell ref="F164:F165"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>